--- a/FieryLedLamp/Таблица эффектов.xlsx
+++ b/FieryLedLamp/Таблица эффектов.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="20827"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6C9F7984-E936-49CC-BD03-D2DD64920716}" xr6:coauthVersionLast="37" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DA60C907-16B0-455F-9A95-E722AE898313}" xr6:coauthVersionLast="37" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11310" tabRatio="168" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="569" uniqueCount="440">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="698" uniqueCount="442">
   <si>
     <t>Наст.по умолчанию</t>
   </si>
@@ -1384,6 +1384,12 @@
   </si>
   <si>
     <t>config_cycle.json</t>
+  </si>
+  <si>
+    <t>background: #1c1c1c;border-color: #ffffff3d;border-style:solidborder-style: none;background: rgba(0, 0, 0, 0);color:#16d3f2;text-shadow: #16d3f2 1px 0 10px;height: 30px;width:15%;border-radius:8px;text-align:center</t>
+  </si>
+  <si>
+    <t>style</t>
   </si>
 </sst>
 </file>
@@ -2024,7 +2030,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:BD137"/>
+  <dimension ref="A1:BD153"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="9.140625" style="35"/>
@@ -2056,12 +2062,13 @@
     <col min="29" max="29" width="17" customWidth="1"/>
     <col min="30" max="30" width="19.140625" customWidth="1"/>
     <col min="31" max="31" width="17.85546875" customWidth="1"/>
-    <col min="32" max="32" width="129.28515625" customWidth="1"/>
-    <col min="33" max="33" width="175.7109375" customWidth="1"/>
+    <col min="32" max="32" width="130" customWidth="1"/>
+    <col min="33" max="33" width="255.5703125" customWidth="1"/>
     <col min="34" max="34" width="34.7109375" customWidth="1"/>
-    <col min="35" max="35" width="14.7109375" customWidth="1"/>
-    <col min="36" max="36" width="40" customWidth="1"/>
+    <col min="35" max="35" width="13" customWidth="1"/>
+    <col min="36" max="36" width="40.28515625" customWidth="1"/>
     <col min="37" max="37" width="29" customWidth="1"/>
+    <col min="38" max="38" width="177.7109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:56" ht="14.25" customHeight="1">
@@ -2150,7 +2157,9 @@
         <v>15</v>
       </c>
       <c r="AK2" s="5"/>
-      <c r="AL2" s="5"/>
+      <c r="AL2" s="5" t="s">
+        <v>441</v>
+      </c>
       <c r="AM2" s="5"/>
       <c r="AN2" s="5"/>
       <c r="AO2" s="25"/>
@@ -2363,8 +2372,8 @@
         <v>{"type":"checkbox","class":"checkbox-big","name":"e0","title":"0. Бeлый cвeт","style":"font-size:16px;display:block","state":"{{e0}}"},</v>
       </c>
       <c r="AG4" s="2" t="str">
-        <f>CONCATENATE("{""type"":""h4"",""title"":""",A4,". ",C4,""",""style"":""width:85%;float:left""},{""type"":""input"",""title"":""папка"",""name"":""e",T4,""",""state"":""{{e",T4,"}}"",""pattern"":""[0-9]{1,2}"",""style"":""width:15%;text-align:center;border-radius:8px""},{""type"":""hr""},")</f>
-        <v>{"type":"h4","title":"0. Бeлый cвeт","style":"width:85%;float:left"},{"type":"input","title":"папка","name":"e0","state":"{{e0}}","pattern":"[0-9]{1,2}","style":"width:15%;text-align:center;border-radius:8px"},{"type":"hr"},</v>
+        <f>CONCATENATE("{""type"":""h4"",""title"":""",A4,". ",C4,""",""style"":""font-size:14px;width:85%;float:left""},{""type"":""input"",""title"":""папка"",""name"":""e",T4,""",""state"":""{{e",T4,"}}"",""pattern"":""[0-9]{1,2}"",""style"":""",AL4,"""},{""type"":""hr""},")</f>
+        <v>{"type":"h4","title":"0. Бeлый cвeт","style":"font-size:14px;width:85%;float:left"},{"type":"input","title":"папка","name":"e0","state":"{{e0}}","pattern":"[0-9]{1,2}","style":"background: #1c1c1c;border-color: #ffffff3d;border-style:solidborder-style: none;background: rgba(0, 0, 0, 0);color:#16d3f2;text-shadow: #16d3f2 1px 0 10px;height: 30px;width:15%;border-radius:8px;text-align:center"},{"type":"hr"},</v>
       </c>
       <c r="AH4" s="2" t="str">
         <f>CONCATENATE("""",A4,"""",": """,A4,".",C4,""",")</f>
@@ -2382,7 +2391,9 @@
         <f t="shared" ref="AK4:AK5" si="10">CONCATENATE("",A4,"",".",C4,"")</f>
         <v>0.Бeлый cвeт</v>
       </c>
-      <c r="AL4" s="2"/>
+      <c r="AL4" s="31" t="s">
+        <v>440</v>
+      </c>
       <c r="AM4" s="2"/>
       <c r="AN4" s="17"/>
       <c r="AO4" s="2"/>
@@ -2479,8 +2490,8 @@
         <v>{"type":"checkbox","class":"checkbox-big","name":"e1","title":"1. Аврора","style":"font-size:16px;display:block","state":"{{e1}}"},</v>
       </c>
       <c r="AG5" s="2" t="str">
-        <f ca="1">CONCATENATE("{""type"":""h4"",""title"":""",A5,". ",C5,""",""style"":""width:85%;float:left""},{""type"":""input"",""title"":""папка"",""name"":""e",T5,""",""state"":""{{e",T5,"}}"",""pattern"":""[0-9]{1,2}"",""style"":""width:15%;text-align:center;border-radius:8px""},{""type"":""hr""},")</f>
-        <v>{"type":"h4","title":"1. Аврора","style":"width:85%;float:left"},{"type":"input","title":"папка","name":"e1","state":"{{e1}}","pattern":"[0-9]{1,2}","style":"width:15%;text-align:center;border-radius:8px"},{"type":"hr"},</v>
+        <f ca="1">CONCATENATE("{""type"":""h4"",""title"":""",A5,". ",C5,""",""style"":""font-size:14px;width:85%;float:left""},{""type"":""input"",""title"":""папка"",""name"":""e",T5,""",""state"":""{{e",T5,"}}"",""pattern"":""[0-9]{1,2}"",""style"":""",AL4,"""},{""type"":""hr""},")</f>
+        <v>{"type":"h4","title":"1. Аврора","style":"font-size:14px;width:85%;float:left"},{"type":"input","title":"папка","name":"e1","state":"{{e1}}","pattern":"[0-9]{1,2}","style":"background: #1c1c1c;border-color: #ffffff3d;border-style:solidborder-style: none;background: rgba(0, 0, 0, 0);color:#16d3f2;text-shadow: #16d3f2 1px 0 10px;height: 30px;width:15%;border-radius:8px;text-align:center"},{"type":"hr"},</v>
       </c>
       <c r="AH5" s="2" t="str">
         <f ca="1">CONCATENATE("""",A5,"""",": """,A5,".",C5,""",")</f>
@@ -2497,6 +2508,9 @@
       <c r="AK5" s="2" t="str">
         <f t="shared" ca="1" si="10"/>
         <v>1.Аврора</v>
+      </c>
+      <c r="AL5" s="31" t="s">
+        <v>440</v>
       </c>
     </row>
     <row r="6" spans="1:56" ht="14.25" customHeight="1">
@@ -2589,8 +2603,8 @@
         <v>{"type":"checkbox","class":"checkbox-big","name":"e2","title":"2. Акварель","style":"font-size:16px;display:block","state":"{{e2}}"},</v>
       </c>
       <c r="AG6" s="2" t="str">
-        <f ca="1">CONCATENATE("{""type"":""h4"",""title"":""",A6,". ",C6,""",""style"":""width:85%;float:left""},{""type"":""input"",""title"":""папка"",""name"":""e",T6,""",""state"":""{{e",T6,"}}"",""pattern"":""[0-9]{1,2}"",""style"":""width:15%;text-align:center;border-radius:8px""},{""type"":""hr""},")</f>
-        <v>{"type":"h4","title":"2. Акварель","style":"width:85%;float:left"},{"type":"input","title":"папка","name":"e2","state":"{{e2}}","pattern":"[0-9]{1,2}","style":"width:15%;text-align:center;border-radius:8px"},{"type":"hr"},</v>
+        <f ca="1">CONCATENATE("{""type"":""h4"",""title"":""",A6,". ",C6,""",""style"":""font-size:14px;width:85%;float:left""},{""type"":""input"",""title"":""папка"",""name"":""e",T6,""",""state"":""{{e",T6,"}}"",""pattern"":""[0-9]{1,2}"",""style"":""",AL5,"""},{""type"":""hr""},")</f>
+        <v>{"type":"h4","title":"2. Акварель","style":"font-size:14px;width:85%;float:left"},{"type":"input","title":"папка","name":"e2","state":"{{e2}}","pattern":"[0-9]{1,2}","style":"background: #1c1c1c;border-color: #ffffff3d;border-style:solidborder-style: none;background: rgba(0, 0, 0, 0);color:#16d3f2;text-shadow: #16d3f2 1px 0 10px;height: 30px;width:15%;border-radius:8px;text-align:center"},{"type":"hr"},</v>
       </c>
       <c r="AH6" s="2" t="str">
         <f t="shared" ref="AH6:AH8" ca="1" si="15">CONCATENATE("""",A6,"""",": """,A6,".",C6,""",")</f>
@@ -2608,7 +2622,9 @@
         <f t="shared" ref="AK6:AK18" ca="1" si="16">CONCATENATE("",A6,"",".",C6,"")</f>
         <v>2.Акварель</v>
       </c>
-      <c r="AL6" s="2"/>
+      <c r="AL6" s="31" t="s">
+        <v>440</v>
+      </c>
       <c r="AM6" s="2"/>
       <c r="AN6" s="17"/>
       <c r="AO6" s="2"/>
@@ -2705,8 +2721,8 @@
         <v>{"type":"checkbox","class":"checkbox-big","name":"e3","title":"3. Аленький цветочек","style":"font-size:16px;display:block","state":"{{e3}}"},</v>
       </c>
       <c r="AG7" s="2" t="str">
-        <f t="shared" ref="AG7:AG48" ca="1" si="17">CONCATENATE("{""type"":""h4"",""title"":""",A7,". ",C7,""",""style"":""width:85%;float:left""},{""type"":""input"",""title"":""папка"",""name"":""e",T7,""",""state"":""{{e",T7,"}}"",""pattern"":""[0-9]{1,2}"",""style"":""width:15%;text-align:center;border-radius:8px""},{""type"":""hr""},")</f>
-        <v>{"type":"h4","title":"3. Аленький цветочек","style":"width:85%;float:left"},{"type":"input","title":"папка","name":"e3","state":"{{e3}}","pattern":"[0-9]{1,2}","style":"width:15%;text-align:center;border-radius:8px"},{"type":"hr"},</v>
+        <f ca="1">CONCATENATE("{""type"":""h4"",""title"":""",A7,". ",C7,""",""style"":""font-size:14px;width:85%;float:left""},{""type"":""input"",""title"":""папка"",""name"":""e",T7,""",""state"":""{{e",T7,"}}"",""pattern"":""[0-9]{1,2}"",""style"":""",AL7,"""},{""type"":""hr""},")</f>
+        <v>{"type":"h4","title":"3. Аленький цветочек","style":"font-size:14px;width:85%;float:left"},{"type":"input","title":"папка","name":"e3","state":"{{e3}}","pattern":"[0-9]{1,2}","style":"background: #1c1c1c;border-color: #ffffff3d;border-style:solidborder-style: none;background: rgba(0, 0, 0, 0);color:#16d3f2;text-shadow: #16d3f2 1px 0 10px;height: 30px;width:15%;border-radius:8px;text-align:center"},{"type":"hr"},</v>
       </c>
       <c r="AH7" s="2" t="str">
         <f t="shared" ca="1" si="15"/>
@@ -2723,6 +2739,9 @@
       <c r="AK7" s="2" t="str">
         <f t="shared" ca="1" si="16"/>
         <v>3.Аленький цветочек</v>
+      </c>
+      <c r="AL7" s="31" t="s">
+        <v>440</v>
       </c>
     </row>
     <row r="8" spans="1:56" ht="14.25" customHeight="1">
@@ -2807,8 +2826,8 @@
         <v>{"type":"checkbox","class":"checkbox-big","name":"e4","title":"4. Бассейн","style":"font-size:16px;display:block","state":"{{e4}}"},</v>
       </c>
       <c r="AG8" s="2" t="str">
-        <f t="shared" ca="1" si="17"/>
-        <v>{"type":"h4","title":"4. Бассейн","style":"width:85%;float:left"},{"type":"input","title":"папка","name":"e4","state":"{{e4}}","pattern":"[0-9]{1,2}","style":"width:15%;text-align:center;border-radius:8px"},{"type":"hr"},</v>
+        <f ca="1">CONCATENATE("{""type"":""h4"",""title"":""",A8,". ",C8,""",""style"":""font-size:14px;width:85%;float:left""},{""type"":""input"",""title"":""папка"",""name"":""e",T8,""",""state"":""{{e",T8,"}}"",""pattern"":""[0-9]{1,2}"",""style"":""",AL8,"""},{""type"":""hr""},")</f>
+        <v>{"type":"h4","title":"4. Бассейн","style":"font-size:14px;width:85%;float:left"},{"type":"input","title":"папка","name":"e4","state":"{{e4}}","pattern":"[0-9]{1,2}","style":"background: #1c1c1c;border-color: #ffffff3d;border-style:solidborder-style: none;background: rgba(0, 0, 0, 0);color:#16d3f2;text-shadow: #16d3f2 1px 0 10px;height: 30px;width:15%;border-radius:8px;text-align:center"},{"type":"hr"},</v>
       </c>
       <c r="AH8" s="2" t="str">
         <f t="shared" ca="1" si="15"/>
@@ -2826,7 +2845,9 @@
         <f t="shared" ca="1" si="16"/>
         <v>4.Бассейн</v>
       </c>
-      <c r="AL8" s="2"/>
+      <c r="AL8" s="31" t="s">
+        <v>440</v>
+      </c>
       <c r="AM8" s="2"/>
       <c r="AN8" s="17"/>
       <c r="AO8" s="2"/>
@@ -2848,7 +2869,7 @@
     </row>
     <row r="9" spans="1:56">
       <c r="A9" s="35">
-        <f t="shared" ref="A9:A18" ca="1" si="18">MAX(OFFSET(A9,-4,0,4,1))+1</f>
+        <f t="shared" ref="A9:A18" ca="1" si="17">MAX(OFFSET(A9,-4,0,4,1))+1</f>
         <v>5</v>
       </c>
       <c r="B9" s="40" t="s">
@@ -2899,23 +2920,23 @@
         <v>#define EFF_BAMBOO              (  5U)    // Бамбук</v>
       </c>
       <c r="Z9" s="2" t="str">
-        <f t="shared" ref="Z9:Z18" si="19">CONCATENATE("  {",REPT(" ",4-LEN(H9)),H9,",",REPT(" ",4-LEN(I9)),I9,",",REPT(" ",4-LEN(J9)),J9,"}, // ",C9)</f>
+        <f t="shared" ref="Z9:Z18" si="18">CONCATENATE("  {",REPT(" ",4-LEN(H9)),H9,",",REPT(" ",4-LEN(I9)),I9,",",REPT(" ",4-LEN(J9)),J9,"}, // ",C9)</f>
         <v xml:space="preserve">  {  20, 215,  90}, // Бамбук</v>
       </c>
       <c r="AA9" s="2" t="str">
-        <f t="shared" ref="AA9:AA18" ca="1" si="20">CONCATENATE("        case EFF_",B9,":",REPT(" ",20-LEN(B9)),Q9," { effTimer = millis(); ",R9,REPT(" ",30-LEN(R9)),"Eff_Tick (); }","  break;  // (",REPT(" ",3-LEN(T9)),T9,"U) ",C9)</f>
+        <f t="shared" ref="AA9:AA18" ca="1" si="19">CONCATENATE("        case EFF_",B9,":",REPT(" ",20-LEN(B9)),Q9," { effTimer = millis(); ",R9,REPT(" ",30-LEN(R9)),"Eff_Tick (); }","  break;  // (",REPT(" ",3-LEN(T9)),T9,"U) ",C9)</f>
         <v xml:space="preserve">        case EFF_BAMBOO :             DYNAMIC_DELAY_TICK { effTimer = millis(); Bamboo();                     Eff_Tick (); }  break;  // (  5U) Бамбук</v>
       </c>
       <c r="AC9" s="4" t="str">
-        <f t="shared" ref="AC9:AC18" ca="1" si="21">CONCATENATE("""","e",T9,"""",":0,")</f>
+        <f t="shared" ref="AC9:AC18" ca="1" si="20">CONCATENATE("""","e",T9,"""",":0,")</f>
         <v>"e5":0,</v>
       </c>
       <c r="AD9" s="4" t="str">
-        <f t="shared" ref="AD9:AD18" ca="1" si="22">CONCATENATE("e",T9,"=[[e",T9,"]]&amp;")</f>
+        <f t="shared" ref="AD9:AD18" ca="1" si="21">CONCATENATE("e",T9,"=[[e",T9,"]]&amp;")</f>
         <v>e5=[[e5]]&amp;</v>
       </c>
       <c r="AE9" s="4" t="str">
-        <f t="shared" ref="AE9:AE18" ca="1" si="23">CONCATENATE("""","e",T9,"""",":",S9,",")</f>
+        <f t="shared" ref="AE9:AE18" ca="1" si="22">CONCATENATE("""","e",T9,"""",":",S9,",")</f>
         <v>"e5":2,</v>
       </c>
       <c r="AF9" s="2" t="str">
@@ -2923,8 +2944,8 @@
         <v>{"type":"checkbox","class":"checkbox-big","name":"e5","title":"5. Бамбук","style":"font-size:16px;display:block","state":"{{e5}}"},</v>
       </c>
       <c r="AG9" s="2" t="str">
-        <f t="shared" ca="1" si="17"/>
-        <v>{"type":"h4","title":"5. Бамбук","style":"width:85%;float:left"},{"type":"input","title":"папка","name":"e5","state":"{{e5}}","pattern":"[0-9]{1,2}","style":"width:15%;text-align:center;border-radius:8px"},{"type":"hr"},</v>
+        <f t="shared" ref="AG9:AG48" ca="1" si="23">CONCATENATE("{""type"":""h4"",""title"":""",A9,". ",C9,""",""style"":""font-size:14px;width:85%;float:left""},{""type"":""input"",""title"":""папка"",""name"":""e",T9,""",""state"":""{{e",T9,"}}"",""pattern"":""[0-9]{1,2}"",""style"":""",AL9,"""},{""type"":""hr""},")</f>
+        <v>{"type":"h4","title":"5. Бамбук","style":"font-size:14px;width:85%;float:left"},{"type":"input","title":"папка","name":"e5","state":"{{e5}}","pattern":"[0-9]{1,2}","style":"background: #1c1c1c;border-color: #ffffff3d;border-style:solidborder-style: none;background: rgba(0, 0, 0, 0);color:#16d3f2;text-shadow: #16d3f2 1px 0 10px;height: 30px;width:15%;border-radius:8px;text-align:center"},{"type":"hr"},</v>
       </c>
       <c r="AH9" s="2" t="str">
         <f t="shared" ref="AH9:AH18" ca="1" si="24">CONCATENATE("""",A9,"""",": """,A9,".",C9,""",")</f>
@@ -2942,10 +2963,13 @@
         <f t="shared" ca="1" si="16"/>
         <v>5.Бамбук</v>
       </c>
+      <c r="AL9" s="31" t="s">
+        <v>440</v>
+      </c>
     </row>
     <row r="10" spans="1:56" ht="14.25" customHeight="1">
       <c r="A10" s="35">
-        <f t="shared" ca="1" si="18"/>
+        <f t="shared" ca="1" si="17"/>
         <v>6</v>
       </c>
       <c r="B10" s="40" t="s">
@@ -3009,11 +3033,11 @@
         <v>String("6. ,1,150,1,100,0;") +</v>
       </c>
       <c r="Z10" s="2" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="18"/>
         <v xml:space="preserve">  {  35,  20,  60}, // Безумие</v>
       </c>
       <c r="AA10" s="2" t="str">
-        <f t="shared" ca="1" si="20"/>
+        <f t="shared" ca="1" si="19"/>
         <v xml:space="preserve">        case EFF_MADNESS:             HIGH_DELAY_TICK { effTimer = millis(); madnessNoiseRoutine();        Eff_Tick (); }  break;  // (  6U) Безумие</v>
       </c>
       <c r="AB10" s="2" t="str">
@@ -3021,15 +3045,15 @@
         <v>{"name":"6. Безумие","spmin":1,"spmax":150,"scmin":1,"scmax":100,"type":0},</v>
       </c>
       <c r="AC10" s="4" t="str">
+        <f t="shared" ca="1" si="20"/>
+        <v>"e6":0,</v>
+      </c>
+      <c r="AD10" s="4" t="str">
         <f t="shared" ca="1" si="21"/>
-        <v>"e6":0,</v>
-      </c>
-      <c r="AD10" s="4" t="str">
+        <v>e6=[[e6]]&amp;</v>
+      </c>
+      <c r="AE10" s="4" t="str">
         <f t="shared" ca="1" si="22"/>
-        <v>e6=[[e6]]&amp;</v>
-      </c>
-      <c r="AE10" s="4" t="str">
-        <f t="shared" ca="1" si="23"/>
         <v>"e6":2,</v>
       </c>
       <c r="AF10" s="2" t="str">
@@ -3037,8 +3061,8 @@
         <v>{"type":"checkbox","class":"checkbox-big","name":"e6","title":"6. Безумие","style":"font-size:16px;display:block","state":"{{e6}}"},</v>
       </c>
       <c r="AG10" s="2" t="str">
-        <f t="shared" ca="1" si="17"/>
-        <v>{"type":"h4","title":"6. Безумие","style":"width:85%;float:left"},{"type":"input","title":"папка","name":"e6","state":"{{e6}}","pattern":"[0-9]{1,2}","style":"width:15%;text-align:center;border-radius:8px"},{"type":"hr"},</v>
+        <f t="shared" ca="1" si="23"/>
+        <v>{"type":"h4","title":"6. Безумие","style":"font-size:14px;width:85%;float:left"},{"type":"input","title":"папка","name":"e6","state":"{{e6}}","pattern":"[0-9]{1,2}","style":"background: #1c1c1c;border-color: #ffffff3d;border-style:solidborder-style: none;background: rgba(0, 0, 0, 0);color:#16d3f2;text-shadow: #16d3f2 1px 0 10px;height: 30px;width:15%;border-radius:8px;text-align:center"},{"type":"hr"},</v>
       </c>
       <c r="AH10" s="2" t="str">
         <f t="shared" ca="1" si="24"/>
@@ -3056,7 +3080,9 @@
         <f t="shared" ca="1" si="16"/>
         <v>6.Безумие</v>
       </c>
-      <c r="AL10" s="2"/>
+      <c r="AL10" s="31" t="s">
+        <v>440</v>
+      </c>
       <c r="AM10" s="2"/>
       <c r="AN10" s="17"/>
       <c r="AO10" s="2"/>
@@ -3078,7 +3104,7 @@
     </row>
     <row r="11" spans="1:56">
       <c r="A11" s="35">
-        <f t="shared" ca="1" si="18"/>
+        <f t="shared" ca="1" si="17"/>
         <v>7</v>
       </c>
       <c r="B11" s="40" t="s">
@@ -3129,23 +3155,23 @@
         <v>#define EFF_BALLROUTINE         (  7U)    // Блуждающий кубик</v>
       </c>
       <c r="Z11" s="2" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="18"/>
         <v xml:space="preserve">  {  20, 150,  50}, // Блуждающий кубик</v>
       </c>
       <c r="AA11" s="2" t="str">
+        <f t="shared" ca="1" si="19"/>
+        <v xml:space="preserve">        case EFF_BALLROUTINE:         DYNAMIC_DELAY_TICK { effTimer = millis(); ballRoutine();                Eff_Tick (); }  break;  // (  7U) Блуждающий кубик</v>
+      </c>
+      <c r="AC11" s="4" t="str">
         <f t="shared" ca="1" si="20"/>
-        <v xml:space="preserve">        case EFF_BALLROUTINE:         DYNAMIC_DELAY_TICK { effTimer = millis(); ballRoutine();                Eff_Tick (); }  break;  // (  7U) Блуждающий кубик</v>
-      </c>
-      <c r="AC11" s="4" t="str">
+        <v>"e7":0,</v>
+      </c>
+      <c r="AD11" s="4" t="str">
         <f t="shared" ca="1" si="21"/>
-        <v>"e7":0,</v>
-      </c>
-      <c r="AD11" s="4" t="str">
+        <v>e7=[[e7]]&amp;</v>
+      </c>
+      <c r="AE11" s="4" t="str">
         <f t="shared" ca="1" si="22"/>
-        <v>e7=[[e7]]&amp;</v>
-      </c>
-      <c r="AE11" s="4" t="str">
-        <f t="shared" ca="1" si="23"/>
         <v>"e7":2,</v>
       </c>
       <c r="AF11" s="2" t="str">
@@ -3153,8 +3179,8 @@
         <v>{"type":"checkbox","class":"checkbox-big","name":"e7","title":"7. Блуждающий кубик","style":"font-size:16px;display:block","state":"{{e7}}"},</v>
       </c>
       <c r="AG11" s="2" t="str">
-        <f t="shared" ca="1" si="17"/>
-        <v>{"type":"h4","title":"7. Блуждающий кубик","style":"width:85%;float:left"},{"type":"input","title":"папка","name":"e7","state":"{{e7}}","pattern":"[0-9]{1,2}","style":"width:15%;text-align:center;border-radius:8px"},{"type":"hr"},</v>
+        <f t="shared" ca="1" si="23"/>
+        <v>{"type":"h4","title":"7. Блуждающий кубик","style":"font-size:14px;width:85%;float:left"},{"type":"input","title":"папка","name":"e7","state":"{{e7}}","pattern":"[0-9]{1,2}","style":"background: #1c1c1c;border-color: #ffffff3d;border-style:solidborder-style: none;background: rgba(0, 0, 0, 0);color:#16d3f2;text-shadow: #16d3f2 1px 0 10px;height: 30px;width:15%;border-radius:8px;text-align:center"},{"type":"hr"},</v>
       </c>
       <c r="AH11" s="2" t="str">
         <f t="shared" ca="1" si="24"/>
@@ -3172,10 +3198,13 @@
         <f t="shared" ca="1" si="16"/>
         <v>7.Блуждающий кубик</v>
       </c>
+      <c r="AL11" s="31" t="s">
+        <v>440</v>
+      </c>
     </row>
     <row r="12" spans="1:56" ht="14.25" customHeight="1">
       <c r="A12" s="35">
-        <f t="shared" ca="1" si="18"/>
+        <f t="shared" ca="1" si="17"/>
         <v>8</v>
       </c>
       <c r="B12" s="40" t="s">
@@ -3239,11 +3268,11 @@
         <v>String("8. ,99,255,1,100,1;") +</v>
       </c>
       <c r="Z12" s="2" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="18"/>
         <v xml:space="preserve">  {  30, 212,  54}, // Водопад</v>
       </c>
       <c r="AA12" s="2" t="str">
-        <f t="shared" ca="1" si="20"/>
+        <f t="shared" ca="1" si="19"/>
         <v xml:space="preserve">        case EFF_WATERFALL:           DYNAMIC_DELAY_TICK { effTimer = millis(); fire2012WithPalette();        Eff_Tick (); }  break;  // (  8U) Водопад</v>
       </c>
       <c r="AB12" s="2" t="str">
@@ -3251,15 +3280,15 @@
         <v>{"name":"8. Водопад","spmin":99,"spmax":255,"scmin":1,"scmax":100,"type":1},</v>
       </c>
       <c r="AC12" s="4" t="str">
+        <f t="shared" ca="1" si="20"/>
+        <v>"e8":0,</v>
+      </c>
+      <c r="AD12" s="4" t="str">
         <f t="shared" ca="1" si="21"/>
-        <v>"e8":0,</v>
-      </c>
-      <c r="AD12" s="4" t="str">
+        <v>e8=[[e8]]&amp;</v>
+      </c>
+      <c r="AE12" s="4" t="str">
         <f t="shared" ca="1" si="22"/>
-        <v>e8=[[e8]]&amp;</v>
-      </c>
-      <c r="AE12" s="4" t="str">
-        <f t="shared" ca="1" si="23"/>
         <v>"e8":7,</v>
       </c>
       <c r="AF12" s="2" t="str">
@@ -3267,8 +3296,8 @@
         <v>{"type":"checkbox","class":"checkbox-big","name":"e8","title":"8. Водопад","style":"font-size:16px;display:block","state":"{{e8}}"},</v>
       </c>
       <c r="AG12" s="2" t="str">
-        <f t="shared" ca="1" si="17"/>
-        <v>{"type":"h4","title":"8. Водопад","style":"width:85%;float:left"},{"type":"input","title":"папка","name":"e8","state":"{{e8}}","pattern":"[0-9]{1,2}","style":"width:15%;text-align:center;border-radius:8px"},{"type":"hr"},</v>
+        <f t="shared" ca="1" si="23"/>
+        <v>{"type":"h4","title":"8. Водопад","style":"font-size:14px;width:85%;float:left"},{"type":"input","title":"папка","name":"e8","state":"{{e8}}","pattern":"[0-9]{1,2}","style":"background: #1c1c1c;border-color: #ffffff3d;border-style:solidborder-style: none;background: rgba(0, 0, 0, 0);color:#16d3f2;text-shadow: #16d3f2 1px 0 10px;height: 30px;width:15%;border-radius:8px;text-align:center"},{"type":"hr"},</v>
       </c>
       <c r="AH12" s="2" t="str">
         <f t="shared" ca="1" si="24"/>
@@ -3286,7 +3315,9 @@
         <f t="shared" ca="1" si="16"/>
         <v>8.Водопад</v>
       </c>
-      <c r="AL12" s="2"/>
+      <c r="AL12" s="31" t="s">
+        <v>440</v>
+      </c>
       <c r="AM12" s="2"/>
       <c r="AN12" s="17"/>
       <c r="AO12" s="2"/>
@@ -3308,7 +3339,7 @@
     </row>
     <row r="13" spans="1:56" ht="14.25" customHeight="1">
       <c r="A13" s="35">
-        <f t="shared" ca="1" si="18"/>
+        <f t="shared" ca="1" si="17"/>
         <v>9</v>
       </c>
       <c r="B13" s="40" t="s">
@@ -3372,23 +3403,23 @@
         <v>String("9. ,99,255,1,100,0;") +</v>
       </c>
       <c r="Z13" s="2" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="18"/>
         <v xml:space="preserve">  {  20, 195,  22}, // Водопад 4в1</v>
       </c>
       <c r="AA13" s="2" t="str">
+        <f t="shared" ca="1" si="19"/>
+        <v xml:space="preserve">        case EFF_WATERFALL_4IN1:      DYNAMIC_DELAY_TICK { effTimer = millis(); fire2012WithPalette4in1();    Eff_Tick (); }  break;  // (  9U) Водопад 4в1</v>
+      </c>
+      <c r="AC13" s="4" t="str">
         <f t="shared" ca="1" si="20"/>
-        <v xml:space="preserve">        case EFF_WATERFALL_4IN1:      DYNAMIC_DELAY_TICK { effTimer = millis(); fire2012WithPalette4in1();    Eff_Tick (); }  break;  // (  9U) Водопад 4в1</v>
-      </c>
-      <c r="AC13" s="4" t="str">
+        <v>"e9":0,</v>
+      </c>
+      <c r="AD13" s="4" t="str">
         <f t="shared" ca="1" si="21"/>
-        <v>"e9":0,</v>
-      </c>
-      <c r="AD13" s="4" t="str">
+        <v>e9=[[e9]]&amp;</v>
+      </c>
+      <c r="AE13" s="4" t="str">
         <f t="shared" ca="1" si="22"/>
-        <v>e9=[[e9]]&amp;</v>
-      </c>
-      <c r="AE13" s="4" t="str">
-        <f t="shared" ca="1" si="23"/>
         <v>"e9":7,</v>
       </c>
       <c r="AF13" s="2" t="str">
@@ -3396,8 +3427,8 @@
         <v>{"type":"checkbox","class":"checkbox-big","name":"e9","title":"9. Водопад 4в1","style":"font-size:16px;display:block","state":"{{e9}}"},</v>
       </c>
       <c r="AG13" s="2" t="str">
-        <f t="shared" ca="1" si="17"/>
-        <v>{"type":"h4","title":"9. Водопад 4в1","style":"width:85%;float:left"},{"type":"input","title":"папка","name":"e9","state":"{{e9}}","pattern":"[0-9]{1,2}","style":"width:15%;text-align:center;border-radius:8px"},{"type":"hr"},</v>
+        <f t="shared" ca="1" si="23"/>
+        <v>{"type":"h4","title":"9. Водопад 4в1","style":"font-size:14px;width:85%;float:left"},{"type":"input","title":"папка","name":"e9","state":"{{e9}}","pattern":"[0-9]{1,2}","style":"background: #1c1c1c;border-color: #ffffff3d;border-style:solidborder-style: none;background: rgba(0, 0, 0, 0);color:#16d3f2;text-shadow: #16d3f2 1px 0 10px;height: 30px;width:15%;border-radius:8px;text-align:center"},{"type":"hr"},</v>
       </c>
       <c r="AH13" s="2" t="str">
         <f t="shared" ca="1" si="24"/>
@@ -3415,7 +3446,9 @@
         <f t="shared" ca="1" si="16"/>
         <v>9.Водопад 4в1</v>
       </c>
-      <c r="AL13" s="2"/>
+      <c r="AL13" s="31" t="s">
+        <v>440</v>
+      </c>
       <c r="AM13" s="2"/>
       <c r="AN13" s="17"/>
       <c r="AO13" s="2"/>
@@ -3437,7 +3470,7 @@
     </row>
     <row r="14" spans="1:56" ht="14.25" customHeight="1">
       <c r="A14" s="35">
-        <f t="shared" ca="1" si="18"/>
+        <f t="shared" ca="1" si="17"/>
         <v>10</v>
       </c>
       <c r="B14" s="40" t="s">
@@ -3501,11 +3534,11 @@
         <v>String("10. ,220,255,1,100,0;") +</v>
       </c>
       <c r="Z14" s="2" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="18"/>
         <v xml:space="preserve">  {  40, 233,  80}, // Волны</v>
       </c>
       <c r="AA14" s="2" t="str">
-        <f t="shared" ca="1" si="20"/>
+        <f t="shared" ca="1" si="19"/>
         <v xml:space="preserve">        case EFF_WAVES:               DYNAMIC_DELAY_TICK { effTimer = millis(); WaveRoutine();                Eff_Tick (); }  break;  // ( 10U) Волны</v>
       </c>
       <c r="AB14" s="2" t="str">
@@ -3513,15 +3546,15 @@
         <v>{"name":"10. Волны","spmin":220,"spmax":255,"scmin":1,"scmax":100,"type":0},</v>
       </c>
       <c r="AC14" s="4" t="str">
+        <f t="shared" ca="1" si="20"/>
+        <v>"e10":0,</v>
+      </c>
+      <c r="AD14" s="4" t="str">
         <f t="shared" ca="1" si="21"/>
-        <v>"e10":0,</v>
-      </c>
-      <c r="AD14" s="4" t="str">
+        <v>e10=[[e10]]&amp;</v>
+      </c>
+      <c r="AE14" s="4" t="str">
         <f t="shared" ca="1" si="22"/>
-        <v>e10=[[e10]]&amp;</v>
-      </c>
-      <c r="AE14" s="4" t="str">
-        <f t="shared" ca="1" si="23"/>
         <v>"e10":9,</v>
       </c>
       <c r="AF14" s="2" t="str">
@@ -3529,8 +3562,8 @@
         <v>{"type":"checkbox","class":"checkbox-big","name":"e10","title":"10. Волны","style":"font-size:16px;display:block","state":"{{e10}}"},</v>
       </c>
       <c r="AG14" s="2" t="str">
-        <f t="shared" ca="1" si="17"/>
-        <v>{"type":"h4","title":"10. Волны","style":"width:85%;float:left"},{"type":"input","title":"папка","name":"e10","state":"{{e10}}","pattern":"[0-9]{1,2}","style":"width:15%;text-align:center;border-radius:8px"},{"type":"hr"},</v>
+        <f t="shared" ca="1" si="23"/>
+        <v>{"type":"h4","title":"10. Волны","style":"font-size:14px;width:85%;float:left"},{"type":"input","title":"папка","name":"e10","state":"{{e10}}","pattern":"[0-9]{1,2}","style":"background: #1c1c1c;border-color: #ffffff3d;border-style:solidborder-style: none;background: rgba(0, 0, 0, 0);color:#16d3f2;text-shadow: #16d3f2 1px 0 10px;height: 30px;width:15%;border-radius:8px;text-align:center"},{"type":"hr"},</v>
       </c>
       <c r="AH14" s="2" t="str">
         <f t="shared" ca="1" si="24"/>
@@ -3548,7 +3581,9 @@
         <f t="shared" ca="1" si="16"/>
         <v>10.Волны</v>
       </c>
-      <c r="AL14" s="2"/>
+      <c r="AL14" s="31" t="s">
+        <v>440</v>
+      </c>
       <c r="AM14" s="2"/>
       <c r="AN14" s="17"/>
       <c r="AO14" s="2"/>
@@ -3570,7 +3605,7 @@
     </row>
     <row r="15" spans="1:56">
       <c r="A15" s="35">
-        <f t="shared" ca="1" si="18"/>
+        <f t="shared" ca="1" si="17"/>
         <v>11</v>
       </c>
       <c r="B15" s="40" t="s">
@@ -3633,11 +3668,11 @@
         <v>String("11. ,1,128,1,100,1;") +</v>
       </c>
       <c r="Z15" s="2" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="18"/>
         <v xml:space="preserve">  {  45, 175,  60}, // Волшебный Фонарик</v>
       </c>
       <c r="AA15" s="2" t="str">
-        <f t="shared" ca="1" si="20"/>
+        <f t="shared" ca="1" si="19"/>
         <v xml:space="preserve">        case EFF_MAGICLANTERN:        DYNAMIC_DELAY_TICK { effTimer = millis(); MagicLantern();               Eff_Tick (); }  break;  // ( 11U) Волшебный Фонарик</v>
       </c>
       <c r="AB15" s="2" t="str">
@@ -3645,15 +3680,15 @@
         <v>{"name":"11. Волшебный Фонарик","spmin":1,"spmax":128,"scmin":1,"scmax":100,"type":1},</v>
       </c>
       <c r="AC15" s="4" t="str">
+        <f t="shared" ca="1" si="20"/>
+        <v>"e11":0,</v>
+      </c>
+      <c r="AD15" s="4" t="str">
         <f t="shared" ca="1" si="21"/>
-        <v>"e11":0,</v>
-      </c>
-      <c r="AD15" s="4" t="str">
+        <v>e11=[[e11]]&amp;</v>
+      </c>
+      <c r="AE15" s="4" t="str">
         <f t="shared" ca="1" si="22"/>
-        <v>e11=[[e11]]&amp;</v>
-      </c>
-      <c r="AE15" s="4" t="str">
-        <f t="shared" ca="1" si="23"/>
         <v>"e11":2,</v>
       </c>
       <c r="AF15" s="2" t="str">
@@ -3661,8 +3696,8 @@
         <v>{"type":"checkbox","class":"checkbox-big","name":"e11","title":"11. Волшебный Фонарик","style":"font-size:16px;display:block","state":"{{e11}}"},</v>
       </c>
       <c r="AG15" s="2" t="str">
-        <f t="shared" ca="1" si="17"/>
-        <v>{"type":"h4","title":"11. Волшебный Фонарик","style":"width:85%;float:left"},{"type":"input","title":"папка","name":"e11","state":"{{e11}}","pattern":"[0-9]{1,2}","style":"width:15%;text-align:center;border-radius:8px"},{"type":"hr"},</v>
+        <f t="shared" ca="1" si="23"/>
+        <v>{"type":"h4","title":"11. Волшебный Фонарик","style":"font-size:14px;width:85%;float:left"},{"type":"input","title":"папка","name":"e11","state":"{{e11}}","pattern":"[0-9]{1,2}","style":"background: #1c1c1c;border-color: #ffffff3d;border-style:solidborder-style: none;background: rgba(0, 0, 0, 0);color:#16d3f2;text-shadow: #16d3f2 1px 0 10px;height: 30px;width:15%;border-radius:8px;text-align:center"},{"type":"hr"},</v>
       </c>
       <c r="AH15" s="2" t="str">
         <f t="shared" ca="1" si="24"/>
@@ -3680,10 +3715,13 @@
         <f t="shared" ca="1" si="16"/>
         <v>11.Волшебный Фонарик</v>
       </c>
+      <c r="AL15" s="31" t="s">
+        <v>440</v>
+      </c>
     </row>
     <row r="16" spans="1:56" ht="14.25" customHeight="1">
       <c r="A16" s="35">
-        <f t="shared" ca="1" si="18"/>
+        <f t="shared" ca="1" si="17"/>
         <v>12</v>
       </c>
       <c r="B16" s="40" t="s">
@@ -3747,11 +3785,11 @@
         <v>String("12. ,200,255,40,75,0;") +</v>
       </c>
       <c r="Z16" s="2" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="18"/>
         <v xml:space="preserve">  {  80, 205,  40}, // Вино</v>
       </c>
       <c r="AA16" s="2" t="str">
-        <f t="shared" ca="1" si="20"/>
+        <f t="shared" ca="1" si="19"/>
         <v xml:space="preserve">        case EFF_WINE:                DYNAMIC_DELAY_TICK { effTimer = millis(); colorsWine();                 Eff_Tick (); }  break;  // ( 12U) Вино</v>
       </c>
       <c r="AB16" s="2" t="str">
@@ -3759,15 +3797,15 @@
         <v>{"name":"12. Вино","spmin":200,"spmax":255,"scmin":40,"scmax":75,"type":0},</v>
       </c>
       <c r="AC16" s="4" t="str">
+        <f t="shared" ca="1" si="20"/>
+        <v>"e12":0,</v>
+      </c>
+      <c r="AD16" s="4" t="str">
         <f t="shared" ca="1" si="21"/>
-        <v>"e12":0,</v>
-      </c>
-      <c r="AD16" s="4" t="str">
+        <v>e12=[[e12]]&amp;</v>
+      </c>
+      <c r="AE16" s="4" t="str">
         <f t="shared" ca="1" si="22"/>
-        <v>e12=[[e12]]&amp;</v>
-      </c>
-      <c r="AE16" s="4" t="str">
-        <f t="shared" ca="1" si="23"/>
         <v>"e12":2,</v>
       </c>
       <c r="AF16" s="2" t="str">
@@ -3775,8 +3813,8 @@
         <v>{"type":"checkbox","class":"checkbox-big","name":"e12","title":"12. Вино","style":"font-size:16px;display:block","state":"{{e12}}"},</v>
       </c>
       <c r="AG16" s="2" t="str">
-        <f t="shared" ca="1" si="17"/>
-        <v>{"type":"h4","title":"12. Вино","style":"width:85%;float:left"},{"type":"input","title":"папка","name":"e12","state":"{{e12}}","pattern":"[0-9]{1,2}","style":"width:15%;text-align:center;border-radius:8px"},{"type":"hr"},</v>
+        <f t="shared" ca="1" si="23"/>
+        <v>{"type":"h4","title":"12. Вино","style":"font-size:14px;width:85%;float:left"},{"type":"input","title":"папка","name":"e12","state":"{{e12}}","pattern":"[0-9]{1,2}","style":"background: #1c1c1c;border-color: #ffffff3d;border-style:solidborder-style: none;background: rgba(0, 0, 0, 0);color:#16d3f2;text-shadow: #16d3f2 1px 0 10px;height: 30px;width:15%;border-radius:8px;text-align:center"},{"type":"hr"},</v>
       </c>
       <c r="AH16" s="2" t="str">
         <f t="shared" ca="1" si="24"/>
@@ -3794,7 +3832,9 @@
         <f t="shared" ca="1" si="16"/>
         <v>12.Вино</v>
       </c>
-      <c r="AL16" s="2"/>
+      <c r="AL16" s="31" t="s">
+        <v>440</v>
+      </c>
       <c r="AM16" s="2"/>
       <c r="AN16" s="17"/>
       <c r="AO16" s="2"/>
@@ -3816,7 +3856,7 @@
     </row>
     <row r="17" spans="1:56" ht="14.25" customHeight="1">
       <c r="A17" s="35">
-        <f t="shared" ca="1" si="18"/>
+        <f t="shared" ca="1" si="17"/>
         <v>13</v>
       </c>
       <c r="B17" s="40" t="s">
@@ -3880,11 +3920,11 @@
         <v>String("13. ,1,255,1,100,1;") +</v>
       </c>
       <c r="Z17" s="2" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="18"/>
         <v xml:space="preserve">  {  25, 210,   1}, // Вихри пламени</v>
       </c>
       <c r="AA17" s="2" t="str">
-        <f t="shared" ca="1" si="20"/>
+        <f t="shared" ca="1" si="19"/>
         <v xml:space="preserve">        case EFF_WHIRL:               DYNAMIC_DELAY_TICK { effTimer = millis(); whirlRoutine(true);           Eff_Tick (); }  break;  // ( 13U) Вихри пламени</v>
       </c>
       <c r="AB17" s="2" t="str">
@@ -3892,15 +3932,15 @@
         <v>{"name":"13. Вихри пламени","spmin":1,"spmax":255,"scmin":1,"scmax":100,"type":1},</v>
       </c>
       <c r="AC17" s="4" t="str">
+        <f t="shared" ca="1" si="20"/>
+        <v>"e13":0,</v>
+      </c>
+      <c r="AD17" s="4" t="str">
         <f t="shared" ca="1" si="21"/>
-        <v>"e13":0,</v>
-      </c>
-      <c r="AD17" s="4" t="str">
+        <v>e13=[[e13]]&amp;</v>
+      </c>
+      <c r="AE17" s="4" t="str">
         <f t="shared" ca="1" si="22"/>
-        <v>e13=[[e13]]&amp;</v>
-      </c>
-      <c r="AE17" s="4" t="str">
-        <f t="shared" ca="1" si="23"/>
         <v>"e13":3,</v>
       </c>
       <c r="AF17" s="2" t="str">
@@ -3908,8 +3948,8 @@
         <v>{"type":"checkbox","class":"checkbox-big","name":"e13","title":"13. Вихри пламени","style":"font-size:16px;display:block","state":"{{e13}}"},</v>
       </c>
       <c r="AG17" s="2" t="str">
-        <f t="shared" ca="1" si="17"/>
-        <v>{"type":"h4","title":"13. Вихри пламени","style":"width:85%;float:left"},{"type":"input","title":"папка","name":"e13","state":"{{e13}}","pattern":"[0-9]{1,2}","style":"width:15%;text-align:center;border-radius:8px"},{"type":"hr"},</v>
+        <f t="shared" ca="1" si="23"/>
+        <v>{"type":"h4","title":"13. Вихри пламени","style":"font-size:14px;width:85%;float:left"},{"type":"input","title":"папка","name":"e13","state":"{{e13}}","pattern":"[0-9]{1,2}","style":"background: #1c1c1c;border-color: #ffffff3d;border-style:solidborder-style: none;background: rgba(0, 0, 0, 0);color:#16d3f2;text-shadow: #16d3f2 1px 0 10px;height: 30px;width:15%;border-radius:8px;text-align:center"},{"type":"hr"},</v>
       </c>
       <c r="AH17" s="2" t="str">
         <f t="shared" ca="1" si="24"/>
@@ -3927,7 +3967,9 @@
         <f t="shared" ca="1" si="16"/>
         <v>13.Вихри пламени</v>
       </c>
-      <c r="AL17" s="2"/>
+      <c r="AL17" s="31" t="s">
+        <v>440</v>
+      </c>
       <c r="AM17" s="2"/>
       <c r="AN17" s="17"/>
       <c r="AO17" s="2"/>
@@ -3949,7 +3991,7 @@
     </row>
     <row r="18" spans="1:56" ht="14.25" customHeight="1">
       <c r="A18" s="35">
-        <f t="shared" ca="1" si="18"/>
+        <f t="shared" ca="1" si="17"/>
         <v>14</v>
       </c>
       <c r="B18" s="40" t="s">
@@ -4013,11 +4055,11 @@
         <v>String("14. ,1,255,1,100,0;") +</v>
       </c>
       <c r="Z18" s="2" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="18"/>
         <v xml:space="preserve">  {  20, 210,  86}, // Вихри разноцветные</v>
       </c>
       <c r="AA18" s="2" t="str">
-        <f t="shared" ca="1" si="20"/>
+        <f t="shared" ca="1" si="19"/>
         <v xml:space="preserve">        case EFF_WHIRL_MULTI:         DYNAMIC_DELAY_TICK { effTimer = millis(); whirlRoutine(false);          Eff_Tick (); }  break;  // ( 14U) Вихри разноцветные</v>
       </c>
       <c r="AB18" s="2" t="str">
@@ -4025,15 +4067,15 @@
         <v>{"name":"14. Вихри разноцветные","spmin":1,"spmax":255,"scmin":1,"scmax":100,"type":0},</v>
       </c>
       <c r="AC18" s="4" t="str">
+        <f t="shared" ca="1" si="20"/>
+        <v>"e14":0,</v>
+      </c>
+      <c r="AD18" s="4" t="str">
         <f t="shared" ca="1" si="21"/>
-        <v>"e14":0,</v>
-      </c>
-      <c r="AD18" s="4" t="str">
+        <v>e14=[[e14]]&amp;</v>
+      </c>
+      <c r="AE18" s="4" t="str">
         <f t="shared" ca="1" si="22"/>
-        <v>e14=[[e14]]&amp;</v>
-      </c>
-      <c r="AE18" s="4" t="str">
-        <f t="shared" ca="1" si="23"/>
         <v>"e14":3,</v>
       </c>
       <c r="AF18" s="2" t="str">
@@ -4041,8 +4083,8 @@
         <v>{"type":"checkbox","class":"checkbox-big","name":"e14","title":"14. Вихри разноцветные","style":"font-size:16px;display:block","state":"{{e14}}"},</v>
       </c>
       <c r="AG18" s="2" t="str">
-        <f t="shared" ca="1" si="17"/>
-        <v>{"type":"h4","title":"14. Вихри разноцветные","style":"width:85%;float:left"},{"type":"input","title":"папка","name":"e14","state":"{{e14}}","pattern":"[0-9]{1,2}","style":"width:15%;text-align:center;border-radius:8px"},{"type":"hr"},</v>
+        <f t="shared" ca="1" si="23"/>
+        <v>{"type":"h4","title":"14. Вихри разноцветные","style":"font-size:14px;width:85%;float:left"},{"type":"input","title":"папка","name":"e14","state":"{{e14}}","pattern":"[0-9]{1,2}","style":"background: #1c1c1c;border-color: #ffffff3d;border-style:solidborder-style: none;background: rgba(0, 0, 0, 0);color:#16d3f2;text-shadow: #16d3f2 1px 0 10px;height: 30px;width:15%;border-radius:8px;text-align:center"},{"type":"hr"},</v>
       </c>
       <c r="AH18" s="2" t="str">
         <f t="shared" ca="1" si="24"/>
@@ -4060,7 +4102,9 @@
         <f t="shared" ca="1" si="16"/>
         <v>14.Вихри разноцветные</v>
       </c>
-      <c r="AL18" s="2"/>
+      <c r="AL18" s="31" t="s">
+        <v>440</v>
+      </c>
       <c r="AM18" s="2"/>
       <c r="AN18" s="17"/>
       <c r="AO18" s="2"/>
@@ -4174,8 +4218,8 @@
         <v>{"type":"checkbox","class":"checkbox-big","name":"e15","title":"15. Вьюга","style":"font-size:16px;display:block","state":"{{e15}}"},</v>
       </c>
       <c r="AG19" s="2" t="str">
-        <f t="shared" ca="1" si="17"/>
-        <v>{"type":"h4","title":"15. Вьюга","style":"width:85%;float:left"},{"type":"input","title":"папка","name":"e15","state":"{{e15}}","pattern":"[0-9]{1,2}","style":"width:15%;text-align:center;border-radius:8px"},{"type":"hr"},</v>
+        <f t="shared" ca="1" si="23"/>
+        <v>{"type":"h4","title":"15. Вьюга","style":"font-size:14px;width:85%;float:left"},{"type":"input","title":"папка","name":"e15","state":"{{e15}}","pattern":"[0-9]{1,2}","style":"background: #1c1c1c;border-color: #ffffff3d;border-style:solidborder-style: none;background: rgba(0, 0, 0, 0);color:#16d3f2;text-shadow: #16d3f2 1px 0 10px;height: 30px;width:15%;border-radius:8px;text-align:center"},{"type":"hr"},</v>
       </c>
       <c r="AH19" s="2" t="str">
         <f t="shared" ref="AH19:AH28" ca="1" si="44">CONCATENATE("""",A19,"""",": """,A19,".",C19,""",")</f>
@@ -4193,7 +4237,9 @@
         <f t="shared" ref="AK19:AK26" ca="1" si="47">CONCATENATE("",A19,"",".",C19,"")</f>
         <v>15.Вьюга</v>
       </c>
-      <c r="AL19" s="2"/>
+      <c r="AL19" s="31" t="s">
+        <v>440</v>
+      </c>
       <c r="AM19" s="2"/>
       <c r="AN19" s="17"/>
       <c r="AO19" s="2"/>
@@ -4307,8 +4353,8 @@
         <v>{"type":"checkbox","class":"checkbox-big","name":"e16","title":"16. Гроза в банке","style":"font-size:16px;display:block","state":"{{e16}}"},</v>
       </c>
       <c r="AG20" s="2" t="str">
-        <f t="shared" ca="1" si="17"/>
-        <v>{"type":"h4","title":"16. Гроза в банке","style":"width:85%;float:left"},{"type":"input","title":"папка","name":"e16","state":"{{e16}}","pattern":"[0-9]{1,2}","style":"width:15%;text-align:center;border-radius:8px"},{"type":"hr"},</v>
+        <f t="shared" ca="1" si="23"/>
+        <v>{"type":"h4","title":"16. Гроза в банке","style":"font-size:14px;width:85%;float:left"},{"type":"input","title":"папка","name":"e16","state":"{{e16}}","pattern":"[0-9]{1,2}","style":"background: #1c1c1c;border-color: #ffffff3d;border-style:solidborder-style: none;background: rgba(0, 0, 0, 0);color:#16d3f2;text-shadow: #16d3f2 1px 0 10px;height: 30px;width:15%;border-radius:8px;text-align:center"},{"type":"hr"},</v>
       </c>
       <c r="AH20" s="2" t="str">
         <f t="shared" ca="1" si="44"/>
@@ -4326,7 +4372,9 @@
         <f t="shared" ca="1" si="47"/>
         <v>16.Гроза в банке</v>
       </c>
-      <c r="AL20" s="2"/>
+      <c r="AL20" s="31" t="s">
+        <v>440</v>
+      </c>
       <c r="AM20" s="2"/>
       <c r="AN20" s="17"/>
       <c r="AO20" s="2"/>
@@ -4436,8 +4484,8 @@
         <v>{"type":"checkbox","class":"checkbox-big","name":"e17","title":"17. ДНК","style":"font-size:16px;display:block","state":"{{e17}}"},</v>
       </c>
       <c r="AG21" s="2" t="str">
-        <f t="shared" ca="1" si="17"/>
-        <v>{"type":"h4","title":"17. ДНК","style":"width:85%;float:left"},{"type":"input","title":"папка","name":"e17","state":"{{e17}}","pattern":"[0-9]{1,2}","style":"width:15%;text-align:center;border-radius:8px"},{"type":"hr"},</v>
+        <f t="shared" ca="1" si="23"/>
+        <v>{"type":"h4","title":"17. ДНК","style":"font-size:14px;width:85%;float:left"},{"type":"input","title":"папка","name":"e17","state":"{{e17}}","pattern":"[0-9]{1,2}","style":"background: #1c1c1c;border-color: #ffffff3d;border-style:solidborder-style: none;background: rgba(0, 0, 0, 0);color:#16d3f2;text-shadow: #16d3f2 1px 0 10px;height: 30px;width:15%;border-radius:8px;text-align:center"},{"type":"hr"},</v>
       </c>
       <c r="AH21" s="2" t="str">
         <f t="shared" ca="1" si="44"/>
@@ -4455,7 +4503,9 @@
         <f t="shared" ca="1" si="47"/>
         <v>17.ДНК</v>
       </c>
-      <c r="AL21" s="2"/>
+      <c r="AL21" s="31" t="s">
+        <v>440</v>
+      </c>
       <c r="AM21" s="2"/>
       <c r="AN21" s="17"/>
       <c r="AO21" s="2"/>
@@ -4569,8 +4619,8 @@
         <v>{"type":"checkbox","class":"checkbox-big","name":"e18","title":"18. Дым","style":"font-size:16px;display:block","state":"{{e18}}"},</v>
       </c>
       <c r="AG22" s="2" t="str">
-        <f t="shared" ca="1" si="17"/>
-        <v>{"type":"h4","title":"18. Дым","style":"width:85%;float:left"},{"type":"input","title":"папка","name":"e18","state":"{{e18}}","pattern":"[0-9]{1,2}","style":"width:15%;text-align:center;border-radius:8px"},{"type":"hr"},</v>
+        <f t="shared" ca="1" si="23"/>
+        <v>{"type":"h4","title":"18. Дым","style":"font-size:14px;width:85%;float:left"},{"type":"input","title":"папка","name":"e18","state":"{{e18}}","pattern":"[0-9]{1,2}","style":"background: #1c1c1c;border-color: #ffffff3d;border-style:solidborder-style: none;background: rgba(0, 0, 0, 0);color:#16d3f2;text-shadow: #16d3f2 1px 0 10px;height: 30px;width:15%;border-radius:8px;text-align:center"},{"type":"hr"},</v>
       </c>
       <c r="AH22" s="2" t="str">
         <f t="shared" ca="1" si="44"/>
@@ -4588,7 +4638,9 @@
         <f t="shared" ca="1" si="47"/>
         <v>18.Дым</v>
       </c>
-      <c r="AL22" s="2"/>
+      <c r="AL22" s="31" t="s">
+        <v>440</v>
+      </c>
       <c r="AM22" s="2"/>
       <c r="AN22" s="17"/>
       <c r="AO22" s="2"/>
@@ -4702,8 +4754,8 @@
         <v>{"type":"checkbox","class":"checkbox-big","name":"e19","title":"19. Дым разноцветный","style":"font-size:16px;display:block","state":"{{e19}}"},</v>
       </c>
       <c r="AG23" s="2" t="str">
-        <f t="shared" ca="1" si="17"/>
-        <v>{"type":"h4","title":"19. Дым разноцветный","style":"width:85%;float:left"},{"type":"input","title":"папка","name":"e19","state":"{{e19}}","pattern":"[0-9]{1,2}","style":"width:15%;text-align:center;border-radius:8px"},{"type":"hr"},</v>
+        <f t="shared" ca="1" si="23"/>
+        <v>{"type":"h4","title":"19. Дым разноцветный","style":"font-size:14px;width:85%;float:left"},{"type":"input","title":"папка","name":"e19","state":"{{e19}}","pattern":"[0-9]{1,2}","style":"background: #1c1c1c;border-color: #ffffff3d;border-style:solidborder-style: none;background: rgba(0, 0, 0, 0);color:#16d3f2;text-shadow: #16d3f2 1px 0 10px;height: 30px;width:15%;border-radius:8px;text-align:center"},{"type":"hr"},</v>
       </c>
       <c r="AH23" s="2" t="str">
         <f t="shared" ca="1" si="44"/>
@@ -4721,7 +4773,9 @@
         <f t="shared" ca="1" si="47"/>
         <v>19.Дым разноцветный</v>
       </c>
-      <c r="AL23" s="2"/>
+      <c r="AL23" s="31" t="s">
+        <v>440</v>
+      </c>
       <c r="AM23" s="2"/>
       <c r="AN23" s="17"/>
       <c r="AO23" s="2"/>
@@ -4835,8 +4889,8 @@
         <v>{"type":"checkbox","class":"checkbox-big","name":"e20","title":"20. Дымовые шашки","style":"font-size:16px;display:block","state":"{{e20}}"},</v>
       </c>
       <c r="AG24" s="2" t="str">
-        <f t="shared" ca="1" si="17"/>
-        <v>{"type":"h4","title":"20. Дымовые шашки","style":"width:85%;float:left"},{"type":"input","title":"папка","name":"e20","state":"{{e20}}","pattern":"[0-9]{1,2}","style":"width:15%;text-align:center;border-radius:8px"},{"type":"hr"},</v>
+        <f t="shared" ca="1" si="23"/>
+        <v>{"type":"h4","title":"20. Дымовые шашки","style":"font-size:14px;width:85%;float:left"},{"type":"input","title":"папка","name":"e20","state":"{{e20}}","pattern":"[0-9]{1,2}","style":"background: #1c1c1c;border-color: #ffffff3d;border-style:solidborder-style: none;background: rgba(0, 0, 0, 0);color:#16d3f2;text-shadow: #16d3f2 1px 0 10px;height: 30px;width:15%;border-radius:8px;text-align:center"},{"type":"hr"},</v>
       </c>
       <c r="AH24" s="2" t="str">
         <f t="shared" ca="1" si="44"/>
@@ -4854,7 +4908,9 @@
         <f t="shared" ca="1" si="47"/>
         <v>20.Дымовые шашки</v>
       </c>
-      <c r="AL24" s="2"/>
+      <c r="AL24" s="31" t="s">
+        <v>440</v>
+      </c>
       <c r="AM24" s="2"/>
       <c r="AN24" s="17"/>
       <c r="AO24" s="2"/>
@@ -4968,8 +5024,8 @@
         <v>{"type":"checkbox","class":"checkbox-big","name":"e21","title":"21. Жидкая лампа","style":"font-size:16px;display:block","state":"{{e21}}"},</v>
       </c>
       <c r="AG25" s="2" t="str">
-        <f t="shared" ca="1" si="17"/>
-        <v>{"type":"h4","title":"21. Жидкая лампа","style":"width:85%;float:left"},{"type":"input","title":"папка","name":"e21","state":"{{e21}}","pattern":"[0-9]{1,2}","style":"width:15%;text-align:center;border-radius:8px"},{"type":"hr"},</v>
+        <f t="shared" ca="1" si="23"/>
+        <v>{"type":"h4","title":"21. Жидкая лампа","style":"font-size:14px;width:85%;float:left"},{"type":"input","title":"папка","name":"e21","state":"{{e21}}","pattern":"[0-9]{1,2}","style":"background: #1c1c1c;border-color: #ffffff3d;border-style:solidborder-style: none;background: rgba(0, 0, 0, 0);color:#16d3f2;text-shadow: #16d3f2 1px 0 10px;height: 30px;width:15%;border-radius:8px;text-align:center"},{"type":"hr"},</v>
       </c>
       <c r="AH25" s="2" t="str">
         <f t="shared" ca="1" si="44"/>
@@ -4987,7 +5043,9 @@
         <f t="shared" ca="1" si="47"/>
         <v>21.Жидкая лампа</v>
       </c>
-      <c r="AL25" s="2"/>
+      <c r="AL25" s="31" t="s">
+        <v>440</v>
+      </c>
       <c r="AM25" s="2"/>
       <c r="AN25" s="17"/>
       <c r="AO25" s="2"/>
@@ -5101,8 +5159,8 @@
         <v>{"type":"checkbox","class":"checkbox-big","name":"e22","title":"22. Жидкая лампа авто","style":"font-size:16px;display:block","state":"{{e22}}"},</v>
       </c>
       <c r="AG26" s="2" t="str">
-        <f t="shared" ca="1" si="17"/>
-        <v>{"type":"h4","title":"22. Жидкая лампа авто","style":"width:85%;float:left"},{"type":"input","title":"папка","name":"e22","state":"{{e22}}","pattern":"[0-9]{1,2}","style":"width:15%;text-align:center;border-radius:8px"},{"type":"hr"},</v>
+        <f t="shared" ca="1" si="23"/>
+        <v>{"type":"h4","title":"22. Жидкая лампа авто","style":"font-size:14px;width:85%;float:left"},{"type":"input","title":"папка","name":"e22","state":"{{e22}}","pattern":"[0-9]{1,2}","style":"background: #1c1c1c;border-color: #ffffff3d;border-style:solidborder-style: none;background: rgba(0, 0, 0, 0);color:#16d3f2;text-shadow: #16d3f2 1px 0 10px;height: 30px;width:15%;border-radius:8px;text-align:center"},{"type":"hr"},</v>
       </c>
       <c r="AH26" s="2" t="str">
         <f t="shared" ca="1" si="44"/>
@@ -5120,7 +5178,9 @@
         <f t="shared" ca="1" si="47"/>
         <v>22.Жидкая лампа авто</v>
       </c>
-      <c r="AL26" s="2"/>
+      <c r="AL26" s="31" t="s">
+        <v>440</v>
+      </c>
       <c r="AM26" s="2"/>
       <c r="AN26" s="17"/>
       <c r="AO26" s="2"/>
@@ -5234,8 +5294,8 @@
         <v>{"type":"checkbox","class":"checkbox-big","name":"e23","title":"23. Завиток","style":"font-size:16px;display:block","state":"{{e23}}"},</v>
       </c>
       <c r="AG27" s="2" t="str">
-        <f t="shared" ca="1" si="17"/>
-        <v>{"type":"h4","title":"23. Завиток","style":"width:85%;float:left"},{"type":"input","title":"папка","name":"e23","state":"{{e23}}","pattern":"[0-9]{1,2}","style":"width:15%;text-align:center;border-radius:8px"},{"type":"hr"},</v>
+        <f t="shared" ca="1" si="23"/>
+        <v>{"type":"h4","title":"23. Завиток","style":"font-size:14px;width:85%;float:left"},{"type":"input","title":"папка","name":"e23","state":"{{e23}}","pattern":"[0-9]{1,2}","style":"background: #1c1c1c;border-color: #ffffff3d;border-style:solidborder-style: none;background: rgba(0, 0, 0, 0);color:#16d3f2;text-shadow: #16d3f2 1px 0 10px;height: 30px;width:15%;border-radius:8px;text-align:center"},{"type":"hr"},</v>
       </c>
       <c r="AH27" s="2" t="str">
         <f t="shared" ca="1" si="44"/>
@@ -5253,7 +5313,9 @@
         <f t="shared" ref="AK27:AK30" ca="1" si="50">CONCATENATE("",A27,"",".",C27,"")</f>
         <v>23.Завиток</v>
       </c>
-      <c r="AL27" s="2"/>
+      <c r="AL27" s="31" t="s">
+        <v>440</v>
+      </c>
       <c r="AM27" s="2"/>
       <c r="AN27" s="17"/>
       <c r="AO27" s="2"/>
@@ -5350,8 +5412,8 @@
         <v>{"type":"checkbox","class":"checkbox-big","name":"e24","title":"24. Звезды","style":"font-size:16px;display:block","state":"{{e24}}"},</v>
       </c>
       <c r="AG28" s="2" t="str">
-        <f t="shared" ca="1" si="17"/>
-        <v>{"type":"h4","title":"24. Звезды","style":"width:85%;float:left"},{"type":"input","title":"папка","name":"e24","state":"{{e24}}","pattern":"[0-9]{1,2}","style":"width:15%;text-align:center;border-radius:8px"},{"type":"hr"},</v>
+        <f t="shared" ca="1" si="23"/>
+        <v>{"type":"h4","title":"24. Звезды","style":"font-size:14px;width:85%;float:left"},{"type":"input","title":"папка","name":"e24","state":"{{e24}}","pattern":"[0-9]{1,2}","style":"background: #1c1c1c;border-color: #ffffff3d;border-style:solidborder-style: none;background: rgba(0, 0, 0, 0);color:#16d3f2;text-shadow: #16d3f2 1px 0 10px;height: 30px;width:15%;border-radius:8px;text-align:center"},{"type":"hr"},</v>
       </c>
       <c r="AH28" s="2" t="str">
         <f t="shared" ca="1" si="44"/>
@@ -5368,6 +5430,9 @@
       <c r="AK28" s="2" t="str">
         <f t="shared" ca="1" si="50"/>
         <v>24.Звезды</v>
+      </c>
+      <c r="AL28" s="31" t="s">
+        <v>440</v>
       </c>
     </row>
     <row r="29" spans="1:56" ht="14.25" customHeight="1">
@@ -5464,8 +5529,8 @@
         <v>{"type":"checkbox","class":"checkbox-big","name":"e25","title":"25. Зебра","style":"font-size:16px;display:block","state":"{{e25}}"},</v>
       </c>
       <c r="AG29" s="2" t="str">
-        <f t="shared" ca="1" si="17"/>
-        <v>{"type":"h4","title":"25. Зебра","style":"width:85%;float:left"},{"type":"input","title":"папка","name":"e25","state":"{{e25}}","pattern":"[0-9]{1,2}","style":"width:15%;text-align:center;border-radius:8px"},{"type":"hr"},</v>
+        <f t="shared" ca="1" si="23"/>
+        <v>{"type":"h4","title":"25. Зебра","style":"font-size:14px;width:85%;float:left"},{"type":"input","title":"папка","name":"e25","state":"{{e25}}","pattern":"[0-9]{1,2}","style":"background: #1c1c1c;border-color: #ffffff3d;border-style:solidborder-style: none;background: rgba(0, 0, 0, 0);color:#16d3f2;text-shadow: #16d3f2 1px 0 10px;height: 30px;width:15%;border-radius:8px;text-align:center"},{"type":"hr"},</v>
       </c>
       <c r="AH29" s="2" t="str">
         <f t="shared" ref="AH29:AH30" ca="1" si="61">CONCATENATE("""",A29,"""",": """,A29,".",C29,""",")</f>
@@ -5483,7 +5548,9 @@
         <f t="shared" ca="1" si="50"/>
         <v>25.Зебра</v>
       </c>
-      <c r="AL29" s="2"/>
+      <c r="AL29" s="31" t="s">
+        <v>440</v>
+      </c>
       <c r="AM29" s="2"/>
       <c r="AN29" s="17"/>
       <c r="AO29" s="2"/>
@@ -5596,8 +5663,8 @@
         <v>{"type":"checkbox","class":"checkbox-big","name":"e26","title":"26. Земля Тикси","style":"font-size:16px;display:block","state":"{{e26}}"},</v>
       </c>
       <c r="AG30" s="2" t="str">
-        <f t="shared" ca="1" si="17"/>
-        <v>{"type":"h4","title":"26. Земля Тикси","style":"width:85%;float:left"},{"type":"input","title":"папка","name":"e26","state":"{{e26}}","pattern":"[0-9]{1,2}","style":"width:15%;text-align:center;border-radius:8px"},{"type":"hr"},</v>
+        <f t="shared" ca="1" si="23"/>
+        <v>{"type":"h4","title":"26. Земля Тикси","style":"font-size:14px;width:85%;float:left"},{"type":"input","title":"папка","name":"e26","state":"{{e26}}","pattern":"[0-9]{1,2}","style":"background: #1c1c1c;border-color: #ffffff3d;border-style:solidborder-style: none;background: rgba(0, 0, 0, 0);color:#16d3f2;text-shadow: #16d3f2 1px 0 10px;height: 30px;width:15%;border-radius:8px;text-align:center"},{"type":"hr"},</v>
       </c>
       <c r="AH30" s="2" t="str">
         <f t="shared" ca="1" si="61"/>
@@ -5614,6 +5681,9 @@
       <c r="AK30" s="2" t="str">
         <f t="shared" ca="1" si="50"/>
         <v>26.Земля Тикси</v>
+      </c>
+      <c r="AL30" s="31" t="s">
+        <v>440</v>
       </c>
     </row>
     <row r="31" spans="1:56" ht="14.25" customHeight="1">
@@ -5710,8 +5780,8 @@
         <v>{"type":"checkbox","class":"checkbox-big","name":"e27","title":"27. Змейки","style":"font-size:16px;display:block","state":"{{e27}}"},</v>
       </c>
       <c r="AG31" s="2" t="str">
-        <f t="shared" ca="1" si="17"/>
-        <v>{"type":"h4","title":"27. Змейки","style":"width:85%;float:left"},{"type":"input","title":"папка","name":"e27","state":"{{e27}}","pattern":"[0-9]{1,2}","style":"width:15%;text-align:center;border-radius:8px"},{"type":"hr"},</v>
+        <f t="shared" ca="1" si="23"/>
+        <v>{"type":"h4","title":"27. Змейки","style":"font-size:14px;width:85%;float:left"},{"type":"input","title":"папка","name":"e27","state":"{{e27}}","pattern":"[0-9]{1,2}","style":"background: #1c1c1c;border-color: #ffffff3d;border-style:solidborder-style: none;background: rgba(0, 0, 0, 0);color:#16d3f2;text-shadow: #16d3f2 1px 0 10px;height: 30px;width:15%;border-radius:8px;text-align:center"},{"type":"hr"},</v>
       </c>
       <c r="AH31" s="2" t="str">
         <f ca="1">CONCATENATE("""",A31,"""",": """,A31,".",C31,""",")</f>
@@ -5729,7 +5799,9 @@
         <f t="shared" ref="AK31:AK42" ca="1" si="65">CONCATENATE("",A31,"",".",C31,"")</f>
         <v>27.Змейки</v>
       </c>
-      <c r="AL31" s="2"/>
+      <c r="AL31" s="31" t="s">
+        <v>440</v>
+      </c>
       <c r="AM31" s="2"/>
       <c r="AN31" s="17"/>
       <c r="AO31" s="2"/>
@@ -5843,8 +5915,8 @@
         <v>{"type":"checkbox","class":"checkbox-big","name":"e28","title":"28. Источник","style":"font-size:16px;display:block","state":"{{e28}}"},</v>
       </c>
       <c r="AG32" s="2" t="str">
-        <f t="shared" ca="1" si="17"/>
-        <v>{"type":"h4","title":"28. Источник","style":"width:85%;float:left"},{"type":"input","title":"папка","name":"e28","state":"{{e28}}","pattern":"[0-9]{1,2}","style":"width:15%;text-align:center;border-radius:8px"},{"type":"hr"},</v>
+        <f t="shared" ca="1" si="23"/>
+        <v>{"type":"h4","title":"28. Источник","style":"font-size:14px;width:85%;float:left"},{"type":"input","title":"папка","name":"e28","state":"{{e28}}","pattern":"[0-9]{1,2}","style":"background: #1c1c1c;border-color: #ffffff3d;border-style:solidborder-style: none;background: rgba(0, 0, 0, 0);color:#16d3f2;text-shadow: #16d3f2 1px 0 10px;height: 30px;width:15%;border-radius:8px;text-align:center"},{"type":"hr"},</v>
       </c>
       <c r="AH32" s="2" t="str">
         <f ca="1">CONCATENATE("""",A32,"""",": """,A32,".",C32,""",")</f>
@@ -5862,7 +5934,9 @@
         <f t="shared" ca="1" si="65"/>
         <v>28.Источник</v>
       </c>
-      <c r="AL32" s="2"/>
+      <c r="AL32" s="31" t="s">
+        <v>440</v>
+      </c>
       <c r="AM32" s="2"/>
       <c r="AN32" s="17"/>
       <c r="AO32" s="2"/>
@@ -5975,8 +6049,8 @@
         <v>{"type":"checkbox","class":"checkbox-big","name":"e29","title":"29. Капли на воде","style":"font-size:16px;display:block","state":"{{e29}}"},</v>
       </c>
       <c r="AG33" s="2" t="str">
-        <f t="shared" ca="1" si="17"/>
-        <v>{"type":"h4","title":"29. Капли на воде","style":"width:85%;float:left"},{"type":"input","title":"папка","name":"e29","state":"{{e29}}","pattern":"[0-9]{1,2}","style":"width:15%;text-align:center;border-radius:8px"},{"type":"hr"},</v>
+        <f t="shared" ca="1" si="23"/>
+        <v>{"type":"h4","title":"29. Капли на воде","style":"font-size:14px;width:85%;float:left"},{"type":"input","title":"папка","name":"e29","state":"{{e29}}","pattern":"[0-9]{1,2}","style":"background: #1c1c1c;border-color: #ffffff3d;border-style:solidborder-style: none;background: rgba(0, 0, 0, 0);color:#16d3f2;text-shadow: #16d3f2 1px 0 10px;height: 30px;width:15%;border-radius:8px;text-align:center"},{"type":"hr"},</v>
       </c>
       <c r="AH33" s="2" t="str">
         <f ca="1">CONCATENATE("""",A33,"""",": """,A33,".",C33,""",")</f>
@@ -5993,6 +6067,9 @@
       <c r="AK33" s="2" t="str">
         <f t="shared" ca="1" si="65"/>
         <v>29.Капли на воде</v>
+      </c>
+      <c r="AL33" s="31" t="s">
+        <v>440</v>
       </c>
     </row>
     <row r="34" spans="1:56" ht="14.25" customHeight="1">
@@ -6089,8 +6166,8 @@
         <v>{"type":"checkbox","class":"checkbox-big","name":"e30","title":"30. Капли на стекле","style":"font-size:16px;display:block","state":"{{e30}}"},</v>
       </c>
       <c r="AG34" s="2" t="str">
-        <f t="shared" ca="1" si="17"/>
-        <v>{"type":"h4","title":"30. Капли на стекле","style":"width:85%;float:left"},{"type":"input","title":"папка","name":"e30","state":"{{e30}}","pattern":"[0-9]{1,2}","style":"width:15%;text-align:center;border-radius:8px"},{"type":"hr"},</v>
+        <f t="shared" ca="1" si="23"/>
+        <v>{"type":"h4","title":"30. Капли на стекле","style":"font-size:14px;width:85%;float:left"},{"type":"input","title":"папка","name":"e30","state":"{{e30}}","pattern":"[0-9]{1,2}","style":"background: #1c1c1c;border-color: #ffffff3d;border-style:solidborder-style: none;background: rgba(0, 0, 0, 0);color:#16d3f2;text-shadow: #16d3f2 1px 0 10px;height: 30px;width:15%;border-radius:8px;text-align:center"},{"type":"hr"},</v>
       </c>
       <c r="AH34" s="2" t="str">
         <f t="shared" ref="AH34:AH42" ca="1" si="78">CONCATENATE("""",A34,"""",": """,A34,".",C34,""",")</f>
@@ -6108,7 +6185,9 @@
         <f t="shared" ca="1" si="65"/>
         <v>30.Капли на стекле</v>
       </c>
-      <c r="AL34" s="2"/>
+      <c r="AL34" s="31" t="s">
+        <v>440</v>
+      </c>
       <c r="AM34" s="2"/>
       <c r="AN34" s="17"/>
       <c r="AO34" s="2"/>
@@ -6222,8 +6301,8 @@
         <v>{"type":"checkbox","class":"checkbox-big","name":"e31","title":"31. Кипение","style":"font-size:16px;display:block","state":"{{e31}}"},</v>
       </c>
       <c r="AG35" s="2" t="str">
-        <f t="shared" ca="1" si="17"/>
-        <v>{"type":"h4","title":"31. Кипение","style":"width:85%;float:left"},{"type":"input","title":"папка","name":"e31","state":"{{e31}}","pattern":"[0-9]{1,2}","style":"width:15%;text-align:center;border-radius:8px"},{"type":"hr"},</v>
+        <f t="shared" ca="1" si="23"/>
+        <v>{"type":"h4","title":"31. Кипение","style":"font-size:14px;width:85%;float:left"},{"type":"input","title":"папка","name":"e31","state":"{{e31}}","pattern":"[0-9]{1,2}","style":"background: #1c1c1c;border-color: #ffffff3d;border-style:solidborder-style: none;background: rgba(0, 0, 0, 0);color:#16d3f2;text-shadow: #16d3f2 1px 0 10px;height: 30px;width:15%;border-radius:8px;text-align:center"},{"type":"hr"},</v>
       </c>
       <c r="AH35" s="2" t="str">
         <f t="shared" ca="1" si="78"/>
@@ -6241,7 +6320,9 @@
         <f t="shared" ca="1" si="65"/>
         <v>31.Кипение</v>
       </c>
-      <c r="AL35" s="2"/>
+      <c r="AL35" s="31" t="s">
+        <v>440</v>
+      </c>
       <c r="AM35" s="2"/>
       <c r="AN35" s="17"/>
       <c r="AO35" s="2"/>
@@ -6355,8 +6436,8 @@
         <v>{"type":"checkbox","class":"checkbox-big","name":"e32","title":"32. Кодовый замок","style":"font-size:16px;display:block","state":"{{e32}}"},</v>
       </c>
       <c r="AG36" s="2" t="str">
-        <f t="shared" ca="1" si="17"/>
-        <v>{"type":"h4","title":"32. Кодовый замок","style":"width:85%;float:left"},{"type":"input","title":"папка","name":"e32","state":"{{e32}}","pattern":"[0-9]{1,2}","style":"width:15%;text-align:center;border-radius:8px"},{"type":"hr"},</v>
+        <f t="shared" ca="1" si="23"/>
+        <v>{"type":"h4","title":"32. Кодовый замок","style":"font-size:14px;width:85%;float:left"},{"type":"input","title":"папка","name":"e32","state":"{{e32}}","pattern":"[0-9]{1,2}","style":"background: #1c1c1c;border-color: #ffffff3d;border-style:solidborder-style: none;background: rgba(0, 0, 0, 0);color:#16d3f2;text-shadow: #16d3f2 1px 0 10px;height: 30px;width:15%;border-radius:8px;text-align:center"},{"type":"hr"},</v>
       </c>
       <c r="AH36" s="2" t="str">
         <f t="shared" ca="1" si="78"/>
@@ -6374,7 +6455,9 @@
         <f t="shared" ca="1" si="65"/>
         <v>32.Кодовый замок</v>
       </c>
-      <c r="AL36" s="2"/>
+      <c r="AL36" s="31" t="s">
+        <v>440</v>
+      </c>
       <c r="AM36" s="2"/>
       <c r="AN36" s="17"/>
       <c r="AO36" s="2"/>
@@ -6488,8 +6571,8 @@
         <v>{"type":"checkbox","class":"checkbox-big","name":"e33","title":"33. Комета","style":"font-size:16px;display:block","state":"{{e33}}"},</v>
       </c>
       <c r="AG37" s="2" t="str">
-        <f t="shared" ca="1" si="17"/>
-        <v>{"type":"h4","title":"33. Комета","style":"width:85%;float:left"},{"type":"input","title":"папка","name":"e33","state":"{{e33}}","pattern":"[0-9]{1,2}","style":"width:15%;text-align:center;border-radius:8px"},{"type":"hr"},</v>
+        <f t="shared" ca="1" si="23"/>
+        <v>{"type":"h4","title":"33. Комета","style":"font-size:14px;width:85%;float:left"},{"type":"input","title":"папка","name":"e33","state":"{{e33}}","pattern":"[0-9]{1,2}","style":"background: #1c1c1c;border-color: #ffffff3d;border-style:solidborder-style: none;background: rgba(0, 0, 0, 0);color:#16d3f2;text-shadow: #16d3f2 1px 0 10px;height: 30px;width:15%;border-radius:8px;text-align:center"},{"type":"hr"},</v>
       </c>
       <c r="AH37" s="2" t="str">
         <f t="shared" ca="1" si="78"/>
@@ -6507,7 +6590,9 @@
         <f t="shared" ca="1" si="65"/>
         <v>33.Комета</v>
       </c>
-      <c r="AL37" s="2"/>
+      <c r="AL37" s="31" t="s">
+        <v>440</v>
+      </c>
       <c r="AM37" s="2"/>
       <c r="AN37" s="17"/>
       <c r="AO37" s="2"/>
@@ -6621,8 +6706,8 @@
         <v>{"type":"checkbox","class":"checkbox-big","name":"e34","title":"34. Комета одноцветная","style":"font-size:16px;display:block","state":"{{e34}}"},</v>
       </c>
       <c r="AG38" s="2" t="str">
-        <f t="shared" ca="1" si="17"/>
-        <v>{"type":"h4","title":"34. Комета одноцветная","style":"width:85%;float:left"},{"type":"input","title":"папка","name":"e34","state":"{{e34}}","pattern":"[0-9]{1,2}","style":"width:15%;text-align:center;border-radius:8px"},{"type":"hr"},</v>
+        <f t="shared" ca="1" si="23"/>
+        <v>{"type":"h4","title":"34. Комета одноцветная","style":"font-size:14px;width:85%;float:left"},{"type":"input","title":"папка","name":"e34","state":"{{e34}}","pattern":"[0-9]{1,2}","style":"background: #1c1c1c;border-color: #ffffff3d;border-style:solidborder-style: none;background: rgba(0, 0, 0, 0);color:#16d3f2;text-shadow: #16d3f2 1px 0 10px;height: 30px;width:15%;border-radius:8px;text-align:center"},{"type":"hr"},</v>
       </c>
       <c r="AH38" s="2" t="str">
         <f t="shared" ca="1" si="78"/>
@@ -6640,7 +6725,9 @@
         <f t="shared" ca="1" si="65"/>
         <v>34.Комета одноцветная</v>
       </c>
-      <c r="AL38" s="2"/>
+      <c r="AL38" s="31" t="s">
+        <v>440</v>
+      </c>
       <c r="AM38" s="2"/>
       <c r="AN38" s="17"/>
       <c r="AO38" s="2"/>
@@ -6754,8 +6841,8 @@
         <v>{"type":"checkbox","class":"checkbox-big","name":"e35","title":"35. Комета двойная","style":"font-size:16px;display:block","state":"{{e35}}"},</v>
       </c>
       <c r="AG39" s="2" t="str">
-        <f t="shared" ca="1" si="17"/>
-        <v>{"type":"h4","title":"35. Комета двойная","style":"width:85%;float:left"},{"type":"input","title":"папка","name":"e35","state":"{{e35}}","pattern":"[0-9]{1,2}","style":"width:15%;text-align:center;border-radius:8px"},{"type":"hr"},</v>
+        <f t="shared" ca="1" si="23"/>
+        <v>{"type":"h4","title":"35. Комета двойная","style":"font-size:14px;width:85%;float:left"},{"type":"input","title":"папка","name":"e35","state":"{{e35}}","pattern":"[0-9]{1,2}","style":"background: #1c1c1c;border-color: #ffffff3d;border-style:solidborder-style: none;background: rgba(0, 0, 0, 0);color:#16d3f2;text-shadow: #16d3f2 1px 0 10px;height: 30px;width:15%;border-radius:8px;text-align:center"},{"type":"hr"},</v>
       </c>
       <c r="AH39" s="2" t="str">
         <f t="shared" ca="1" si="78"/>
@@ -6773,7 +6860,9 @@
         <f t="shared" ca="1" si="65"/>
         <v>35.Комета двойная</v>
       </c>
-      <c r="AL39" s="2"/>
+      <c r="AL39" s="31" t="s">
+        <v>440</v>
+      </c>
       <c r="AM39" s="2"/>
       <c r="AN39" s="17"/>
       <c r="AO39" s="2"/>
@@ -6887,8 +6976,8 @@
         <v>{"type":"checkbox","class":"checkbox-big","name":"e36","title":"36. Комета тройная","style":"font-size:16px;display:block","state":"{{e36}}"},</v>
       </c>
       <c r="AG40" s="2" t="str">
-        <f t="shared" ca="1" si="17"/>
-        <v>{"type":"h4","title":"36. Комета тройная","style":"width:85%;float:left"},{"type":"input","title":"папка","name":"e36","state":"{{e36}}","pattern":"[0-9]{1,2}","style":"width:15%;text-align:center;border-radius:8px"},{"type":"hr"},</v>
+        <f t="shared" ca="1" si="23"/>
+        <v>{"type":"h4","title":"36. Комета тройная","style":"font-size:14px;width:85%;float:left"},{"type":"input","title":"папка","name":"e36","state":"{{e36}}","pattern":"[0-9]{1,2}","style":"background: #1c1c1c;border-color: #ffffff3d;border-style:solidborder-style: none;background: rgba(0, 0, 0, 0);color:#16d3f2;text-shadow: #16d3f2 1px 0 10px;height: 30px;width:15%;border-radius:8px;text-align:center"},{"type":"hr"},</v>
       </c>
       <c r="AH40" s="2" t="str">
         <f t="shared" ca="1" si="78"/>
@@ -6906,7 +6995,9 @@
         <f t="shared" ca="1" si="65"/>
         <v>36.Комета тройная</v>
       </c>
-      <c r="AL40" s="2"/>
+      <c r="AL40" s="31" t="s">
+        <v>440</v>
+      </c>
       <c r="AM40" s="2"/>
       <c r="AN40" s="17"/>
       <c r="AO40" s="2"/>
@@ -7020,8 +7111,8 @@
         <v>{"type":"checkbox","class":"checkbox-big","name":"e37","title":"37. Контакты","style":"font-size:16px;display:block","state":"{{e37}}"},</v>
       </c>
       <c r="AG41" s="2" t="str">
-        <f t="shared" ca="1" si="17"/>
-        <v>{"type":"h4","title":"37. Контакты","style":"width:85%;float:left"},{"type":"input","title":"папка","name":"e37","state":"{{e37}}","pattern":"[0-9]{1,2}","style":"width:15%;text-align:center;border-radius:8px"},{"type":"hr"},</v>
+        <f t="shared" ca="1" si="23"/>
+        <v>{"type":"h4","title":"37. Контакты","style":"font-size:14px;width:85%;float:left"},{"type":"input","title":"папка","name":"e37","state":"{{e37}}","pattern":"[0-9]{1,2}","style":"background: #1c1c1c;border-color: #ffffff3d;border-style:solidborder-style: none;background: rgba(0, 0, 0, 0);color:#16d3f2;text-shadow: #16d3f2 1px 0 10px;height: 30px;width:15%;border-radius:8px;text-align:center"},{"type":"hr"},</v>
       </c>
       <c r="AH41" s="2" t="str">
         <f t="shared" ca="1" si="78"/>
@@ -7039,7 +7130,9 @@
         <f t="shared" ca="1" si="65"/>
         <v>37.Контакты</v>
       </c>
-      <c r="AL41" s="2"/>
+      <c r="AL41" s="31" t="s">
+        <v>440</v>
+      </c>
       <c r="AM41" s="2"/>
       <c r="AN41" s="17"/>
       <c r="AO41" s="2"/>
@@ -7153,8 +7246,8 @@
         <v>{"type":"checkbox","class":"checkbox-big","name":"e38","title":"38. Конфетти","style":"font-size:16px;display:block","state":"{{e38}}"},</v>
       </c>
       <c r="AG42" s="2" t="str">
-        <f t="shared" ca="1" si="17"/>
-        <v>{"type":"h4","title":"38. Конфетти","style":"width:85%;float:left"},{"type":"input","title":"папка","name":"e38","state":"{{e38}}","pattern":"[0-9]{1,2}","style":"width:15%;text-align:center;border-radius:8px"},{"type":"hr"},</v>
+        <f t="shared" ca="1" si="23"/>
+        <v>{"type":"h4","title":"38. Конфетти","style":"font-size:14px;width:85%;float:left"},{"type":"input","title":"папка","name":"e38","state":"{{e38}}","pattern":"[0-9]{1,2}","style":"background: #1c1c1c;border-color: #ffffff3d;border-style:solidborder-style: none;background: rgba(0, 0, 0, 0);color:#16d3f2;text-shadow: #16d3f2 1px 0 10px;height: 30px;width:15%;border-radius:8px;text-align:center"},{"type":"hr"},</v>
       </c>
       <c r="AH42" s="2" t="str">
         <f t="shared" ca="1" si="78"/>
@@ -7172,7 +7265,9 @@
         <f t="shared" ca="1" si="65"/>
         <v>38.Конфетти</v>
       </c>
-      <c r="AL42" s="2"/>
+      <c r="AL42" s="31" t="s">
+        <v>440</v>
+      </c>
       <c r="AM42" s="2"/>
       <c r="AN42" s="17"/>
       <c r="AO42" s="2"/>
@@ -7282,8 +7377,8 @@
         <v>{"type":"checkbox","class":"checkbox-big","name":"e39","title":"39. Кубик Рубика","style":"font-size:16px;display:block","state":"{{e39}}"},</v>
       </c>
       <c r="AG43" s="2" t="str">
-        <f t="shared" ca="1" si="17"/>
-        <v>{"type":"h4","title":"39. Кубик Рубика","style":"width:85%;float:left"},{"type":"input","title":"папка","name":"e39","state":"{{e39}}","pattern":"[0-9]{1,2}","style":"width:15%;text-align:center;border-radius:8px"},{"type":"hr"},</v>
+        <f t="shared" ca="1" si="23"/>
+        <v>{"type":"h4","title":"39. Кубик Рубика","style":"font-size:14px;width:85%;float:left"},{"type":"input","title":"папка","name":"e39","state":"{{e39}}","pattern":"[0-9]{1,2}","style":"background: #1c1c1c;border-color: #ffffff3d;border-style:solidborder-style: none;background: rgba(0, 0, 0, 0);color:#16d3f2;text-shadow: #16d3f2 1px 0 10px;height: 30px;width:15%;border-radius:8px;text-align:center"},{"type":"hr"},</v>
       </c>
       <c r="AH43" s="2" t="str">
         <f t="shared" ref="AH43:AH48" ca="1" si="92">CONCATENATE("""",A43,"""",": """,A43,".",C43,""",")</f>
@@ -7301,7 +7396,9 @@
         <f t="shared" ref="AK43:AK48" ca="1" si="95">CONCATENATE("",A43,"",".",C43,"")</f>
         <v>39.Кубик Рубика</v>
       </c>
-      <c r="AL43" s="2"/>
+      <c r="AL43" s="31" t="s">
+        <v>440</v>
+      </c>
       <c r="AM43" s="2"/>
       <c r="AN43" s="17"/>
       <c r="AO43" s="2"/>
@@ -7415,8 +7512,8 @@
         <v>{"type":"checkbox","class":"checkbox-big","name":"e40","title":"40. Лава","style":"font-size:16px;display:block","state":"{{e40}}"},</v>
       </c>
       <c r="AG44" s="2" t="str">
-        <f t="shared" ca="1" si="17"/>
-        <v>{"type":"h4","title":"40. Лава","style":"width:85%;float:left"},{"type":"input","title":"папка","name":"e40","state":"{{e40}}","pattern":"[0-9]{1,2}","style":"width:15%;text-align:center;border-radius:8px"},{"type":"hr"},</v>
+        <f t="shared" ca="1" si="23"/>
+        <v>{"type":"h4","title":"40. Лава","style":"font-size:14px;width:85%;float:left"},{"type":"input","title":"папка","name":"e40","state":"{{e40}}","pattern":"[0-9]{1,2}","style":"background: #1c1c1c;border-color: #ffffff3d;border-style:solidborder-style: none;background: rgba(0, 0, 0, 0);color:#16d3f2;text-shadow: #16d3f2 1px 0 10px;height: 30px;width:15%;border-radius:8px;text-align:center"},{"type":"hr"},</v>
       </c>
       <c r="AH44" s="2" t="str">
         <f t="shared" ca="1" si="92"/>
@@ -7434,7 +7531,9 @@
         <f t="shared" ca="1" si="95"/>
         <v>40.Лава</v>
       </c>
-      <c r="AL44" s="2"/>
+      <c r="AL44" s="31" t="s">
+        <v>440</v>
+      </c>
       <c r="AM44" s="2"/>
       <c r="AN44" s="17"/>
       <c r="AO44" s="2"/>
@@ -7548,8 +7647,8 @@
         <v>{"type":"checkbox","class":"checkbox-big","name":"e41","title":"41. Лавовая лампа","style":"font-size:16px;display:block","state":"{{e41}}"},</v>
       </c>
       <c r="AG45" s="2" t="str">
-        <f t="shared" ca="1" si="17"/>
-        <v>{"type":"h4","title":"41. Лавовая лампа","style":"width:85%;float:left"},{"type":"input","title":"папка","name":"e41","state":"{{e41}}","pattern":"[0-9]{1,2}","style":"width:15%;text-align:center;border-radius:8px"},{"type":"hr"},</v>
+        <f t="shared" ca="1" si="23"/>
+        <v>{"type":"h4","title":"41. Лавовая лампа","style":"font-size:14px;width:85%;float:left"},{"type":"input","title":"папка","name":"e41","state":"{{e41}}","pattern":"[0-9]{1,2}","style":"background: #1c1c1c;border-color: #ffffff3d;border-style:solidborder-style: none;background: rgba(0, 0, 0, 0);color:#16d3f2;text-shadow: #16d3f2 1px 0 10px;height: 30px;width:15%;border-radius:8px;text-align:center"},{"type":"hr"},</v>
       </c>
       <c r="AH45" s="2" t="str">
         <f t="shared" ca="1" si="92"/>
@@ -7567,7 +7666,9 @@
         <f t="shared" ca="1" si="95"/>
         <v>41.Лавовая лампа</v>
       </c>
-      <c r="AL45" s="2"/>
+      <c r="AL45" s="31" t="s">
+        <v>440</v>
+      </c>
       <c r="AM45" s="2"/>
       <c r="AN45" s="17"/>
       <c r="AO45" s="2"/>
@@ -7681,8 +7782,8 @@
         <v>{"type":"checkbox","class":"checkbox-big","name":"e42","title":"42. Лампа с мотыльками","style":"font-size:16px;display:block","state":"{{e42}}"},</v>
       </c>
       <c r="AG46" s="2" t="str">
-        <f t="shared" ca="1" si="17"/>
-        <v>{"type":"h4","title":"42. Лампа с мотыльками","style":"width:85%;float:left"},{"type":"input","title":"папка","name":"e42","state":"{{e42}}","pattern":"[0-9]{1,2}","style":"width:15%;text-align:center;border-radius:8px"},{"type":"hr"},</v>
+        <f t="shared" ca="1" si="23"/>
+        <v>{"type":"h4","title":"42. Лампа с мотыльками","style":"font-size:14px;width:85%;float:left"},{"type":"input","title":"папка","name":"e42","state":"{{e42}}","pattern":"[0-9]{1,2}","style":"background: #1c1c1c;border-color: #ffffff3d;border-style:solidborder-style: none;background: rgba(0, 0, 0, 0);color:#16d3f2;text-shadow: #16d3f2 1px 0 10px;height: 30px;width:15%;border-radius:8px;text-align:center"},{"type":"hr"},</v>
       </c>
       <c r="AH46" s="2" t="str">
         <f t="shared" ca="1" si="92"/>
@@ -7700,7 +7801,9 @@
         <f t="shared" ca="1" si="95"/>
         <v>42.Лампа с мотыльками</v>
       </c>
-      <c r="AL46" s="2"/>
+      <c r="AL46" s="31" t="s">
+        <v>440</v>
+      </c>
       <c r="AM46" s="2"/>
       <c r="AN46" s="17"/>
       <c r="AO46" s="2"/>
@@ -7814,8 +7917,8 @@
         <v>{"type":"checkbox","class":"checkbox-big","name":"e43","title":"43. Лес","style":"font-size:16px;display:block","state":"{{e43}}"},</v>
       </c>
       <c r="AG47" s="2" t="str">
-        <f t="shared" ca="1" si="17"/>
-        <v>{"type":"h4","title":"43. Лес","style":"width:85%;float:left"},{"type":"input","title":"папка","name":"e43","state":"{{e43}}","pattern":"[0-9]{1,2}","style":"width:15%;text-align:center;border-radius:8px"},{"type":"hr"},</v>
+        <f t="shared" ca="1" si="23"/>
+        <v>{"type":"h4","title":"43. Лес","style":"font-size:14px;width:85%;float:left"},{"type":"input","title":"папка","name":"e43","state":"{{e43}}","pattern":"[0-9]{1,2}","style":"background: #1c1c1c;border-color: #ffffff3d;border-style:solidborder-style: none;background: rgba(0, 0, 0, 0);color:#16d3f2;text-shadow: #16d3f2 1px 0 10px;height: 30px;width:15%;border-radius:8px;text-align:center"},{"type":"hr"},</v>
       </c>
       <c r="AH47" s="2" t="str">
         <f t="shared" ca="1" si="92"/>
@@ -7833,7 +7936,9 @@
         <f t="shared" ca="1" si="95"/>
         <v>43.Лес</v>
       </c>
-      <c r="AL47" s="2"/>
+      <c r="AL47" s="31" t="s">
+        <v>440</v>
+      </c>
       <c r="AM47" s="2"/>
       <c r="AN47" s="17"/>
       <c r="AO47" s="2"/>
@@ -7947,8 +8052,8 @@
         <v>{"type":"checkbox","class":"checkbox-big","name":"e44","title":"44. Люмeньep","style":"font-size:16px;display:block","state":"{{e44}}"},</v>
       </c>
       <c r="AG48" s="2" t="str">
-        <f t="shared" ca="1" si="17"/>
-        <v>{"type":"h4","title":"44. Люмeньep","style":"width:85%;float:left"},{"type":"input","title":"папка","name":"e44","state":"{{e44}}","pattern":"[0-9]{1,2}","style":"width:15%;text-align:center;border-radius:8px"},{"type":"hr"},</v>
+        <f t="shared" ca="1" si="23"/>
+        <v>{"type":"h4","title":"44. Люмeньep","style":"font-size:14px;width:85%;float:left"},{"type":"input","title":"папка","name":"e44","state":"{{e44}}","pattern":"[0-9]{1,2}","style":"background: #1c1c1c;border-color: #ffffff3d;border-style:solidborder-style: none;background: rgba(0, 0, 0, 0);color:#16d3f2;text-shadow: #16d3f2 1px 0 10px;height: 30px;width:15%;border-radius:8px;text-align:center"},{"type":"hr"},</v>
       </c>
       <c r="AH48" s="2" t="str">
         <f t="shared" ca="1" si="92"/>
@@ -7966,7 +8071,9 @@
         <f t="shared" ca="1" si="95"/>
         <v>44.Люмeньep</v>
       </c>
-      <c r="AL48" s="2"/>
+      <c r="AL48" s="31" t="s">
+        <v>440</v>
+      </c>
       <c r="AM48" s="2"/>
       <c r="AN48" s="17"/>
       <c r="AO48" s="2"/>
@@ -8025,7 +8132,7 @@
         <v>155</v>
       </c>
       <c r="AK49" s="2"/>
-      <c r="AL49" s="2"/>
+      <c r="AL49" s="31"/>
       <c r="AM49" s="4"/>
       <c r="AN49" s="5"/>
       <c r="AO49" s="25"/>
@@ -8084,7 +8191,7 @@
         <v>157</v>
       </c>
       <c r="AK50" s="2"/>
-      <c r="AL50" s="2"/>
+      <c r="AL50" s="31"/>
       <c r="AM50" s="4"/>
       <c r="AN50" s="4"/>
       <c r="AO50" s="5"/>
@@ -8198,8 +8305,8 @@
         <v>{"type":"checkbox","class":"checkbox-big","name":"e45","title":"45. Магма","style":"font-size:16px;display:block","state":"{{e45}}"},</v>
       </c>
       <c r="AG51" s="2" t="str">
-        <f t="shared" ref="AG51:AG90" ca="1" si="110">CONCATENATE("{""type"":""h4"",""title"":""",A51,". ",C51,""",""style"":""width:85%;float:left""},{""type"":""input"",""title"":""папка"",""name"":""e",T51,""",""state"":""{{e",T51,"}}"",""pattern"":""[0-9]{1,2}"",""style"":""width:15%;text-align:center;border-radius:8px""},{""type"":""hr""},")</f>
-        <v>{"type":"h4","title":"45. Магма","style":"width:85%;float:left"},{"type":"input","title":"папка","name":"e45","state":"{{e45}}","pattern":"[0-9]{1,2}","style":"width:15%;text-align:center;border-radius:8px"},{"type":"hr"},</v>
+        <f t="shared" ref="AG51:AG90" ca="1" si="110">CONCATENATE("{""type"":""h4"",""title"":""",A51,". ",C51,""",""style"":""font-size:14px;width:85%;float:left""},{""type"":""input"",""title"":""папка"",""name"":""e",T51,""",""state"":""{{e",T51,"}}"",""pattern"":""[0-9]{1,2}"",""style"":""",AL51,"""},{""type"":""hr""},")</f>
+        <v>{"type":"h4","title":"45. Магма","style":"font-size:14px;width:85%;float:left"},{"type":"input","title":"папка","name":"e45","state":"{{e45}}","pattern":"[0-9]{1,2}","style":"background: #1c1c1c;border-color: #ffffff3d;border-style:solidborder-style: none;background: rgba(0, 0, 0, 0);color:#16d3f2;text-shadow: #16d3f2 1px 0 10px;height: 30px;width:15%;border-radius:8px;text-align:center"},{"type":"hr"},</v>
       </c>
       <c r="AH51" s="2" t="str">
         <f t="shared" ref="AH51:AH62" ca="1" si="111">CONCATENATE("""",A51,"""",": """,A51,".",C51,""",")</f>
@@ -8217,7 +8324,9 @@
         <f t="shared" ref="AK51:AK62" ca="1" si="113">CONCATENATE("",A51,"",".",C51,"")</f>
         <v>45.Магма</v>
       </c>
-      <c r="AL51" s="2"/>
+      <c r="AL51" s="31" t="s">
+        <v>440</v>
+      </c>
       <c r="AM51" s="2"/>
       <c r="AN51" s="17"/>
       <c r="AO51" s="2"/>
@@ -8332,7 +8441,7 @@
       </c>
       <c r="AG52" s="2" t="str">
         <f t="shared" ca="1" si="110"/>
-        <v>{"type":"h4","title":"46. Масляные краски","style":"width:85%;float:left"},{"type":"input","title":"папка","name":"e46","state":"{{e46}}","pattern":"[0-9]{1,2}","style":"width:15%;text-align:center;border-radius:8px"},{"type":"hr"},</v>
+        <v>{"type":"h4","title":"46. Масляные краски","style":"font-size:14px;width:85%;float:left"},{"type":"input","title":"папка","name":"e46","state":"{{e46}}","pattern":"[0-9]{1,2}","style":"background: #1c1c1c;border-color: #ffffff3d;border-style:solidborder-style: none;background: rgba(0, 0, 0, 0);color:#16d3f2;text-shadow: #16d3f2 1px 0 10px;height: 30px;width:15%;border-radius:8px;text-align:center"},{"type":"hr"},</v>
       </c>
       <c r="AH52" s="2" t="str">
         <f t="shared" ca="1" si="111"/>
@@ -8350,7 +8459,9 @@
         <f t="shared" ca="1" si="113"/>
         <v>46.Масляные краски</v>
       </c>
-      <c r="AL52" s="2"/>
+      <c r="AL52" s="31" t="s">
+        <v>440</v>
+      </c>
       <c r="AM52" s="2"/>
       <c r="AN52" s="17"/>
       <c r="AO52" s="2"/>
@@ -8465,7 +8576,7 @@
       </c>
       <c r="AG53" s="2" t="str">
         <f t="shared" ca="1" si="110"/>
-        <v>{"type":"h4","title":"47. Матрица","style":"width:85%;float:left"},{"type":"input","title":"папка","name":"e47","state":"{{e47}}","pattern":"[0-9]{1,2}","style":"width:15%;text-align:center;border-radius:8px"},{"type":"hr"},</v>
+        <v>{"type":"h4","title":"47. Матрица","style":"font-size:14px;width:85%;float:left"},{"type":"input","title":"папка","name":"e47","state":"{{e47}}","pattern":"[0-9]{1,2}","style":"background: #1c1c1c;border-color: #ffffff3d;border-style:solidborder-style: none;background: rgba(0, 0, 0, 0);color:#16d3f2;text-shadow: #16d3f2 1px 0 10px;height: 30px;width:15%;border-radius:8px;text-align:center"},{"type":"hr"},</v>
       </c>
       <c r="AH53" s="2" t="str">
         <f t="shared" ca="1" si="111"/>
@@ -8483,7 +8594,9 @@
         <f t="shared" ca="1" si="113"/>
         <v>47.Матрица</v>
       </c>
-      <c r="AL53" s="2"/>
+      <c r="AL53" s="31" t="s">
+        <v>440</v>
+      </c>
       <c r="AM53" s="2"/>
       <c r="AN53" s="17"/>
       <c r="AO53" s="2"/>
@@ -8598,7 +8711,7 @@
       </c>
       <c r="AG54" s="2" t="str">
         <f t="shared" ca="1" si="110"/>
-        <v>{"type":"h4","title":"48. Мерцание","style":"width:85%;float:left"},{"type":"input","title":"папка","name":"e48","state":"{{e48}}","pattern":"[0-9]{1,2}","style":"width:15%;text-align:center;border-radius:8px"},{"type":"hr"},</v>
+        <v>{"type":"h4","title":"48. Мерцание","style":"font-size:14px;width:85%;float:left"},{"type":"input","title":"папка","name":"e48","state":"{{e48}}","pattern":"[0-9]{1,2}","style":"background: #1c1c1c;border-color: #ffffff3d;border-style:solidborder-style: none;background: rgba(0, 0, 0, 0);color:#16d3f2;text-shadow: #16d3f2 1px 0 10px;height: 30px;width:15%;border-radius:8px;text-align:center"},{"type":"hr"},</v>
       </c>
       <c r="AH54" s="2" t="str">
         <f t="shared" ca="1" si="111"/>
@@ -8616,7 +8729,9 @@
         <f t="shared" ca="1" si="113"/>
         <v>48.Мерцание</v>
       </c>
-      <c r="AL54" s="2"/>
+      <c r="AL54" s="31" t="s">
+        <v>440</v>
+      </c>
       <c r="AM54" s="2"/>
       <c r="AN54" s="17"/>
       <c r="AO54" s="2"/>
@@ -8731,7 +8846,7 @@
       </c>
       <c r="AG55" s="2" t="str">
         <f t="shared" ca="1" si="110"/>
-        <v>{"type":"h4","title":"49. Метоболз","style":"width:85%;float:left"},{"type":"input","title":"папка","name":"e49","state":"{{e49}}","pattern":"[0-9]{1,2}","style":"width:15%;text-align:center;border-radius:8px"},{"type":"hr"},</v>
+        <v>{"type":"h4","title":"49. Метоболз","style":"font-size:14px;width:85%;float:left"},{"type":"input","title":"папка","name":"e49","state":"{{e49}}","pattern":"[0-9]{1,2}","style":"background: #1c1c1c;border-color: #ffffff3d;border-style:solidborder-style: none;background: rgba(0, 0, 0, 0);color:#16d3f2;text-shadow: #16d3f2 1px 0 10px;height: 30px;width:15%;border-radius:8px;text-align:center"},{"type":"hr"},</v>
       </c>
       <c r="AH55" s="2" t="str">
         <f t="shared" ca="1" si="111"/>
@@ -8749,7 +8864,9 @@
         <f t="shared" ca="1" si="113"/>
         <v>49.Метоболз</v>
       </c>
-      <c r="AL55" s="2"/>
+      <c r="AL55" s="31" t="s">
+        <v>440</v>
+      </c>
       <c r="AM55" s="2"/>
       <c r="AN55" s="17"/>
       <c r="AO55" s="2"/>
@@ -8864,7 +8981,7 @@
       </c>
       <c r="AG56" s="2" t="str">
         <f t="shared" ca="1" si="110"/>
-        <v>{"type":"h4","title":"50. Мечта дизайнера","style":"width:85%;float:left"},{"type":"input","title":"папка","name":"e50","state":"{{e50}}","pattern":"[0-9]{1,2}","style":"width:15%;text-align:center;border-radius:8px"},{"type":"hr"},</v>
+        <v>{"type":"h4","title":"50. Мечта дизайнера","style":"font-size:14px;width:85%;float:left"},{"type":"input","title":"папка","name":"e50","state":"{{e50}}","pattern":"[0-9]{1,2}","style":"background: #1c1c1c;border-color: #ffffff3d;border-style:solidborder-style: none;background: rgba(0, 0, 0, 0);color:#16d3f2;text-shadow: #16d3f2 1px 0 10px;height: 30px;width:15%;border-radius:8px;text-align:center"},{"type":"hr"},</v>
       </c>
       <c r="AH56" s="2" t="str">
         <f t="shared" ca="1" si="111"/>
@@ -8882,7 +8999,9 @@
         <f t="shared" ca="1" si="113"/>
         <v>50.Мечта дизайнера</v>
       </c>
-      <c r="AL56" s="2"/>
+      <c r="AL56" s="31" t="s">
+        <v>440</v>
+      </c>
       <c r="AM56" s="2"/>
       <c r="AN56" s="17"/>
       <c r="AO56" s="2"/>
@@ -8997,7 +9116,7 @@
       </c>
       <c r="AG57" s="2" t="str">
         <f t="shared" ca="1" si="110"/>
-        <v>{"type":"h4","title":"51. Мозайка","style":"width:85%;float:left"},{"type":"input","title":"папка","name":"e51","state":"{{e51}}","pattern":"[0-9]{1,2}","style":"width:15%;text-align:center;border-radius:8px"},{"type":"hr"},</v>
+        <v>{"type":"h4","title":"51. Мозайка","style":"font-size:14px;width:85%;float:left"},{"type":"input","title":"папка","name":"e51","state":"{{e51}}","pattern":"[0-9]{1,2}","style":"background: #1c1c1c;border-color: #ffffff3d;border-style:solidborder-style: none;background: rgba(0, 0, 0, 0);color:#16d3f2;text-shadow: #16d3f2 1px 0 10px;height: 30px;width:15%;border-radius:8px;text-align:center"},{"type":"hr"},</v>
       </c>
       <c r="AH57" s="2" t="str">
         <f t="shared" ca="1" si="111"/>
@@ -9015,7 +9134,9 @@
         <f t="shared" ca="1" si="113"/>
         <v>51.Мозайка</v>
       </c>
-      <c r="AL57" s="2"/>
+      <c r="AL57" s="31" t="s">
+        <v>440</v>
+      </c>
       <c r="AM57" s="2"/>
       <c r="AN57" s="17"/>
       <c r="AO57" s="2"/>
@@ -9130,7 +9251,7 @@
       </c>
       <c r="AG58" s="2" t="str">
         <f t="shared" ca="1" si="110"/>
-        <v>{"type":"h4","title":"52. Moтыльки","style":"width:85%;float:left"},{"type":"input","title":"папка","name":"e52","state":"{{e52}}","pattern":"[0-9]{1,2}","style":"width:15%;text-align:center;border-radius:8px"},{"type":"hr"},</v>
+        <v>{"type":"h4","title":"52. Moтыльки","style":"font-size:14px;width:85%;float:left"},{"type":"input","title":"папка","name":"e52","state":"{{e52}}","pattern":"[0-9]{1,2}","style":"background: #1c1c1c;border-color: #ffffff3d;border-style:solidborder-style: none;background: rgba(0, 0, 0, 0);color:#16d3f2;text-shadow: #16d3f2 1px 0 10px;height: 30px;width:15%;border-radius:8px;text-align:center"},{"type":"hr"},</v>
       </c>
       <c r="AH58" s="2" t="str">
         <f t="shared" ca="1" si="111"/>
@@ -9148,7 +9269,9 @@
         <f t="shared" ca="1" si="113"/>
         <v>52.Moтыльки</v>
       </c>
-      <c r="AL58" s="2"/>
+      <c r="AL58" s="31" t="s">
+        <v>440</v>
+      </c>
       <c r="AM58" s="2"/>
       <c r="AN58" s="17"/>
       <c r="AO58" s="2"/>
@@ -9263,7 +9386,7 @@
       </c>
       <c r="AG59" s="2" t="str">
         <f t="shared" ca="1" si="110"/>
-        <v>{"type":"h4","title":"53. Мячики","style":"width:85%;float:left"},{"type":"input","title":"папка","name":"e53","state":"{{e53}}","pattern":"[0-9]{1,2}","style":"width:15%;text-align:center;border-radius:8px"},{"type":"hr"},</v>
+        <v>{"type":"h4","title":"53. Мячики","style":"font-size:14px;width:85%;float:left"},{"type":"input","title":"папка","name":"e53","state":"{{e53}}","pattern":"[0-9]{1,2}","style":"background: #1c1c1c;border-color: #ffffff3d;border-style:solidborder-style: none;background: rgba(0, 0, 0, 0);color:#16d3f2;text-shadow: #16d3f2 1px 0 10px;height: 30px;width:15%;border-radius:8px;text-align:center"},{"type":"hr"},</v>
       </c>
       <c r="AH59" s="2" t="str">
         <f t="shared" ca="1" si="111"/>
@@ -9281,7 +9404,9 @@
         <f t="shared" ca="1" si="113"/>
         <v>53.Мячики</v>
       </c>
-      <c r="AL59" s="2"/>
+      <c r="AL59" s="31" t="s">
+        <v>440</v>
+      </c>
       <c r="AM59" s="2"/>
       <c r="AN59" s="17"/>
       <c r="AO59" s="2"/>
@@ -9396,7 +9521,7 @@
       </c>
       <c r="AG60" s="2" t="str">
         <f t="shared" ca="1" si="110"/>
-        <v>{"type":"h4","title":"54. Мячики без границ","style":"width:85%;float:left"},{"type":"input","title":"папка","name":"e54","state":"{{e54}}","pattern":"[0-9]{1,2}","style":"width:15%;text-align:center;border-radius:8px"},{"type":"hr"},</v>
+        <v>{"type":"h4","title":"54. Мячики без границ","style":"font-size:14px;width:85%;float:left"},{"type":"input","title":"папка","name":"e54","state":"{{e54}}","pattern":"[0-9]{1,2}","style":"background: #1c1c1c;border-color: #ffffff3d;border-style:solidborder-style: none;background: rgba(0, 0, 0, 0);color:#16d3f2;text-shadow: #16d3f2 1px 0 10px;height: 30px;width:15%;border-radius:8px;text-align:center"},{"type":"hr"},</v>
       </c>
       <c r="AH60" s="2" t="str">
         <f t="shared" ca="1" si="111"/>
@@ -9414,7 +9539,9 @@
         <f t="shared" ca="1" si="113"/>
         <v>54.Мячики без границ</v>
       </c>
-      <c r="AL60" s="2"/>
+      <c r="AL60" s="31" t="s">
+        <v>440</v>
+      </c>
       <c r="AM60" s="2"/>
       <c r="AN60" s="17"/>
       <c r="AO60" s="2"/>
@@ -9529,7 +9656,7 @@
       </c>
       <c r="AG61" s="2" t="str">
         <f t="shared" ca="1" si="110"/>
-        <v>{"type":"h4","title":"55. Новогодняя Елка","style":"width:85%;float:left"},{"type":"input","title":"папка","name":"e55","state":"{{e55}}","pattern":"[0-9]{1,2}","style":"width:15%;text-align:center;border-radius:8px"},{"type":"hr"},</v>
+        <v>{"type":"h4","title":"55. Новогодняя Елка","style":"font-size:14px;width:85%;float:left"},{"type":"input","title":"папка","name":"e55","state":"{{e55}}","pattern":"[0-9]{1,2}","style":"background: #1c1c1c;border-color: #ffffff3d;border-style:solidborder-style: none;background: rgba(0, 0, 0, 0);color:#16d3f2;text-shadow: #16d3f2 1px 0 10px;height: 30px;width:15%;border-radius:8px;text-align:center"},{"type":"hr"},</v>
       </c>
       <c r="AH61" s="2" t="str">
         <f t="shared" ca="1" si="111"/>
@@ -9547,7 +9674,9 @@
         <f t="shared" ca="1" si="113"/>
         <v>55.Новогодняя Елка</v>
       </c>
-      <c r="AL61" s="2"/>
+      <c r="AL61" s="31" t="s">
+        <v>440</v>
+      </c>
       <c r="AM61" s="2"/>
       <c r="AN61" s="17"/>
       <c r="AO61" s="2"/>
@@ -9661,7 +9790,7 @@
       </c>
       <c r="AG62" s="2" t="str">
         <f t="shared" ca="1" si="110"/>
-        <v>{"type":"h4","title":"56. Ночной Город","style":"width:85%;float:left"},{"type":"input","title":"папка","name":"e56","state":"{{e56}}","pattern":"[0-9]{1,2}","style":"width:15%;text-align:center;border-radius:8px"},{"type":"hr"},</v>
+        <v>{"type":"h4","title":"56. Ночной Город","style":"font-size:14px;width:85%;float:left"},{"type":"input","title":"папка","name":"e56","state":"{{e56}}","pattern":"[0-9]{1,2}","style":"background: #1c1c1c;border-color: #ffffff3d;border-style:solidborder-style: none;background: rgba(0, 0, 0, 0);color:#16d3f2;text-shadow: #16d3f2 1px 0 10px;height: 30px;width:15%;border-radius:8px;text-align:center"},{"type":"hr"},</v>
       </c>
       <c r="AH62" s="2" t="str">
         <f t="shared" ca="1" si="111"/>
@@ -9678,6 +9807,9 @@
       <c r="AK62" s="2" t="str">
         <f t="shared" ca="1" si="113"/>
         <v>56.Ночной Город</v>
+      </c>
+      <c r="AL62" s="31" t="s">
+        <v>440</v>
       </c>
     </row>
     <row r="63" spans="1:56" ht="14.25" customHeight="1">
@@ -9775,7 +9907,7 @@
       </c>
       <c r="AG63" s="2" t="str">
         <f t="shared" ca="1" si="110"/>
-        <v>{"type":"h4","title":"57. Огонь","style":"width:85%;float:left"},{"type":"input","title":"папка","name":"e57","state":"{{e57}}","pattern":"[0-9]{1,2}","style":"width:15%;text-align:center;border-radius:8px"},{"type":"hr"},</v>
+        <v>{"type":"h4","title":"57. Огонь","style":"font-size:14px;width:85%;float:left"},{"type":"input","title":"папка","name":"e57","state":"{{e57}}","pattern":"[0-9]{1,2}","style":"background: #1c1c1c;border-color: #ffffff3d;border-style:solidborder-style: none;background: rgba(0, 0, 0, 0);color:#16d3f2;text-shadow: #16d3f2 1px 0 10px;height: 30px;width:15%;border-radius:8px;text-align:center"},{"type":"hr"},</v>
       </c>
       <c r="AH63" s="2" t="str">
         <f t="shared" ref="AH63:AH75" ca="1" si="128">CONCATENATE("""",A63,"""",": """,A63,".",C63,""",")</f>
@@ -9793,7 +9925,9 @@
         <f t="shared" ref="AK63:AK90" ca="1" si="131">CONCATENATE("",A63,"",".",C63,"")</f>
         <v>57.Огонь</v>
       </c>
-      <c r="AL63" s="2"/>
+      <c r="AL63" s="31" t="s">
+        <v>440</v>
+      </c>
       <c r="AM63" s="2"/>
       <c r="AN63" s="17"/>
       <c r="AO63" s="2"/>
@@ -9908,7 +10042,7 @@
       </c>
       <c r="AG64" s="2" t="str">
         <f t="shared" ca="1" si="110"/>
-        <v>{"type":"h4","title":"58. Огонь 2012","style":"width:85%;float:left"},{"type":"input","title":"папка","name":"e58","state":"{{e58}}","pattern":"[0-9]{1,2}","style":"width:15%;text-align:center;border-radius:8px"},{"type":"hr"},</v>
+        <v>{"type":"h4","title":"58. Огонь 2012","style":"font-size:14px;width:85%;float:left"},{"type":"input","title":"папка","name":"e58","state":"{{e58}}","pattern":"[0-9]{1,2}","style":"background: #1c1c1c;border-color: #ffffff3d;border-style:solidborder-style: none;background: rgba(0, 0, 0, 0);color:#16d3f2;text-shadow: #16d3f2 1px 0 10px;height: 30px;width:15%;border-radius:8px;text-align:center"},{"type":"hr"},</v>
       </c>
       <c r="AH64" s="2" t="str">
         <f t="shared" ca="1" si="128"/>
@@ -9926,7 +10060,9 @@
         <f t="shared" ca="1" si="131"/>
         <v>58.Огонь 2012</v>
       </c>
-      <c r="AL64" s="2"/>
+      <c r="AL64" s="31" t="s">
+        <v>440</v>
+      </c>
       <c r="AM64" s="2"/>
       <c r="AN64" s="17"/>
       <c r="AO64" s="2"/>
@@ -10041,7 +10177,7 @@
       </c>
       <c r="AG65" s="2" t="str">
         <f t="shared" ca="1" si="110"/>
-        <v>{"type":"h4","title":"59. Огонь 2018","style":"width:85%;float:left"},{"type":"input","title":"папка","name":"e59","state":"{{e59}}","pattern":"[0-9]{1,2}","style":"width:15%;text-align:center;border-radius:8px"},{"type":"hr"},</v>
+        <v>{"type":"h4","title":"59. Огонь 2018","style":"font-size:14px;width:85%;float:left"},{"type":"input","title":"папка","name":"e59","state":"{{e59}}","pattern":"[0-9]{1,2}","style":"background: #1c1c1c;border-color: #ffffff3d;border-style:solidborder-style: none;background: rgba(0, 0, 0, 0);color:#16d3f2;text-shadow: #16d3f2 1px 0 10px;height: 30px;width:15%;border-radius:8px;text-align:center"},{"type":"hr"},</v>
       </c>
       <c r="AH65" s="2" t="str">
         <f t="shared" ca="1" si="128"/>
@@ -10059,7 +10195,9 @@
         <f t="shared" ca="1" si="131"/>
         <v>59.Огонь 2018</v>
       </c>
-      <c r="AL65" s="2"/>
+      <c r="AL65" s="31" t="s">
+        <v>440</v>
+      </c>
       <c r="AM65" s="2"/>
       <c r="AN65" s="17"/>
       <c r="AO65" s="2"/>
@@ -10174,7 +10312,7 @@
       </c>
       <c r="AG66" s="2" t="str">
         <f t="shared" ca="1" si="110"/>
-        <v>{"type":"h4","title":"60. Огонь 2020","style":"width:85%;float:left"},{"type":"input","title":"папка","name":"e60","state":"{{e60}}","pattern":"[0-9]{1,2}","style":"width:15%;text-align:center;border-radius:8px"},{"type":"hr"},</v>
+        <v>{"type":"h4","title":"60. Огонь 2020","style":"font-size:14px;width:85%;float:left"},{"type":"input","title":"папка","name":"e60","state":"{{e60}}","pattern":"[0-9]{1,2}","style":"background: #1c1c1c;border-color: #ffffff3d;border-style:solidborder-style: none;background: rgba(0, 0, 0, 0);color:#16d3f2;text-shadow: #16d3f2 1px 0 10px;height: 30px;width:15%;border-radius:8px;text-align:center"},{"type":"hr"},</v>
       </c>
       <c r="AH66" s="2" t="str">
         <f t="shared" ca="1" si="128"/>
@@ -10192,7 +10330,9 @@
         <f t="shared" ca="1" si="131"/>
         <v>60.Огонь 2020</v>
       </c>
-      <c r="AL66" s="2"/>
+      <c r="AL66" s="31" t="s">
+        <v>440</v>
+      </c>
       <c r="AM66" s="2"/>
       <c r="AN66" s="17"/>
       <c r="AO66" s="2"/>
@@ -10307,7 +10447,7 @@
       </c>
       <c r="AG67" s="2" t="str">
         <f t="shared" ca="1" si="110"/>
-        <v>{"type":"h4","title":"61. Огонь 2021","style":"width:85%;float:left"},{"type":"input","title":"папка","name":"e61","state":"{{e61}}","pattern":"[0-9]{1,2}","style":"width:15%;text-align:center;border-radius:8px"},{"type":"hr"},</v>
+        <v>{"type":"h4","title":"61. Огонь 2021","style":"font-size:14px;width:85%;float:left"},{"type":"input","title":"папка","name":"e61","state":"{{e61}}","pattern":"[0-9]{1,2}","style":"background: #1c1c1c;border-color: #ffffff3d;border-style:solidborder-style: none;background: rgba(0, 0, 0, 0);color:#16d3f2;text-shadow: #16d3f2 1px 0 10px;height: 30px;width:15%;border-radius:8px;text-align:center"},{"type":"hr"},</v>
       </c>
       <c r="AH67" s="2" t="str">
         <f t="shared" ca="1" si="128"/>
@@ -10325,7 +10465,9 @@
         <f t="shared" ca="1" si="131"/>
         <v>61.Огонь 2021</v>
       </c>
-      <c r="AL67" s="2"/>
+      <c r="AL67" s="31" t="s">
+        <v>440</v>
+      </c>
       <c r="AM67" s="2"/>
       <c r="AN67" s="17"/>
       <c r="AO67" s="2"/>
@@ -10440,7 +10582,7 @@
       </c>
       <c r="AG68" s="2" t="str">
         <f t="shared" ca="1" si="110"/>
-        <v>{"type":"h4","title":"62. Огoнь верховой","style":"width:85%;float:left"},{"type":"input","title":"папка","name":"e62","state":"{{e62}}","pattern":"[0-9]{1,2}","style":"width:15%;text-align:center;border-radius:8px"},{"type":"hr"},</v>
+        <v>{"type":"h4","title":"62. Огoнь верховой","style":"font-size:14px;width:85%;float:left"},{"type":"input","title":"папка","name":"e62","state":"{{e62}}","pattern":"[0-9]{1,2}","style":"background: #1c1c1c;border-color: #ffffff3d;border-style:solidborder-style: none;background: rgba(0, 0, 0, 0);color:#16d3f2;text-shadow: #16d3f2 1px 0 10px;height: 30px;width:15%;border-radius:8px;text-align:center"},{"type":"hr"},</v>
       </c>
       <c r="AH68" s="2" t="str">
         <f t="shared" ca="1" si="128"/>
@@ -10458,7 +10600,9 @@
         <f t="shared" ca="1" si="131"/>
         <v>62.Огoнь верховой</v>
       </c>
-      <c r="AL68" s="2"/>
+      <c r="AL68" s="31" t="s">
+        <v>440</v>
+      </c>
       <c r="AM68" s="2"/>
       <c r="AN68" s="17"/>
       <c r="AO68" s="2"/>
@@ -10573,7 +10717,7 @@
       </c>
       <c r="AG69" s="2" t="str">
         <f t="shared" ca="1" si="110"/>
-        <v>{"type":"h4","title":"63. Огoнь парящий","style":"width:85%;float:left"},{"type":"input","title":"папка","name":"e63","state":"{{e63}}","pattern":"[0-9]{1,2}","style":"width:15%;text-align:center;border-radius:8px"},{"type":"hr"},</v>
+        <v>{"type":"h4","title":"63. Огoнь парящий","style":"font-size:14px;width:85%;float:left"},{"type":"input","title":"папка","name":"e63","state":"{{e63}}","pattern":"[0-9]{1,2}","style":"background: #1c1c1c;border-color: #ffffff3d;border-style:solidborder-style: none;background: rgba(0, 0, 0, 0);color:#16d3f2;text-shadow: #16d3f2 1px 0 10px;height: 30px;width:15%;border-radius:8px;text-align:center"},{"type":"hr"},</v>
       </c>
       <c r="AH69" s="2" t="str">
         <f t="shared" ca="1" si="128"/>
@@ -10591,7 +10735,9 @@
         <f t="shared" ca="1" si="131"/>
         <v>63.Огoнь парящий</v>
       </c>
-      <c r="AL69" s="2"/>
+      <c r="AL69" s="31" t="s">
+        <v>440</v>
+      </c>
       <c r="AM69" s="2"/>
       <c r="AN69" s="17"/>
       <c r="AO69" s="2"/>
@@ -10705,7 +10851,7 @@
       </c>
       <c r="AG70" s="2" t="str">
         <f t="shared" ca="1" si="110"/>
-        <v>{"type":"h4","title":"64. Огонь с искрами","style":"width:85%;float:left"},{"type":"input","title":"папка","name":"e64","state":"{{e64}}","pattern":"[0-9]{1,2}","style":"width:15%;text-align:center;border-radius:8px"},{"type":"hr"},</v>
+        <v>{"type":"h4","title":"64. Огонь с искрами","style":"font-size:14px;width:85%;float:left"},{"type":"input","title":"папка","name":"e64","state":"{{e64}}","pattern":"[0-9]{1,2}","style":"background: #1c1c1c;border-color: #ffffff3d;border-style:solidborder-style: none;background: rgba(0, 0, 0, 0);color:#16d3f2;text-shadow: #16d3f2 1px 0 10px;height: 30px;width:15%;border-radius:8px;text-align:center"},{"type":"hr"},</v>
       </c>
       <c r="AH70" s="2" t="str">
         <f t="shared" ca="1" si="128"/>
@@ -10722,6 +10868,9 @@
       <c r="AK70" s="2" t="str">
         <f t="shared" ca="1" si="131"/>
         <v>64.Огонь с искрами</v>
+      </c>
+      <c r="AL70" s="31" t="s">
+        <v>440</v>
       </c>
     </row>
     <row r="71" spans="1:56" ht="14.25" customHeight="1">
@@ -10819,7 +10968,7 @@
       </c>
       <c r="AG71" s="2" t="str">
         <f t="shared" ca="1" si="110"/>
-        <v>{"type":"h4","title":"65. Осадки","style":"width:85%;float:left"},{"type":"input","title":"папка","name":"e65","state":"{{e65}}","pattern":"[0-9]{1,2}","style":"width:15%;text-align:center;border-radius:8px"},{"type":"hr"},</v>
+        <v>{"type":"h4","title":"65. Осадки","style":"font-size:14px;width:85%;float:left"},{"type":"input","title":"папка","name":"e65","state":"{{e65}}","pattern":"[0-9]{1,2}","style":"background: #1c1c1c;border-color: #ffffff3d;border-style:solidborder-style: none;background: rgba(0, 0, 0, 0);color:#16d3f2;text-shadow: #16d3f2 1px 0 10px;height: 30px;width:15%;border-radius:8px;text-align:center"},{"type":"hr"},</v>
       </c>
       <c r="AH71" s="2" t="str">
         <f t="shared" ca="1" si="128"/>
@@ -10837,7 +10986,9 @@
         <f t="shared" ca="1" si="131"/>
         <v>65.Осадки</v>
       </c>
-      <c r="AL71" s="2"/>
+      <c r="AL71" s="31" t="s">
+        <v>440</v>
+      </c>
       <c r="AM71" s="2"/>
       <c r="AN71" s="17"/>
       <c r="AO71" s="2"/>
@@ -10952,7 +11103,7 @@
       </c>
       <c r="AG72" s="2" t="str">
         <f t="shared" ca="1" si="110"/>
-        <v>{"type":"h4","title":"66. Осциллятор","style":"width:85%;float:left"},{"type":"input","title":"папка","name":"e66","state":"{{e66}}","pattern":"[0-9]{1,2}","style":"width:15%;text-align:center;border-radius:8px"},{"type":"hr"},</v>
+        <v>{"type":"h4","title":"66. Осциллятор","style":"font-size:14px;width:85%;float:left"},{"type":"input","title":"папка","name":"e66","state":"{{e66}}","pattern":"[0-9]{1,2}","style":"background: #1c1c1c;border-color: #ffffff3d;border-style:solidborder-style: none;background: rgba(0, 0, 0, 0);color:#16d3f2;text-shadow: #16d3f2 1px 0 10px;height: 30px;width:15%;border-radius:8px;text-align:center"},{"type":"hr"},</v>
       </c>
       <c r="AH72" s="2" t="str">
         <f t="shared" ca="1" si="128"/>
@@ -10970,7 +11121,9 @@
         <f t="shared" ca="1" si="131"/>
         <v>66.Осциллятор</v>
       </c>
-      <c r="AL72" s="2"/>
+      <c r="AL72" s="31" t="s">
+        <v>440</v>
+      </c>
       <c r="AM72" s="2"/>
       <c r="AN72" s="17"/>
       <c r="AO72" s="2"/>
@@ -11085,7 +11238,7 @@
       </c>
       <c r="AG73" s="2" t="str">
         <f t="shared" ca="1" si="110"/>
-        <v>{"type":"h4","title":"67. Облака","style":"width:85%;float:left"},{"type":"input","title":"папка","name":"e67","state":"{{e67}}","pattern":"[0-9]{1,2}","style":"width:15%;text-align:center;border-radius:8px"},{"type":"hr"},</v>
+        <v>{"type":"h4","title":"67. Облака","style":"font-size:14px;width:85%;float:left"},{"type":"input","title":"папка","name":"e67","state":"{{e67}}","pattern":"[0-9]{1,2}","style":"background: #1c1c1c;border-color: #ffffff3d;border-style:solidborder-style: none;background: rgba(0, 0, 0, 0);color:#16d3f2;text-shadow: #16d3f2 1px 0 10px;height: 30px;width:15%;border-radius:8px;text-align:center"},{"type":"hr"},</v>
       </c>
       <c r="AH73" s="2" t="str">
         <f t="shared" ca="1" si="128"/>
@@ -11103,7 +11256,9 @@
         <f t="shared" ca="1" si="131"/>
         <v>67.Облака</v>
       </c>
-      <c r="AL73" s="2"/>
+      <c r="AL73" s="31" t="s">
+        <v>440</v>
+      </c>
       <c r="AM73" s="2"/>
       <c r="AN73" s="17"/>
       <c r="AO73" s="2"/>
@@ -11223,7 +11378,7 @@
       </c>
       <c r="AG74" s="2" t="str">
         <f t="shared" ca="1" si="110"/>
-        <v>{"type":"h4","title":"68. Океан","style":"width:85%;float:left"},{"type":"input","title":"папка","name":"e68","state":"{{e68}}","pattern":"[0-9]{1,2}","style":"width:15%;text-align:center;border-radius:8px"},{"type":"hr"},</v>
+        <v>{"type":"h4","title":"68. Океан","style":"font-size:14px;width:85%;float:left"},{"type":"input","title":"папка","name":"e68","state":"{{e68}}","pattern":"[0-9]{1,2}","style":"background: #1c1c1c;border-color: #ffffff3d;border-style:solidborder-style: none;background: rgba(0, 0, 0, 0);color:#16d3f2;text-shadow: #16d3f2 1px 0 10px;height: 30px;width:15%;border-radius:8px;text-align:center"},{"type":"hr"},</v>
       </c>
       <c r="AH74" s="31" t="str">
         <f t="shared" ca="1" si="128"/>
@@ -11241,7 +11396,9 @@
         <f t="shared" ca="1" si="131"/>
         <v>68.Океан</v>
       </c>
-      <c r="AL74" s="31"/>
+      <c r="AL74" s="31" t="s">
+        <v>440</v>
+      </c>
       <c r="AM74" s="31"/>
       <c r="AN74" s="34"/>
       <c r="AO74" s="31"/>
@@ -11336,7 +11493,7 @@
       </c>
       <c r="AG75" s="2" t="str">
         <f t="shared" ca="1" si="110"/>
-        <v>{"type":"h4","title":"69. Осьминог","style":"width:85%;float:left"},{"type":"input","title":"папка","name":"e69","state":"{{e69}}","pattern":"[0-9]{1,2}","style":"width:15%;text-align:center;border-radius:8px"},{"type":"hr"},</v>
+        <v>{"type":"h4","title":"69. Осьминог","style":"font-size:14px;width:85%;float:left"},{"type":"input","title":"папка","name":"e69","state":"{{e69}}","pattern":"[0-9]{1,2}","style":"background: #1c1c1c;border-color: #ffffff3d;border-style:solidborder-style: none;background: rgba(0, 0, 0, 0);color:#16d3f2;text-shadow: #16d3f2 1px 0 10px;height: 30px;width:15%;border-radius:8px;text-align:center"},{"type":"hr"},</v>
       </c>
       <c r="AH75" s="31" t="str">
         <f t="shared" ca="1" si="128"/>
@@ -11353,6 +11510,9 @@
       <c r="AK75" s="2" t="str">
         <f t="shared" ca="1" si="131"/>
         <v>69.Осьминог</v>
+      </c>
+      <c r="AL75" s="31" t="s">
+        <v>440</v>
       </c>
     </row>
     <row r="76" spans="1:56" s="30" customFormat="1" ht="14.25" customHeight="1">
@@ -11451,7 +11611,7 @@
       </c>
       <c r="AG76" s="2" t="str">
         <f t="shared" ca="1" si="110"/>
-        <v>{"type":"h4","title":"70. Павлин","style":"width:85%;float:left"},{"type":"input","title":"папка","name":"e70","state":"{{e70}}","pattern":"[0-9]{1,2}","style":"width:15%;text-align:center;border-radius:8px"},{"type":"hr"},</v>
+        <v>{"type":"h4","title":"70. Павлин","style":"font-size:14px;width:85%;float:left"},{"type":"input","title":"папка","name":"e70","state":"{{e70}}","pattern":"[0-9]{1,2}","style":"background: #1c1c1c;border-color: #ffffff3d;border-style:solidborder-style: none;background: rgba(0, 0, 0, 0);color:#16d3f2;text-shadow: #16d3f2 1px 0 10px;height: 30px;width:15%;border-radius:8px;text-align:center"},{"type":"hr"},</v>
       </c>
       <c r="AH76" s="31" t="str">
         <f t="shared" ref="AH76:AH82" ca="1" si="143">CONCATENATE("""",A76,"""",": """,A76,".",C76,""",")</f>
@@ -11469,7 +11629,9 @@
         <f t="shared" ca="1" si="131"/>
         <v>70.Павлин</v>
       </c>
-      <c r="AL76" s="31"/>
+      <c r="AL76" s="31" t="s">
+        <v>440</v>
+      </c>
       <c r="AM76" s="31"/>
       <c r="AN76" s="34"/>
       <c r="AO76" s="31"/>
@@ -11575,7 +11737,7 @@
       </c>
       <c r="AG77" s="2" t="str">
         <f t="shared" ca="1" si="110"/>
-        <v>{"type":"h4","title":"71. Песочные часы","style":"width:85%;float:left"},{"type":"input","title":"папка","name":"e71","state":"{{e71}}","pattern":"[0-9]{1,2}","style":"width:15%;text-align:center;border-radius:8px"},{"type":"hr"},</v>
+        <v>{"type":"h4","title":"71. Песочные часы","style":"font-size:14px;width:85%;float:left"},{"type":"input","title":"папка","name":"e71","state":"{{e71}}","pattern":"[0-9]{1,2}","style":"background: #1c1c1c;border-color: #ffffff3d;border-style:solidborder-style: none;background: rgba(0, 0, 0, 0);color:#16d3f2;text-shadow: #16d3f2 1px 0 10px;height: 30px;width:15%;border-radius:8px;text-align:center"},{"type":"hr"},</v>
       </c>
       <c r="AH77" s="2" t="str">
         <f t="shared" ca="1" si="143"/>
@@ -11593,7 +11755,9 @@
         <f t="shared" ca="1" si="131"/>
         <v>71.Песочные часы</v>
       </c>
-      <c r="AL77" s="2"/>
+      <c r="AL77" s="31" t="s">
+        <v>440</v>
+      </c>
       <c r="AM77" s="2"/>
       <c r="AN77" s="17"/>
       <c r="AO77" s="2"/>
@@ -11704,7 +11868,7 @@
       </c>
       <c r="AG78" s="2" t="str">
         <f t="shared" ca="1" si="110"/>
-        <v>{"type":"h4","title":"72. Пейнтбол","style":"width:85%;float:left"},{"type":"input","title":"папка","name":"e72","state":"{{e72}}","pattern":"[0-9]{1,2}","style":"width:15%;text-align:center;border-radius:8px"},{"type":"hr"},</v>
+        <v>{"type":"h4","title":"72. Пейнтбол","style":"font-size:14px;width:85%;float:left"},{"type":"input","title":"папка","name":"e72","state":"{{e72}}","pattern":"[0-9]{1,2}","style":"background: #1c1c1c;border-color: #ffffff3d;border-style:solidborder-style: none;background: rgba(0, 0, 0, 0);color:#16d3f2;text-shadow: #16d3f2 1px 0 10px;height: 30px;width:15%;border-radius:8px;text-align:center"},{"type":"hr"},</v>
       </c>
       <c r="AH78" s="2" t="str">
         <f t="shared" ca="1" si="143"/>
@@ -11722,7 +11886,9 @@
         <f t="shared" ca="1" si="131"/>
         <v>72.Пейнтбол</v>
       </c>
-      <c r="AL78" s="2"/>
+      <c r="AL78" s="31" t="s">
+        <v>440</v>
+      </c>
       <c r="AM78" s="2"/>
       <c r="AN78" s="17"/>
       <c r="AO78" s="2"/>
@@ -11837,7 +12003,7 @@
       </c>
       <c r="AG79" s="2" t="str">
         <f t="shared" ca="1" si="110"/>
-        <v>{"type":"h4","title":"73. Пикассо","style":"width:85%;float:left"},{"type":"input","title":"папка","name":"e73","state":"{{e73}}","pattern":"[0-9]{1,2}","style":"width:15%;text-align:center;border-radius:8px"},{"type":"hr"},</v>
+        <v>{"type":"h4","title":"73. Пикассо","style":"font-size:14px;width:85%;float:left"},{"type":"input","title":"папка","name":"e73","state":"{{e73}}","pattern":"[0-9]{1,2}","style":"background: #1c1c1c;border-color: #ffffff3d;border-style:solidborder-style: none;background: rgba(0, 0, 0, 0);color:#16d3f2;text-shadow: #16d3f2 1px 0 10px;height: 30px;width:15%;border-radius:8px;text-align:center"},{"type":"hr"},</v>
       </c>
       <c r="AH79" s="2" t="str">
         <f t="shared" ca="1" si="143"/>
@@ -11855,7 +12021,9 @@
         <f t="shared" ca="1" si="131"/>
         <v>73.Пикассо</v>
       </c>
-      <c r="AL79" s="2"/>
+      <c r="AL79" s="31" t="s">
+        <v>440</v>
+      </c>
       <c r="AM79" s="2"/>
       <c r="AN79" s="17"/>
       <c r="AO79" s="2"/>
@@ -11970,7 +12138,7 @@
       </c>
       <c r="AG80" s="2" t="str">
         <f t="shared" ca="1" si="110"/>
-        <v>{"type":"h4","title":"74. Плазма","style":"width:85%;float:left"},{"type":"input","title":"папка","name":"e74","state":"{{e74}}","pattern":"[0-9]{1,2}","style":"width:15%;text-align:center;border-radius:8px"},{"type":"hr"},</v>
+        <v>{"type":"h4","title":"74. Плазма","style":"font-size:14px;width:85%;float:left"},{"type":"input","title":"папка","name":"e74","state":"{{e74}}","pattern":"[0-9]{1,2}","style":"background: #1c1c1c;border-color: #ffffff3d;border-style:solidborder-style: none;background: rgba(0, 0, 0, 0);color:#16d3f2;text-shadow: #16d3f2 1px 0 10px;height: 30px;width:15%;border-radius:8px;text-align:center"},{"type":"hr"},</v>
       </c>
       <c r="AH80" s="2" t="str">
         <f t="shared" ca="1" si="143"/>
@@ -11988,7 +12156,9 @@
         <f t="shared" ca="1" si="131"/>
         <v>74.Плазма</v>
       </c>
-      <c r="AL80" s="2"/>
+      <c r="AL80" s="31" t="s">
+        <v>440</v>
+      </c>
       <c r="AM80" s="2"/>
       <c r="AN80" s="17"/>
       <c r="AO80" s="2"/>
@@ -12103,7 +12273,7 @@
       </c>
       <c r="AG81" s="2" t="str">
         <f t="shared" ca="1" si="110"/>
-        <v>{"type":"h4","title":"75. Плазменная лампа","style":"width:85%;float:left"},{"type":"input","title":"папка","name":"e75","state":"{{e75}}","pattern":"[0-9]{1,2}","style":"width:15%;text-align:center;border-radius:8px"},{"type":"hr"},</v>
+        <v>{"type":"h4","title":"75. Плазменная лампа","style":"font-size:14px;width:85%;float:left"},{"type":"input","title":"папка","name":"e75","state":"{{e75}}","pattern":"[0-9]{1,2}","style":"background: #1c1c1c;border-color: #ffffff3d;border-style:solidborder-style: none;background: rgba(0, 0, 0, 0);color:#16d3f2;text-shadow: #16d3f2 1px 0 10px;height: 30px;width:15%;border-radius:8px;text-align:center"},{"type":"hr"},</v>
       </c>
       <c r="AH81" s="2" t="str">
         <f t="shared" ca="1" si="143"/>
@@ -12121,7 +12291,9 @@
         <f t="shared" ca="1" si="131"/>
         <v>75.Плазменная лампа</v>
       </c>
-      <c r="AL81" s="2"/>
+      <c r="AL81" s="31" t="s">
+        <v>440</v>
+      </c>
       <c r="AM81" s="2"/>
       <c r="AN81" s="17"/>
       <c r="AO81" s="2"/>
@@ -12235,7 +12407,7 @@
       </c>
       <c r="AG82" s="2" t="str">
         <f t="shared" ca="1" si="110"/>
-        <v>{"type":"h4","title":"76. Плазменные волны","style":"width:85%;float:left"},{"type":"input","title":"папка","name":"e76","state":"{{e76}}","pattern":"[0-9]{1,2}","style":"width:15%;text-align:center;border-radius:8px"},{"type":"hr"},</v>
+        <v>{"type":"h4","title":"76. Плазменные волны","style":"font-size:14px;width:85%;float:left"},{"type":"input","title":"папка","name":"e76","state":"{{e76}}","pattern":"[0-9]{1,2}","style":"background: #1c1c1c;border-color: #ffffff3d;border-style:solidborder-style: none;background: rgba(0, 0, 0, 0);color:#16d3f2;text-shadow: #16d3f2 1px 0 10px;height: 30px;width:15%;border-radius:8px;text-align:center"},{"type":"hr"},</v>
       </c>
       <c r="AH82" s="2" t="str">
         <f t="shared" ca="1" si="143"/>
@@ -12252,6 +12424,9 @@
       <c r="AK82" s="2" t="str">
         <f t="shared" ca="1" si="131"/>
         <v>76.Плазменные волны</v>
+      </c>
+      <c r="AL82" s="31" t="s">
+        <v>440</v>
       </c>
     </row>
     <row r="83" spans="1:56" ht="14.25" customHeight="1">
@@ -12349,7 +12524,7 @@
       </c>
       <c r="AG83" s="2" t="str">
         <f t="shared" ca="1" si="110"/>
-        <v>{"type":"h4","title":"77. Пламя","style":"width:85%;float:left"},{"type":"input","title":"папка","name":"e77","state":"{{e77}}","pattern":"[0-9]{1,2}","style":"width:15%;text-align:center;border-radius:8px"},{"type":"hr"},</v>
+        <v>{"type":"h4","title":"77. Пламя","style":"font-size:14px;width:85%;float:left"},{"type":"input","title":"папка","name":"e77","state":"{{e77}}","pattern":"[0-9]{1,2}","style":"background: #1c1c1c;border-color: #ffffff3d;border-style:solidborder-style: none;background: rgba(0, 0, 0, 0);color:#16d3f2;text-shadow: #16d3f2 1px 0 10px;height: 30px;width:15%;border-radius:8px;text-align:center"},{"type":"hr"},</v>
       </c>
       <c r="AH83" s="2" t="str">
         <f ca="1">CONCATENATE("""",A83,"""",": """,A83,".",C83,""",")</f>
@@ -12367,7 +12542,9 @@
         <f t="shared" ca="1" si="131"/>
         <v>77.Пламя</v>
       </c>
-      <c r="AL83" s="2"/>
+      <c r="AL83" s="31" t="s">
+        <v>440</v>
+      </c>
       <c r="AM83" s="2"/>
       <c r="AN83" s="17"/>
       <c r="AO83" s="2"/>
@@ -12465,7 +12642,7 @@
       </c>
       <c r="AG84" s="2" t="str">
         <f t="shared" ca="1" si="110"/>
-        <v>{"type":"h4","title":"78. Планета Земля","style":"width:85%;float:left"},{"type":"input","title":"папка","name":"e78","state":"{{e78}}","pattern":"[0-9]{1,2}","style":"width:15%;text-align:center;border-radius:8px"},{"type":"hr"},</v>
+        <v>{"type":"h4","title":"78. Планета Земля","style":"font-size:14px;width:85%;float:left"},{"type":"input","title":"папка","name":"e78","state":"{{e78}}","pattern":"[0-9]{1,2}","style":"background: #1c1c1c;border-color: #ffffff3d;border-style:solidborder-style: none;background: rgba(0, 0, 0, 0);color:#16d3f2;text-shadow: #16d3f2 1px 0 10px;height: 30px;width:15%;border-radius:8px;text-align:center"},{"type":"hr"},</v>
       </c>
       <c r="AH84" s="2" t="str">
         <f ca="1">CONCATENATE("""",A84,"""",": """,A84,".",C84,""",")</f>
@@ -12482,6 +12659,9 @@
       <c r="AK84" s="2" t="str">
         <f t="shared" ca="1" si="131"/>
         <v>78.Планета Земля</v>
+      </c>
+      <c r="AL84" s="31" t="s">
+        <v>440</v>
       </c>
     </row>
     <row r="85" spans="1:56" ht="14.25" customHeight="1">
@@ -12579,7 +12759,7 @@
       </c>
       <c r="AG85" s="2" t="str">
         <f t="shared" ca="1" si="110"/>
-        <v>{"type":"h4","title":"79. Побочный эффект","style":"width:85%;float:left"},{"type":"input","title":"папка","name":"e79","state":"{{e79}}","pattern":"[0-9]{1,2}","style":"width:15%;text-align:center;border-radius:8px"},{"type":"hr"},</v>
+        <v>{"type":"h4","title":"79. Побочный эффект","style":"font-size:14px;width:85%;float:left"},{"type":"input","title":"папка","name":"e79","state":"{{e79}}","pattern":"[0-9]{1,2}","style":"background: #1c1c1c;border-color: #ffffff3d;border-style:solidborder-style: none;background: rgba(0, 0, 0, 0);color:#16d3f2;text-shadow: #16d3f2 1px 0 10px;height: 30px;width:15%;border-radius:8px;text-align:center"},{"type":"hr"},</v>
       </c>
       <c r="AH85" s="2" t="str">
         <f t="shared" ref="AH85:AH90" ca="1" si="158">CONCATENATE("""",A85,"""",": """,A85,".",C85,""",")</f>
@@ -12597,7 +12777,9 @@
         <f t="shared" ca="1" si="131"/>
         <v>79.Побочный эффект</v>
       </c>
-      <c r="AL85" s="2"/>
+      <c r="AL85" s="31" t="s">
+        <v>440</v>
+      </c>
       <c r="AM85" s="2"/>
       <c r="AN85" s="17"/>
       <c r="AO85" s="2"/>
@@ -12712,7 +12894,7 @@
       </c>
       <c r="AG86" s="2" t="str">
         <f t="shared" ca="1" si="110"/>
-        <v>{"type":"h4","title":"80. Попкорн","style":"width:85%;float:left"},{"type":"input","title":"папка","name":"e80","state":"{{e80}}","pattern":"[0-9]{1,2}","style":"width:15%;text-align:center;border-radius:8px"},{"type":"hr"},</v>
+        <v>{"type":"h4","title":"80. Попкорн","style":"font-size:14px;width:85%;float:left"},{"type":"input","title":"папка","name":"e80","state":"{{e80}}","pattern":"[0-9]{1,2}","style":"background: #1c1c1c;border-color: #ffffff3d;border-style:solidborder-style: none;background: rgba(0, 0, 0, 0);color:#16d3f2;text-shadow: #16d3f2 1px 0 10px;height: 30px;width:15%;border-radius:8px;text-align:center"},{"type":"hr"},</v>
       </c>
       <c r="AH86" s="2" t="str">
         <f t="shared" ca="1" si="158"/>
@@ -12730,7 +12912,9 @@
         <f t="shared" ca="1" si="131"/>
         <v>80.Попкорн</v>
       </c>
-      <c r="AL86" s="2"/>
+      <c r="AL86" s="31" t="s">
+        <v>440</v>
+      </c>
       <c r="AM86" s="2"/>
       <c r="AN86" s="17"/>
       <c r="AO86" s="2"/>
@@ -12841,7 +13025,7 @@
       </c>
       <c r="AG87" s="2" t="str">
         <f t="shared" ca="1" si="110"/>
-        <v>{"type":"h4","title":"81. Призмата","style":"width:85%;float:left"},{"type":"input","title":"папка","name":"e81","state":"{{e81}}","pattern":"[0-9]{1,2}","style":"width:15%;text-align:center;border-radius:8px"},{"type":"hr"},</v>
+        <v>{"type":"h4","title":"81. Призмата","style":"font-size:14px;width:85%;float:left"},{"type":"input","title":"папка","name":"e81","state":"{{e81}}","pattern":"[0-9]{1,2}","style":"background: #1c1c1c;border-color: #ffffff3d;border-style:solidborder-style: none;background: rgba(0, 0, 0, 0);color:#16d3f2;text-shadow: #16d3f2 1px 0 10px;height: 30px;width:15%;border-radius:8px;text-align:center"},{"type":"hr"},</v>
       </c>
       <c r="AH87" s="2" t="str">
         <f t="shared" ca="1" si="158"/>
@@ -12859,7 +13043,9 @@
         <f t="shared" ca="1" si="131"/>
         <v>81.Призмата</v>
       </c>
-      <c r="AL87" s="2"/>
+      <c r="AL87" s="31" t="s">
+        <v>440</v>
+      </c>
       <c r="AM87" s="2"/>
       <c r="AN87" s="17"/>
       <c r="AO87" s="2"/>
@@ -12974,7 +13160,7 @@
       </c>
       <c r="AG88" s="2" t="str">
         <f t="shared" ca="1" si="110"/>
-        <v>{"type":"h4","title":"82. Притяжение","style":"width:85%;float:left"},{"type":"input","title":"папка","name":"e82","state":"{{e82}}","pattern":"[0-9]{1,2}","style":"width:15%;text-align:center;border-radius:8px"},{"type":"hr"},</v>
+        <v>{"type":"h4","title":"82. Притяжение","style":"font-size:14px;width:85%;float:left"},{"type":"input","title":"папка","name":"e82","state":"{{e82}}","pattern":"[0-9]{1,2}","style":"background: #1c1c1c;border-color: #ffffff3d;border-style:solidborder-style: none;background: rgba(0, 0, 0, 0);color:#16d3f2;text-shadow: #16d3f2 1px 0 10px;height: 30px;width:15%;border-radius:8px;text-align:center"},{"type":"hr"},</v>
       </c>
       <c r="AH88" s="2" t="str">
         <f t="shared" ca="1" si="158"/>
@@ -12992,7 +13178,9 @@
         <f t="shared" ca="1" si="131"/>
         <v>82.Притяжение</v>
       </c>
-      <c r="AL88" s="2"/>
+      <c r="AL88" s="31" t="s">
+        <v>440</v>
+      </c>
       <c r="AM88" s="2"/>
       <c r="AN88" s="17"/>
       <c r="AO88" s="2"/>
@@ -13107,7 +13295,7 @@
       </c>
       <c r="AG89" s="2" t="str">
         <f t="shared" ca="1" si="110"/>
-        <v>{"type":"h4","title":"83. Пpыгyны","style":"width:85%;float:left"},{"type":"input","title":"папка","name":"e83","state":"{{e83}}","pattern":"[0-9]{1,2}","style":"width:15%;text-align:center;border-radius:8px"},{"type":"hr"},</v>
+        <v>{"type":"h4","title":"83. Пpыгyны","style":"font-size:14px;width:85%;float:left"},{"type":"input","title":"папка","name":"e83","state":"{{e83}}","pattern":"[0-9]{1,2}","style":"background: #1c1c1c;border-color: #ffffff3d;border-style:solidborder-style: none;background: rgba(0, 0, 0, 0);color:#16d3f2;text-shadow: #16d3f2 1px 0 10px;height: 30px;width:15%;border-radius:8px;text-align:center"},{"type":"hr"},</v>
       </c>
       <c r="AH89" s="2" t="str">
         <f t="shared" ca="1" si="158"/>
@@ -13125,7 +13313,9 @@
         <f t="shared" ca="1" si="131"/>
         <v>83.Пpыгyны</v>
       </c>
-      <c r="AL89" s="2"/>
+      <c r="AL89" s="31" t="s">
+        <v>440</v>
+      </c>
       <c r="AM89" s="2"/>
       <c r="AN89" s="17"/>
       <c r="AO89" s="2"/>
@@ -13236,7 +13426,7 @@
       </c>
       <c r="AG90" s="2" t="str">
         <f t="shared" ca="1" si="110"/>
-        <v>{"type":"h4","title":"84. Пульс","style":"width:85%;float:left"},{"type":"input","title":"папка","name":"e84","state":"{{e84}}","pattern":"[0-9]{1,2}","style":"width:15%;text-align:center;border-radius:8px"},{"type":"hr"},</v>
+        <v>{"type":"h4","title":"84. Пульс","style":"font-size:14px;width:85%;float:left"},{"type":"input","title":"папка","name":"e84","state":"{{e84}}","pattern":"[0-9]{1,2}","style":"background: #1c1c1c;border-color: #ffffff3d;border-style:solidborder-style: none;background: rgba(0, 0, 0, 0);color:#16d3f2;text-shadow: #16d3f2 1px 0 10px;height: 30px;width:15%;border-radius:8px;text-align:center"},{"type":"hr"},</v>
       </c>
       <c r="AH90" s="2" t="str">
         <f t="shared" ca="1" si="158"/>
@@ -13254,7 +13444,9 @@
         <f t="shared" ca="1" si="131"/>
         <v>84.Пульс</v>
       </c>
-      <c r="AL90" s="2"/>
+      <c r="AL90" s="31" t="s">
+        <v>440</v>
+      </c>
       <c r="AM90" s="2"/>
       <c r="AN90" s="17"/>
       <c r="AO90" s="2"/>
@@ -13313,7 +13505,7 @@
         <v>267</v>
       </c>
       <c r="AK91" s="2"/>
-      <c r="AL91" s="2"/>
+      <c r="AL91" s="31"/>
       <c r="AM91" s="2"/>
       <c r="AN91" s="5"/>
       <c r="AO91" s="25"/>
@@ -13372,7 +13564,7 @@
         <v>269</v>
       </c>
       <c r="AK92" s="2"/>
-      <c r="AL92" s="2"/>
+      <c r="AL92" s="31"/>
       <c r="AM92" s="2"/>
       <c r="AN92" s="4"/>
       <c r="AO92" s="5"/>
@@ -13482,8 +13674,8 @@
         <v>{"type":"checkbox","class":"checkbox-big","name":"e85","title":"85. Пульс белый","style":"font-size:16px;display:block","state":"{{e85}}"},</v>
       </c>
       <c r="AG93" s="2" t="str">
-        <f t="shared" ref="AG93:AG135" ca="1" si="174">CONCATENATE("{""type"":""h4"",""title"":""",A93,". ",C93,""",""style"":""width:85%;float:left""},{""type"":""input"",""title"":""папка"",""name"":""e",T93,""",""state"":""{{e",T93,"}}"",""pattern"":""[0-9]{1,2}"",""style"":""width:15%;text-align:center;border-radius:8px""},{""type"":""hr""},")</f>
-        <v>{"type":"h4","title":"85. Пульс белый","style":"width:85%;float:left"},{"type":"input","title":"папка","name":"e85","state":"{{e85}}","pattern":"[0-9]{1,2}","style":"width:15%;text-align:center;border-radius:8px"},{"type":"hr"},</v>
+        <f t="shared" ref="AG93:AG135" ca="1" si="174">CONCATENATE("{""type"":""h4"",""title"":""",A93,". ",C93,""",""style"":""font-size:14px;width:85%;float:left""},{""type"":""input"",""title"":""папка"",""name"":""e",T93,""",""state"":""{{e",T93,"}}"",""pattern"":""[0-9]{1,2}"",""style"":""",AL93,"""},{""type"":""hr""},")</f>
+        <v>{"type":"h4","title":"85. Пульс белый","style":"font-size:14px;width:85%;float:left"},{"type":"input","title":"папка","name":"e85","state":"{{e85}}","pattern":"[0-9]{1,2}","style":"background: #1c1c1c;border-color: #ffffff3d;border-style:solidborder-style: none;background: rgba(0, 0, 0, 0);color:#16d3f2;text-shadow: #16d3f2 1px 0 10px;height: 30px;width:15%;border-radius:8px;text-align:center"},{"type":"hr"},</v>
       </c>
       <c r="AH93" s="2" t="str">
         <f t="shared" ref="AH93:AH99" ca="1" si="175">CONCATENATE("""",A93,"""",": """,A93,".",C93,""",")</f>
@@ -13501,7 +13693,9 @@
         <f t="shared" ref="AK93:AK99" ca="1" si="178">CONCATENATE("",A93,"",".",C93,"")</f>
         <v>85.Пульс белый</v>
       </c>
-      <c r="AL93" s="2"/>
+      <c r="AL93" s="31" t="s">
+        <v>440</v>
+      </c>
       <c r="AM93" s="2"/>
       <c r="AN93" s="17"/>
       <c r="AO93" s="2"/>
@@ -13616,7 +13810,7 @@
       </c>
       <c r="AG94" s="2" t="str">
         <f t="shared" ca="1" si="174"/>
-        <v>{"type":"h4","title":"86. Пульс радужный","style":"width:85%;float:left"},{"type":"input","title":"папка","name":"e86","state":"{{e86}}","pattern":"[0-9]{1,2}","style":"width:15%;text-align:center;border-radius:8px"},{"type":"hr"},</v>
+        <v>{"type":"h4","title":"86. Пульс радужный","style":"font-size:14px;width:85%;float:left"},{"type":"input","title":"папка","name":"e86","state":"{{e86}}","pattern":"[0-9]{1,2}","style":"background: #1c1c1c;border-color: #ffffff3d;border-style:solidborder-style: none;background: rgba(0, 0, 0, 0);color:#16d3f2;text-shadow: #16d3f2 1px 0 10px;height: 30px;width:15%;border-radius:8px;text-align:center"},{"type":"hr"},</v>
       </c>
       <c r="AH94" s="2" t="str">
         <f t="shared" ca="1" si="175"/>
@@ -13634,7 +13828,9 @@
         <f t="shared" ca="1" si="178"/>
         <v>86.Пульс радужный</v>
       </c>
-      <c r="AL94" s="2"/>
+      <c r="AL94" s="31" t="s">
+        <v>440</v>
+      </c>
       <c r="AM94" s="2"/>
       <c r="AN94" s="17"/>
       <c r="AO94" s="2"/>
@@ -13749,7 +13945,7 @@
       </c>
       <c r="AG95" s="2" t="str">
         <f t="shared" ca="1" si="174"/>
-        <v>{"type":"h4","title":"87. Радиальная волна","style":"width:85%;float:left"},{"type":"input","title":"папка","name":"e87","state":"{{e87}}","pattern":"[0-9]{1,2}","style":"width:15%;text-align:center;border-radius:8px"},{"type":"hr"},</v>
+        <v>{"type":"h4","title":"87. Радиальная волна","style":"font-size:14px;width:85%;float:left"},{"type":"input","title":"папка","name":"e87","state":"{{e87}}","pattern":"[0-9]{1,2}","style":"background: #1c1c1c;border-color: #ffffff3d;border-style:solidborder-style: none;background: rgba(0, 0, 0, 0);color:#16d3f2;text-shadow: #16d3f2 1px 0 10px;height: 30px;width:15%;border-radius:8px;text-align:center"},{"type":"hr"},</v>
       </c>
       <c r="AH95" s="2" t="str">
         <f t="shared" ca="1" si="175"/>
@@ -13767,7 +13963,9 @@
         <f t="shared" ca="1" si="178"/>
         <v>87.Радиальная волна</v>
       </c>
-      <c r="AL95" s="2"/>
+      <c r="AL95" s="31" t="s">
+        <v>440</v>
+      </c>
       <c r="AM95" s="2"/>
       <c r="AN95" s="17"/>
       <c r="AO95" s="2"/>
@@ -13881,8 +14079,8 @@
         <v>{"type":"checkbox","class":"checkbox-big","name":"e88","title":"88. Радуга","style":"font-size:16px;display:block","state":"{{e88}}"},</v>
       </c>
       <c r="AG96" s="2" t="str">
-        <f t="shared" ca="1" si="174"/>
-        <v>{"type":"h4","title":"88. Радуга","style":"width:85%;float:left"},{"type":"input","title":"папка","name":"e88","state":"{{e88}}","pattern":"[0-9]{1,2}","style":"width:15%;text-align:center;border-radius:8px"},{"type":"hr"},</v>
+        <f ca="1">CONCATENATE("{""type"":""h4"",""title"":""",A96,". ",C96,""",""style"":""font-size:14px;width:85%;float:left""},{""type"":""input"",""title"":""папка"",""name"":""e",T96,""",""state"":""{{e",T96,"}}"",""pattern"":""[0-9]{1,2}"",""style"":""",AL96,"""},{""type"":""hr""},")</f>
+        <v>{"type":"h4","title":"88. Радуга","style":"font-size:14px;width:85%;float:left"},{"type":"input","title":"папка","name":"e88","state":"{{e88}}","pattern":"[0-9]{1,2}","style":"background: #1c1c1c;border-color: #ffffff3d;border-style:solidborder-style: none;background: rgba(0, 0, 0, 0);color:#16d3f2;text-shadow: #16d3f2 1px 0 10px;height: 30px;width:15%;border-radius:8px;text-align:center"},{"type":"hr"},</v>
       </c>
       <c r="AH96" s="2" t="str">
         <f t="shared" ca="1" si="175"/>
@@ -13900,7 +14098,9 @@
         <f t="shared" ca="1" si="178"/>
         <v>88.Радуга</v>
       </c>
-      <c r="AL96" s="2"/>
+      <c r="AL96" s="31" t="s">
+        <v>440</v>
+      </c>
       <c r="AM96" s="2"/>
       <c r="AN96" s="17"/>
       <c r="AO96" s="2"/>
@@ -14015,7 +14215,7 @@
       </c>
       <c r="AG97" s="2" t="str">
         <f t="shared" ca="1" si="174"/>
-        <v>{"type":"h4","title":"89. Радуга 3D","style":"width:85%;float:left"},{"type":"input","title":"папка","name":"e89","state":"{{e89}}","pattern":"[0-9]{1,2}","style":"width:15%;text-align:center;border-radius:8px"},{"type":"hr"},</v>
+        <v>{"type":"h4","title":"89. Радуга 3D","style":"font-size:14px;width:85%;float:left"},{"type":"input","title":"папка","name":"e89","state":"{{e89}}","pattern":"[0-9]{1,2}","style":"background: #1c1c1c;border-color: #ffffff3d;border-style:solidborder-style: none;background: rgba(0, 0, 0, 0);color:#16d3f2;text-shadow: #16d3f2 1px 0 10px;height: 30px;width:15%;border-radius:8px;text-align:center"},{"type":"hr"},</v>
       </c>
       <c r="AH97" s="2" t="str">
         <f t="shared" ca="1" si="175"/>
@@ -14033,7 +14233,9 @@
         <f t="shared" ca="1" si="178"/>
         <v>89.Радуга 3D</v>
       </c>
-      <c r="AL97" s="2"/>
+      <c r="AL97" s="31" t="s">
+        <v>440</v>
+      </c>
       <c r="AM97" s="2"/>
       <c r="AN97" s="17"/>
       <c r="AO97" s="2"/>
@@ -14143,7 +14345,7 @@
       </c>
       <c r="AG98" s="2" t="str">
         <f t="shared" ca="1" si="174"/>
-        <v>{"type":"h4","title":"90. Радужное Пятно","style":"width:85%;float:left"},{"type":"input","title":"папка","name":"e90","state":"{{e90}}","pattern":"[0-9]{1,2}","style":"width:15%;text-align:center;border-radius:8px"},{"type":"hr"},</v>
+        <v>{"type":"h4","title":"90. Радужное Пятно","style":"font-size:14px;width:85%;float:left"},{"type":"input","title":"папка","name":"e90","state":"{{e90}}","pattern":"[0-9]{1,2}","style":"background: #1c1c1c;border-color: #ffffff3d;border-style:solidborder-style: none;background: rgba(0, 0, 0, 0);color:#16d3f2;text-shadow: #16d3f2 1px 0 10px;height: 30px;width:15%;border-radius:8px;text-align:center"},{"type":"hr"},</v>
       </c>
       <c r="AH98" s="2" t="str">
         <f t="shared" ca="1" si="175"/>
@@ -14160,6 +14362,9 @@
       <c r="AK98" s="2" t="str">
         <f t="shared" ca="1" si="178"/>
         <v>90.Радужное Пятно</v>
+      </c>
+      <c r="AL98" s="31" t="s">
+        <v>440</v>
       </c>
     </row>
     <row r="99" spans="1:56">
@@ -14252,7 +14457,7 @@
       </c>
       <c r="AG99" s="2" t="str">
         <f t="shared" ca="1" si="174"/>
-        <v>{"type":"h4","title":"91. Радужные кольца","style":"width:85%;float:left"},{"type":"input","title":"папка","name":"e91","state":"{{e91}}","pattern":"[0-9]{1,2}","style":"width:15%;text-align:center;border-radius:8px"},{"type":"hr"},</v>
+        <v>{"type":"h4","title":"91. Радужные кольца","style":"font-size:14px;width:85%;float:left"},{"type":"input","title":"папка","name":"e91","state":"{{e91}}","pattern":"[0-9]{1,2}","style":"background: #1c1c1c;border-color: #ffffff3d;border-style:solidborder-style: none;background: rgba(0, 0, 0, 0);color:#16d3f2;text-shadow: #16d3f2 1px 0 10px;height: 30px;width:15%;border-radius:8px;text-align:center"},{"type":"hr"},</v>
       </c>
       <c r="AH99" s="2" t="str">
         <f t="shared" ca="1" si="175"/>
@@ -14269,6 +14474,9 @@
       <c r="AK99" s="2" t="str">
         <f t="shared" ca="1" si="178"/>
         <v>91.Радужные кольца</v>
+      </c>
+      <c r="AL99" s="31" t="s">
+        <v>440</v>
       </c>
     </row>
     <row r="100" spans="1:56" ht="14.25" customHeight="1">
@@ -14366,7 +14574,7 @@
       </c>
       <c r="AG100" s="2" t="str">
         <f t="shared" ca="1" si="174"/>
-        <v>{"type":"h4","title":"92. Радужный змей","style":"width:85%;float:left"},{"type":"input","title":"папка","name":"e92","state":"{{e92}}","pattern":"[0-9]{1,2}","style":"width:15%;text-align:center;border-radius:8px"},{"type":"hr"},</v>
+        <v>{"type":"h4","title":"92. Радужный змей","style":"font-size:14px;width:85%;float:left"},{"type":"input","title":"папка","name":"e92","state":"{{e92}}","pattern":"[0-9]{1,2}","style":"background: #1c1c1c;border-color: #ffffff3d;border-style:solidborder-style: none;background: rgba(0, 0, 0, 0);color:#16d3f2;text-shadow: #16d3f2 1px 0 10px;height: 30px;width:15%;border-radius:8px;text-align:center"},{"type":"hr"},</v>
       </c>
       <c r="AH100" s="2" t="str">
         <f ca="1">CONCATENATE("""",A100,"""",": """,A100,".",C100,""",")</f>
@@ -14384,7 +14592,9 @@
         <f ca="1">CONCATENATE("",A100,"",".",C100,"")</f>
         <v>92.Радужный змей</v>
       </c>
-      <c r="AL100" s="2"/>
+      <c r="AL100" s="31" t="s">
+        <v>440</v>
+      </c>
       <c r="AM100" s="2"/>
       <c r="AN100" s="17"/>
       <c r="AO100" s="2"/>
@@ -14499,7 +14709,7 @@
       </c>
       <c r="AG101" s="2" t="str">
         <f t="shared" ca="1" si="174"/>
-        <v>{"type":"h4","title":"93. Разноцветный дождь","style":"width:85%;float:left"},{"type":"input","title":"папка","name":"e93","state":"{{e93}}","pattern":"[0-9]{1,2}","style":"width:15%;text-align:center;border-radius:8px"},{"type":"hr"},</v>
+        <v>{"type":"h4","title":"93. Разноцветный дождь","style":"font-size:14px;width:85%;float:left"},{"type":"input","title":"папка","name":"e93","state":"{{e93}}","pattern":"[0-9]{1,2}","style":"background: #1c1c1c;border-color: #ffffff3d;border-style:solidborder-style: none;background: rgba(0, 0, 0, 0);color:#16d3f2;text-shadow: #16d3f2 1px 0 10px;height: 30px;width:15%;border-radius:8px;text-align:center"},{"type":"hr"},</v>
       </c>
       <c r="AH101" s="2" t="str">
         <f t="shared" ref="AH101:AH102" ca="1" si="192">CONCATENATE("""",A101,"""",": """,A101,".",C101,""",")</f>
@@ -14517,7 +14727,9 @@
         <f t="shared" ref="AK101:AK102" ca="1" si="195">CONCATENATE("",A101,"",".",C101,"")</f>
         <v>93.Разноцветный дождь</v>
       </c>
-      <c r="AL101" s="2"/>
+      <c r="AL101" s="31" t="s">
+        <v>440</v>
+      </c>
       <c r="AM101" s="2"/>
       <c r="AN101" s="17"/>
       <c r="AO101" s="2"/>
@@ -14627,7 +14839,7 @@
       </c>
       <c r="AG102" s="2" t="str">
         <f t="shared" ca="1" si="174"/>
-        <v>{"type":"h4","title":"94. Разноцветные одуванчики","style":"width:85%;float:left"},{"type":"input","title":"папка","name":"e94","state":"{{e94}}","pattern":"[0-9]{1,2}","style":"width:15%;text-align:center;border-radius:8px"},{"type":"hr"},</v>
+        <v>{"type":"h4","title":"94. Разноцветные одуванчики","style":"font-size:14px;width:85%;float:left"},{"type":"input","title":"папка","name":"e94","state":"{{e94}}","pattern":"[0-9]{1,2}","style":"background: #1c1c1c;border-color: #ffffff3d;border-style:solidborder-style: none;background: rgba(0, 0, 0, 0);color:#16d3f2;text-shadow: #16d3f2 1px 0 10px;height: 30px;width:15%;border-radius:8px;text-align:center"},{"type":"hr"},</v>
       </c>
       <c r="AH102" s="2" t="str">
         <f t="shared" ca="1" si="192"/>
@@ -14644,6 +14856,9 @@
       <c r="AK102" s="2" t="str">
         <f t="shared" ca="1" si="195"/>
         <v>94.Разноцветные одуванчики</v>
+      </c>
+      <c r="AL102" s="31" t="s">
+        <v>440</v>
       </c>
     </row>
     <row r="103" spans="1:56" ht="14.25" customHeight="1">
@@ -14741,7 +14956,7 @@
       </c>
       <c r="AG103" s="2" t="str">
         <f t="shared" ca="1" si="174"/>
-        <v>{"type":"h4","title":"95. Реки Ботсваны","style":"width:85%;float:left"},{"type":"input","title":"папка","name":"e95","state":"{{e95}}","pattern":"[0-9]{1,2}","style":"width:15%;text-align:center;border-radius:8px"},{"type":"hr"},</v>
+        <v>{"type":"h4","title":"95. Реки Ботсваны","style":"font-size:14px;width:85%;float:left"},{"type":"input","title":"папка","name":"e95","state":"{{e95}}","pattern":"[0-9]{1,2}","style":"background: #1c1c1c;border-color: #ffffff3d;border-style:solidborder-style: none;background: rgba(0, 0, 0, 0);color:#16d3f2;text-shadow: #16d3f2 1px 0 10px;height: 30px;width:15%;border-radius:8px;text-align:center"},{"type":"hr"},</v>
       </c>
       <c r="AH103" s="2" t="str">
         <f ca="1">CONCATENATE("""",A103,"""",": """,A103,".",C103,""",")</f>
@@ -14759,7 +14974,9 @@
         <f ca="1">CONCATENATE("",A103,"",".",C103,"")</f>
         <v>95.Реки Ботсваны</v>
       </c>
-      <c r="AL103" s="2"/>
+      <c r="AL103" s="31" t="s">
+        <v>440</v>
+      </c>
       <c r="AM103" s="2"/>
       <c r="AN103" s="17"/>
       <c r="AO103" s="2"/>
@@ -14874,7 +15091,7 @@
       </c>
       <c r="AG104" s="2" t="str">
         <f t="shared" ca="1" si="174"/>
-        <v>{"type":"h4","title":"96. Светлячки","style":"width:85%;float:left"},{"type":"input","title":"папка","name":"e96","state":"{{e96}}","pattern":"[0-9]{1,2}","style":"width:15%;text-align:center;border-radius:8px"},{"type":"hr"},</v>
+        <v>{"type":"h4","title":"96. Светлячки","style":"font-size:14px;width:85%;float:left"},{"type":"input","title":"папка","name":"e96","state":"{{e96}}","pattern":"[0-9]{1,2}","style":"background: #1c1c1c;border-color: #ffffff3d;border-style:solidborder-style: none;background: rgba(0, 0, 0, 0);color:#16d3f2;text-shadow: #16d3f2 1px 0 10px;height: 30px;width:15%;border-radius:8px;text-align:center"},{"type":"hr"},</v>
       </c>
       <c r="AH104" s="2" t="str">
         <f t="shared" ref="AH104:AH109" ca="1" si="209">CONCATENATE("""",A104,"""",": """,A104,".",C104,""",")</f>
@@ -14892,7 +15109,9 @@
         <f t="shared" ref="AK104:AK109" ca="1" si="212">CONCATENATE("",A104,"",".",C104,"")</f>
         <v>96.Светлячки</v>
       </c>
-      <c r="AL104" s="2"/>
+      <c r="AL104" s="31" t="s">
+        <v>440</v>
+      </c>
       <c r="AM104" s="2"/>
       <c r="AN104" s="17"/>
       <c r="AO104" s="2"/>
@@ -15007,7 +15226,7 @@
       </c>
       <c r="AG105" s="2" t="str">
         <f t="shared" ca="1" si="174"/>
-        <v>{"type":"h4","title":"97. Светлячки со шлейфом","style":"width:85%;float:left"},{"type":"input","title":"папка","name":"e97","state":"{{e97}}","pattern":"[0-9]{1,2}","style":"width:15%;text-align:center;border-radius:8px"},{"type":"hr"},</v>
+        <v>{"type":"h4","title":"97. Светлячки со шлейфом","style":"font-size:14px;width:85%;float:left"},{"type":"input","title":"папка","name":"e97","state":"{{e97}}","pattern":"[0-9]{1,2}","style":"background: #1c1c1c;border-color: #ffffff3d;border-style:solidborder-style: none;background: rgba(0, 0, 0, 0);color:#16d3f2;text-shadow: #16d3f2 1px 0 10px;height: 30px;width:15%;border-radius:8px;text-align:center"},{"type":"hr"},</v>
       </c>
       <c r="AH105" s="2" t="str">
         <f t="shared" ca="1" si="209"/>
@@ -15025,7 +15244,9 @@
         <f t="shared" ca="1" si="212"/>
         <v>97.Светлячки со шлейфом</v>
       </c>
-      <c r="AL105" s="2"/>
+      <c r="AL105" s="31" t="s">
+        <v>440</v>
+      </c>
       <c r="AM105" s="2"/>
       <c r="AN105" s="17"/>
       <c r="AO105" s="2"/>
@@ -15140,7 +15361,7 @@
       </c>
       <c r="AG106" s="2" t="str">
         <f t="shared" ca="1" si="174"/>
-        <v>{"type":"h4","title":"98. Свеча","style":"width:85%;float:left"},{"type":"input","title":"папка","name":"e98","state":"{{e98}}","pattern":"[0-9]{1,2}","style":"width:15%;text-align:center;border-radius:8px"},{"type":"hr"},</v>
+        <v>{"type":"h4","title":"98. Свеча","style":"font-size:14px;width:85%;float:left"},{"type":"input","title":"папка","name":"e98","state":"{{e98}}","pattern":"[0-9]{1,2}","style":"background: #1c1c1c;border-color: #ffffff3d;border-style:solidborder-style: none;background: rgba(0, 0, 0, 0);color:#16d3f2;text-shadow: #16d3f2 1px 0 10px;height: 30px;width:15%;border-radius:8px;text-align:center"},{"type":"hr"},</v>
       </c>
       <c r="AH106" s="2" t="str">
         <f t="shared" ca="1" si="209"/>
@@ -15158,7 +15379,9 @@
         <f t="shared" ca="1" si="212"/>
         <v>98.Свеча</v>
       </c>
-      <c r="AL106" s="2"/>
+      <c r="AL106" s="31" t="s">
+        <v>440</v>
+      </c>
       <c r="AM106" s="2"/>
       <c r="AN106" s="17"/>
       <c r="AO106" s="2"/>
@@ -15273,7 +15496,7 @@
       </c>
       <c r="AG107" s="2" t="str">
         <f t="shared" ca="1" si="174"/>
-        <v>{"type":"h4","title":"99. Северное сияние","style":"width:85%;float:left"},{"type":"input","title":"папка","name":"e99","state":"{{e99}}","pattern":"[0-9]{1,2}","style":"width:15%;text-align:center;border-radius:8px"},{"type":"hr"},</v>
+        <v>{"type":"h4","title":"99. Северное сияние","style":"font-size:14px;width:85%;float:left"},{"type":"input","title":"папка","name":"e99","state":"{{e99}}","pattern":"[0-9]{1,2}","style":"background: #1c1c1c;border-color: #ffffff3d;border-style:solidborder-style: none;background: rgba(0, 0, 0, 0);color:#16d3f2;text-shadow: #16d3f2 1px 0 10px;height: 30px;width:15%;border-radius:8px;text-align:center"},{"type":"hr"},</v>
       </c>
       <c r="AH107" s="2" t="str">
         <f t="shared" ca="1" si="209"/>
@@ -15291,7 +15514,9 @@
         <f t="shared" ca="1" si="212"/>
         <v>99.Северное сияние</v>
       </c>
-      <c r="AL107" s="2"/>
+      <c r="AL107" s="31" t="s">
+        <v>440</v>
+      </c>
       <c r="AM107" s="2"/>
       <c r="AN107" s="17"/>
       <c r="AO107" s="2"/>
@@ -15405,7 +15630,7 @@
       </c>
       <c r="AG108" s="2" t="str">
         <f t="shared" ca="1" si="174"/>
-        <v>{"type":"h4","title":"100. Серпантин","style":"width:85%;float:left"},{"type":"input","title":"папка","name":"e100","state":"{{e100}}","pattern":"[0-9]{1,2}","style":"width:15%;text-align:center;border-radius:8px"},{"type":"hr"},</v>
+        <v>{"type":"h4","title":"100. Серпантин","style":"font-size:14px;width:85%;float:left"},{"type":"input","title":"папка","name":"e100","state":"{{e100}}","pattern":"[0-9]{1,2}","style":"background: #1c1c1c;border-color: #ffffff3d;border-style:solidborder-style: none;background: rgba(0, 0, 0, 0);color:#16d3f2;text-shadow: #16d3f2 1px 0 10px;height: 30px;width:15%;border-radius:8px;text-align:center"},{"type":"hr"},</v>
       </c>
       <c r="AH108" s="2" t="str">
         <f t="shared" ca="1" si="209"/>
@@ -15422,6 +15647,9 @@
       <c r="AK108" s="2" t="str">
         <f t="shared" ca="1" si="212"/>
         <v>100.Серпантин</v>
+      </c>
+      <c r="AL108" s="31" t="s">
+        <v>440</v>
       </c>
     </row>
     <row r="109" spans="1:56">
@@ -15518,7 +15746,7 @@
       </c>
       <c r="AG109" s="2" t="str">
         <f t="shared" ca="1" si="174"/>
-        <v>{"type":"h4","title":"101. Сканер","style":"width:85%;float:left"},{"type":"input","title":"папка","name":"e101","state":"{{e101}}","pattern":"[0-9]{1,2}","style":"width:15%;text-align:center;border-radius:8px"},{"type":"hr"},</v>
+        <v>{"type":"h4","title":"101. Сканер","style":"font-size:14px;width:85%;float:left"},{"type":"input","title":"папка","name":"e101","state":"{{e101}}","pattern":"[0-9]{1,2}","style":"background: #1c1c1c;border-color: #ffffff3d;border-style:solidborder-style: none;background: rgba(0, 0, 0, 0);color:#16d3f2;text-shadow: #16d3f2 1px 0 10px;height: 30px;width:15%;border-radius:8px;text-align:center"},{"type":"hr"},</v>
       </c>
       <c r="AH109" s="2" t="str">
         <f t="shared" ca="1" si="209"/>
@@ -15535,6 +15763,9 @@
       <c r="AK109" s="2" t="str">
         <f t="shared" ca="1" si="212"/>
         <v>101.Сканер</v>
+      </c>
+      <c r="AL109" s="31" t="s">
+        <v>440</v>
       </c>
     </row>
     <row r="110" spans="1:56" ht="14.25" customHeight="1">
@@ -15632,7 +15863,7 @@
       </c>
       <c r="AG110" s="2" t="str">
         <f t="shared" ca="1" si="174"/>
-        <v>{"type":"h4","title":"102. Синусоид","style":"width:85%;float:left"},{"type":"input","title":"папка","name":"e102","state":"{{e102}}","pattern":"[0-9]{1,2}","style":"width:15%;text-align:center;border-radius:8px"},{"type":"hr"},</v>
+        <v>{"type":"h4","title":"102. Синусоид","style":"font-size:14px;width:85%;float:left"},{"type":"input","title":"папка","name":"e102","state":"{{e102}}","pattern":"[0-9]{1,2}","style":"background: #1c1c1c;border-color: #ffffff3d;border-style:solidborder-style: none;background: rgba(0, 0, 0, 0);color:#16d3f2;text-shadow: #16d3f2 1px 0 10px;height: 30px;width:15%;border-radius:8px;text-align:center"},{"type":"hr"},</v>
       </c>
       <c r="AH110" s="2" t="str">
         <f t="shared" ref="AH110:AH126" ca="1" si="224">CONCATENATE("""",A110,"""",": """,A110,".",C110,""",")</f>
@@ -15650,7 +15881,9 @@
         <f t="shared" ref="AK110:AK126" ca="1" si="227">CONCATENATE("",A110,"",".",C110,"")</f>
         <v>102.Синусоид</v>
       </c>
-      <c r="AL110" s="2"/>
+      <c r="AL110" s="31" t="s">
+        <v>440</v>
+      </c>
       <c r="AM110" s="2"/>
       <c r="AN110" s="17"/>
       <c r="AO110" s="2"/>
@@ -15765,7 +15998,7 @@
       </c>
       <c r="AG111" s="2" t="str">
         <f t="shared" ca="1" si="174"/>
-        <v>{"type":"h4","title":"103. Смена цвета","style":"width:85%;float:left"},{"type":"input","title":"папка","name":"e103","state":"{{e103}}","pattern":"[0-9]{1,2}","style":"width:15%;text-align:center;border-radius:8px"},{"type":"hr"},</v>
+        <v>{"type":"h4","title":"103. Смена цвета","style":"font-size:14px;width:85%;float:left"},{"type":"input","title":"папка","name":"e103","state":"{{e103}}","pattern":"[0-9]{1,2}","style":"background: #1c1c1c;border-color: #ffffff3d;border-style:solidborder-style: none;background: rgba(0, 0, 0, 0);color:#16d3f2;text-shadow: #16d3f2 1px 0 10px;height: 30px;width:15%;border-radius:8px;text-align:center"},{"type":"hr"},</v>
       </c>
       <c r="AH111" s="2" t="str">
         <f t="shared" ca="1" si="224"/>
@@ -15783,7 +16016,9 @@
         <f t="shared" ca="1" si="227"/>
         <v>103.Смена цвета</v>
       </c>
-      <c r="AL111" s="2"/>
+      <c r="AL111" s="31" t="s">
+        <v>440</v>
+      </c>
       <c r="AM111" s="2"/>
       <c r="AN111" s="17"/>
       <c r="AO111" s="2"/>
@@ -15898,7 +16133,7 @@
       </c>
       <c r="AG112" s="2" t="str">
         <f t="shared" ca="1" si="174"/>
-        <v>{"type":"h4","title":"104. Снегопад","style":"width:85%;float:left"},{"type":"input","title":"папка","name":"e104","state":"{{e104}}","pattern":"[0-9]{1,2}","style":"width:15%;text-align:center;border-radius:8px"},{"type":"hr"},</v>
+        <v>{"type":"h4","title":"104. Снегопад","style":"font-size:14px;width:85%;float:left"},{"type":"input","title":"папка","name":"e104","state":"{{e104}}","pattern":"[0-9]{1,2}","style":"background: #1c1c1c;border-color: #ffffff3d;border-style:solidborder-style: none;background: rgba(0, 0, 0, 0);color:#16d3f2;text-shadow: #16d3f2 1px 0 10px;height: 30px;width:15%;border-radius:8px;text-align:center"},{"type":"hr"},</v>
       </c>
       <c r="AH112" s="2" t="str">
         <f t="shared" ca="1" si="224"/>
@@ -15916,7 +16151,9 @@
         <f t="shared" ca="1" si="227"/>
         <v>104.Снегопад</v>
       </c>
-      <c r="AL112" s="2"/>
+      <c r="AL112" s="31" t="s">
+        <v>440</v>
+      </c>
       <c r="AM112" s="2"/>
       <c r="AN112" s="17"/>
       <c r="AO112" s="2"/>
@@ -16027,7 +16264,7 @@
       </c>
       <c r="AG113" s="2" t="str">
         <f t="shared" ca="1" si="174"/>
-        <v>{"type":"h4","title":"105. Спектрум","style":"width:85%;float:left"},{"type":"input","title":"папка","name":"e105","state":"{{e105}}","pattern":"[0-9]{1,2}","style":"width:15%;text-align:center;border-radius:8px"},{"type":"hr"},</v>
+        <v>{"type":"h4","title":"105. Спектрум","style":"font-size:14px;width:85%;float:left"},{"type":"input","title":"папка","name":"e105","state":"{{e105}}","pattern":"[0-9]{1,2}","style":"background: #1c1c1c;border-color: #ffffff3d;border-style:solidborder-style: none;background: rgba(0, 0, 0, 0);color:#16d3f2;text-shadow: #16d3f2 1px 0 10px;height: 30px;width:15%;border-radius:8px;text-align:center"},{"type":"hr"},</v>
       </c>
       <c r="AH113" s="2" t="str">
         <f t="shared" ca="1" si="224"/>
@@ -16045,7 +16282,9 @@
         <f t="shared" ca="1" si="227"/>
         <v>105.Спектрум</v>
       </c>
-      <c r="AL113" s="2"/>
+      <c r="AL113" s="31" t="s">
+        <v>440</v>
+      </c>
       <c r="AM113" s="2"/>
       <c r="AN113" s="17"/>
       <c r="AO113" s="2"/>
@@ -16160,7 +16399,7 @@
       </c>
       <c r="AG114" s="2" t="str">
         <f t="shared" ca="1" si="174"/>
-        <v>{"type":"h4","title":"106. Спирали","style":"width:85%;float:left"},{"type":"input","title":"папка","name":"e106","state":"{{e106}}","pattern":"[0-9]{1,2}","style":"width:15%;text-align:center;border-radius:8px"},{"type":"hr"},</v>
+        <v>{"type":"h4","title":"106. Спирали","style":"font-size:14px;width:85%;float:left"},{"type":"input","title":"папка","name":"e106","state":"{{e106}}","pattern":"[0-9]{1,2}","style":"background: #1c1c1c;border-color: #ffffff3d;border-style:solidborder-style: none;background: rgba(0, 0, 0, 0);color:#16d3f2;text-shadow: #16d3f2 1px 0 10px;height: 30px;width:15%;border-radius:8px;text-align:center"},{"type":"hr"},</v>
       </c>
       <c r="AH114" s="2" t="str">
         <f t="shared" ca="1" si="224"/>
@@ -16178,7 +16417,9 @@
         <f t="shared" ca="1" si="227"/>
         <v>106.Спирали</v>
       </c>
-      <c r="AL114" s="2"/>
+      <c r="AL114" s="31" t="s">
+        <v>440</v>
+      </c>
       <c r="AM114" s="2"/>
       <c r="AN114" s="17"/>
       <c r="AO114" s="2"/>
@@ -16293,7 +16534,7 @@
       </c>
       <c r="AG115" s="2" t="str">
         <f t="shared" ca="1" si="174"/>
-        <v>{"type":"h4","title":"107. Стая","style":"width:85%;float:left"},{"type":"input","title":"папка","name":"e107","state":"{{e107}}","pattern":"[0-9]{1,2}","style":"width:15%;text-align:center;border-radius:8px"},{"type":"hr"},</v>
+        <v>{"type":"h4","title":"107. Стая","style":"font-size:14px;width:85%;float:left"},{"type":"input","title":"папка","name":"e107","state":"{{e107}}","pattern":"[0-9]{1,2}","style":"background: #1c1c1c;border-color: #ffffff3d;border-style:solidborder-style: none;background: rgba(0, 0, 0, 0);color:#16d3f2;text-shadow: #16d3f2 1px 0 10px;height: 30px;width:15%;border-radius:8px;text-align:center"},{"type":"hr"},</v>
       </c>
       <c r="AH115" s="2" t="str">
         <f t="shared" ca="1" si="224"/>
@@ -16311,7 +16552,9 @@
         <f t="shared" ca="1" si="227"/>
         <v>107.Стая</v>
       </c>
-      <c r="AL115" s="2"/>
+      <c r="AL115" s="31" t="s">
+        <v>440</v>
+      </c>
       <c r="AM115" s="2"/>
       <c r="AN115" s="17"/>
       <c r="AO115" s="2"/>
@@ -16422,7 +16665,7 @@
       </c>
       <c r="AG116" s="2" t="str">
         <f t="shared" ca="1" si="174"/>
-        <v>{"type":"h4","title":"108. Стая и хищник","style":"width:85%;float:left"},{"type":"input","title":"папка","name":"e108","state":"{{e108}}","pattern":"[0-9]{1,2}","style":"width:15%;text-align:center;border-radius:8px"},{"type":"hr"},</v>
+        <v>{"type":"h4","title":"108. Стая и хищник","style":"font-size:14px;width:85%;float:left"},{"type":"input","title":"папка","name":"e108","state":"{{e108}}","pattern":"[0-9]{1,2}","style":"background: #1c1c1c;border-color: #ffffff3d;border-style:solidborder-style: none;background: rgba(0, 0, 0, 0);color:#16d3f2;text-shadow: #16d3f2 1px 0 10px;height: 30px;width:15%;border-radius:8px;text-align:center"},{"type":"hr"},</v>
       </c>
       <c r="AH116" s="2" t="str">
         <f t="shared" ca="1" si="224"/>
@@ -16440,7 +16683,9 @@
         <f t="shared" ca="1" si="227"/>
         <v>108.Стая и хищник</v>
       </c>
-      <c r="AL116" s="2"/>
+      <c r="AL116" s="31" t="s">
+        <v>440</v>
+      </c>
       <c r="AM116" s="2"/>
       <c r="AN116" s="17"/>
       <c r="AO116" s="2"/>
@@ -16555,7 +16800,7 @@
       </c>
       <c r="AG117" s="2" t="str">
         <f t="shared" ca="1" si="174"/>
-        <v>{"type":"h4","title":"109. Стрелки","style":"width:85%;float:left"},{"type":"input","title":"папка","name":"e109","state":"{{e109}}","pattern":"[0-9]{1,2}","style":"width:15%;text-align:center;border-radius:8px"},{"type":"hr"},</v>
+        <v>{"type":"h4","title":"109. Стрелки","style":"font-size:14px;width:85%;float:left"},{"type":"input","title":"папка","name":"e109","state":"{{e109}}","pattern":"[0-9]{1,2}","style":"background: #1c1c1c;border-color: #ffffff3d;border-style:solidborder-style: none;background: rgba(0, 0, 0, 0);color:#16d3f2;text-shadow: #16d3f2 1px 0 10px;height: 30px;width:15%;border-radius:8px;text-align:center"},{"type":"hr"},</v>
       </c>
       <c r="AH117" s="2" t="str">
         <f t="shared" ca="1" si="224"/>
@@ -16573,7 +16818,9 @@
         <f t="shared" ca="1" si="227"/>
         <v>109.Стрелки</v>
       </c>
-      <c r="AL117" s="2"/>
+      <c r="AL117" s="31" t="s">
+        <v>440</v>
+      </c>
       <c r="AM117" s="2"/>
       <c r="AN117" s="17"/>
       <c r="AO117" s="2"/>
@@ -16688,7 +16935,7 @@
       </c>
       <c r="AG118" s="2" t="str">
         <f t="shared" ca="1" si="174"/>
-        <v>{"type":"h4","title":"110. Строб.Хаос.Дифузия","style":"width:85%;float:left"},{"type":"input","title":"папка","name":"e110","state":"{{e110}}","pattern":"[0-9]{1,2}","style":"width:15%;text-align:center;border-radius:8px"},{"type":"hr"},</v>
+        <v>{"type":"h4","title":"110. Строб.Хаос.Дифузия","style":"font-size:14px;width:85%;float:left"},{"type":"input","title":"папка","name":"e110","state":"{{e110}}","pattern":"[0-9]{1,2}","style":"background: #1c1c1c;border-color: #ffffff3d;border-style:solidborder-style: none;background: rgba(0, 0, 0, 0);color:#16d3f2;text-shadow: #16d3f2 1px 0 10px;height: 30px;width:15%;border-radius:8px;text-align:center"},{"type":"hr"},</v>
       </c>
       <c r="AH118" s="2" t="str">
         <f t="shared" ca="1" si="224"/>
@@ -16706,7 +16953,9 @@
         <f t="shared" ca="1" si="227"/>
         <v>110.Строб.Хаос.Дифузия</v>
       </c>
-      <c r="AL118" s="2"/>
+      <c r="AL118" s="31" t="s">
+        <v>440</v>
+      </c>
       <c r="AM118" s="2"/>
       <c r="AN118" s="17"/>
       <c r="AO118" s="2"/>
@@ -16821,7 +17070,7 @@
       </c>
       <c r="AG119" s="2" t="str">
         <f t="shared" ca="1" si="174"/>
-        <v>{"type":"h4","title":"111. Тени","style":"width:85%;float:left"},{"type":"input","title":"папка","name":"e111","state":"{{e111}}","pattern":"[0-9]{1,2}","style":"width:15%;text-align:center;border-radius:8px"},{"type":"hr"},</v>
+        <v>{"type":"h4","title":"111. Тени","style":"font-size:14px;width:85%;float:left"},{"type":"input","title":"папка","name":"e111","state":"{{e111}}","pattern":"[0-9]{1,2}","style":"background: #1c1c1c;border-color: #ffffff3d;border-style:solidborder-style: none;background: rgba(0, 0, 0, 0);color:#16d3f2;text-shadow: #16d3f2 1px 0 10px;height: 30px;width:15%;border-radius:8px;text-align:center"},{"type":"hr"},</v>
       </c>
       <c r="AH119" s="2" t="str">
         <f t="shared" ca="1" si="224"/>
@@ -16839,7 +17088,9 @@
         <f t="shared" ca="1" si="227"/>
         <v>111.Тени</v>
       </c>
-      <c r="AL119" s="2"/>
+      <c r="AL119" s="31" t="s">
+        <v>440</v>
+      </c>
       <c r="AM119" s="2"/>
       <c r="AN119" s="17"/>
       <c r="AO119" s="2"/>
@@ -16954,7 +17205,7 @@
       </c>
       <c r="AG120" s="2" t="str">
         <f t="shared" ca="1" si="174"/>
-        <v>{"type":"h4","title":"112. Тихий океан","style":"width:85%;float:left"},{"type":"input","title":"папка","name":"e112","state":"{{e112}}","pattern":"[0-9]{1,2}","style":"width:15%;text-align:center;border-radius:8px"},{"type":"hr"},</v>
+        <v>{"type":"h4","title":"112. Тихий океан","style":"font-size:14px;width:85%;float:left"},{"type":"input","title":"папка","name":"e112","state":"{{e112}}","pattern":"[0-9]{1,2}","style":"background: #1c1c1c;border-color: #ffffff3d;border-style:solidborder-style: none;background: rgba(0, 0, 0, 0);color:#16d3f2;text-shadow: #16d3f2 1px 0 10px;height: 30px;width:15%;border-radius:8px;text-align:center"},{"type":"hr"},</v>
       </c>
       <c r="AH120" s="2" t="str">
         <f t="shared" ca="1" si="224"/>
@@ -16972,7 +17223,9 @@
         <f t="shared" ca="1" si="227"/>
         <v>112.Тихий океан</v>
       </c>
-      <c r="AL120" s="2"/>
+      <c r="AL120" s="31" t="s">
+        <v>440</v>
+      </c>
       <c r="AM120" s="2"/>
       <c r="AN120" s="17"/>
       <c r="AO120" s="2"/>
@@ -17086,7 +17339,7 @@
       </c>
       <c r="AG121" s="2" t="str">
         <f t="shared" ca="1" si="174"/>
-        <v>{"type":"h4","title":"113. Торнадо","style":"width:85%;float:left"},{"type":"input","title":"папка","name":"e113","state":"{{e113}}","pattern":"[0-9]{1,2}","style":"width:15%;text-align:center;border-radius:8px"},{"type":"hr"},</v>
+        <v>{"type":"h4","title":"113. Торнадо","style":"font-size:14px;width:85%;float:left"},{"type":"input","title":"папка","name":"e113","state":"{{e113}}","pattern":"[0-9]{1,2}","style":"background: #1c1c1c;border-color: #ffffff3d;border-style:solidborder-style: none;background: rgba(0, 0, 0, 0);color:#16d3f2;text-shadow: #16d3f2 1px 0 10px;height: 30px;width:15%;border-radius:8px;text-align:center"},{"type":"hr"},</v>
       </c>
       <c r="AH121" s="2" t="str">
         <f t="shared" ca="1" si="224"/>
@@ -17103,6 +17356,9 @@
       <c r="AK121" s="2" t="str">
         <f t="shared" ca="1" si="227"/>
         <v>113.Торнадо</v>
+      </c>
+      <c r="AL121" s="31" t="s">
+        <v>440</v>
       </c>
     </row>
     <row r="122" spans="1:56" ht="14.25" customHeight="1">
@@ -17200,7 +17456,7 @@
       </c>
       <c r="AG122" s="2" t="str">
         <f t="shared" ca="1" si="174"/>
-        <v>{"type":"h4","title":"114. Tyчкa в банке","style":"width:85%;float:left"},{"type":"input","title":"папка","name":"e114","state":"{{e114}}","pattern":"[0-9]{1,2}","style":"width:15%;text-align:center;border-radius:8px"},{"type":"hr"},</v>
+        <v>{"type":"h4","title":"114. Tyчкa в банке","style":"font-size:14px;width:85%;float:left"},{"type":"input","title":"папка","name":"e114","state":"{{e114}}","pattern":"[0-9]{1,2}","style":"background: #1c1c1c;border-color: #ffffff3d;border-style:solidborder-style: none;background: rgba(0, 0, 0, 0);color:#16d3f2;text-shadow: #16d3f2 1px 0 10px;height: 30px;width:15%;border-radius:8px;text-align:center"},{"type":"hr"},</v>
       </c>
       <c r="AH122" s="2" t="str">
         <f t="shared" ca="1" si="224"/>
@@ -17218,7 +17474,9 @@
         <f t="shared" ca="1" si="227"/>
         <v>114.Tyчкa в банке</v>
       </c>
-      <c r="AL122" s="2"/>
+      <c r="AL122" s="31" t="s">
+        <v>440</v>
+      </c>
       <c r="AM122" s="2"/>
       <c r="AN122" s="17"/>
       <c r="AO122" s="2"/>
@@ -17333,7 +17591,7 @@
       </c>
       <c r="AG123" s="2" t="str">
         <f t="shared" ca="1" si="174"/>
-        <v>{"type":"h4","title":"115. Фейерверк","style":"width:85%;float:left"},{"type":"input","title":"папка","name":"e115","state":"{{e115}}","pattern":"[0-9]{1,2}","style":"width:15%;text-align:center;border-radius:8px"},{"type":"hr"},</v>
+        <v>{"type":"h4","title":"115. Фейерверк","style":"font-size:14px;width:85%;float:left"},{"type":"input","title":"папка","name":"e115","state":"{{e115}}","pattern":"[0-9]{1,2}","style":"background: #1c1c1c;border-color: #ffffff3d;border-style:solidborder-style: none;background: rgba(0, 0, 0, 0);color:#16d3f2;text-shadow: #16d3f2 1px 0 10px;height: 30px;width:15%;border-radius:8px;text-align:center"},{"type":"hr"},</v>
       </c>
       <c r="AH123" s="2" t="str">
         <f t="shared" ca="1" si="224"/>
@@ -17351,7 +17609,9 @@
         <f t="shared" ca="1" si="227"/>
         <v>115.Фейерверк</v>
       </c>
-      <c r="AL123" s="2"/>
+      <c r="AL123" s="31" t="s">
+        <v>440</v>
+      </c>
       <c r="AM123" s="2"/>
       <c r="AN123" s="17"/>
       <c r="AO123" s="2"/>
@@ -17466,7 +17726,7 @@
       </c>
       <c r="AG124" s="2" t="str">
         <f t="shared" ca="1" si="174"/>
-        <v>{"type":"h4","title":"116. Фейерверк 2","style":"width:85%;float:left"},{"type":"input","title":"папка","name":"e116","state":"{{e116}}","pattern":"[0-9]{1,2}","style":"width:15%;text-align:center;border-radius:8px"},{"type":"hr"},</v>
+        <v>{"type":"h4","title":"116. Фейерверк 2","style":"font-size:14px;width:85%;float:left"},{"type":"input","title":"папка","name":"e116","state":"{{e116}}","pattern":"[0-9]{1,2}","style":"background: #1c1c1c;border-color: #ffffff3d;border-style:solidborder-style: none;background: rgba(0, 0, 0, 0);color:#16d3f2;text-shadow: #16d3f2 1px 0 10px;height: 30px;width:15%;border-radius:8px;text-align:center"},{"type":"hr"},</v>
       </c>
       <c r="AH124" s="2" t="str">
         <f t="shared" ca="1" si="224"/>
@@ -17484,7 +17744,9 @@
         <f t="shared" ca="1" si="227"/>
         <v>116.Фейерверк 2</v>
       </c>
-      <c r="AL124" s="2"/>
+      <c r="AL124" s="31" t="s">
+        <v>440</v>
+      </c>
       <c r="AM124" s="2"/>
       <c r="AN124" s="17"/>
       <c r="AO124" s="2"/>
@@ -17599,7 +17861,7 @@
       </c>
       <c r="AG125" s="2" t="str">
         <f t="shared" ca="1" si="174"/>
-        <v>{"type":"h4","title":"117. Фея","style":"width:85%;float:left"},{"type":"input","title":"папка","name":"e117","state":"{{e117}}","pattern":"[0-9]{1,2}","style":"width:15%;text-align:center;border-radius:8px"},{"type":"hr"},</v>
+        <v>{"type":"h4","title":"117. Фея","style":"font-size:14px;width:85%;float:left"},{"type":"input","title":"папка","name":"e117","state":"{{e117}}","pattern":"[0-9]{1,2}","style":"background: #1c1c1c;border-color: #ffffff3d;border-style:solidborder-style: none;background: rgba(0, 0, 0, 0);color:#16d3f2;text-shadow: #16d3f2 1px 0 10px;height: 30px;width:15%;border-radius:8px;text-align:center"},{"type":"hr"},</v>
       </c>
       <c r="AH125" s="2" t="str">
         <f t="shared" ca="1" si="224"/>
@@ -17617,7 +17879,9 @@
         <f t="shared" ca="1" si="227"/>
         <v>117.Фея</v>
       </c>
-      <c r="AL125" s="2"/>
+      <c r="AL125" s="31" t="s">
+        <v>440</v>
+      </c>
       <c r="AM125" s="2"/>
       <c r="AN125" s="17"/>
       <c r="AO125" s="2"/>
@@ -17731,7 +17995,7 @@
       </c>
       <c r="AG126" s="2" t="str">
         <f t="shared" ca="1" si="174"/>
-        <v>{"type":"h4","title":"118. Фонтан","style":"width:85%;float:left"},{"type":"input","title":"папка","name":"e118","state":"{{e118}}","pattern":"[0-9]{1,2}","style":"width:15%;text-align:center;border-radius:8px"},{"type":"hr"},</v>
+        <v>{"type":"h4","title":"118. Фонтан","style":"font-size:14px;width:85%;float:left"},{"type":"input","title":"папка","name":"e118","state":"{{e118}}","pattern":"[0-9]{1,2}","style":"background: #1c1c1c;border-color: #ffffff3d;border-style:solidborder-style: none;background: rgba(0, 0, 0, 0);color:#16d3f2;text-shadow: #16d3f2 1px 0 10px;height: 30px;width:15%;border-radius:8px;text-align:center"},{"type":"hr"},</v>
       </c>
       <c r="AH126" s="2" t="str">
         <f t="shared" ca="1" si="224"/>
@@ -17748,6 +18012,9 @@
       <c r="AK126" s="2" t="str">
         <f t="shared" ca="1" si="227"/>
         <v>118.Фонтан</v>
+      </c>
+      <c r="AL126" s="31" t="s">
+        <v>440</v>
       </c>
     </row>
     <row r="127" spans="1:56" ht="14.25" customHeight="1">
@@ -17845,7 +18112,7 @@
       </c>
       <c r="AG127" s="2" t="str">
         <f t="shared" ca="1" si="174"/>
-        <v>{"type":"h4","title":"119. Цвет","style":"width:85%;float:left"},{"type":"input","title":"папка","name":"e119","state":"{{e119}}","pattern":"[0-9]{1,2}","style":"width:15%;text-align:center;border-radius:8px"},{"type":"hr"},</v>
+        <v>{"type":"h4","title":"119. Цвет","style":"font-size:14px;width:85%;float:left"},{"type":"input","title":"папка","name":"e119","state":"{{e119}}","pattern":"[0-9]{1,2}","style":"background: #1c1c1c;border-color: #ffffff3d;border-style:solidborder-style: none;background: rgba(0, 0, 0, 0);color:#16d3f2;text-shadow: #16d3f2 1px 0 10px;height: 30px;width:15%;border-radius:8px;text-align:center"},{"type":"hr"},</v>
       </c>
       <c r="AH127" s="2" t="str">
         <f ca="1">CONCATENATE("""",A127,"""",": """,A127,".",C127,""",")</f>
@@ -17863,7 +18130,9 @@
         <f t="shared" ref="AK127:AK135" ca="1" si="238">CONCATENATE("",A127,"",".",C127,"")</f>
         <v>119.Цвет</v>
       </c>
-      <c r="AL127" s="2"/>
+      <c r="AL127" s="31" t="s">
+        <v>440</v>
+      </c>
       <c r="AM127" s="2"/>
       <c r="AN127" s="17"/>
       <c r="AO127" s="2"/>
@@ -17977,7 +18246,7 @@
       </c>
       <c r="AG128" s="2" t="str">
         <f t="shared" ca="1" si="174"/>
-        <v>{"type":"h4","title":"120. Цветной Питон","style":"width:85%;float:left"},{"type":"input","title":"папка","name":"e120","state":"{{e120}}","pattern":"[0-9]{1,2}","style":"width:15%;text-align:center;border-radius:8px"},{"type":"hr"},</v>
+        <v>{"type":"h4","title":"120. Цветной Питон","style":"font-size:14px;width:85%;float:left"},{"type":"input","title":"папка","name":"e120","state":"{{e120}}","pattern":"[0-9]{1,2}","style":"background: #1c1c1c;border-color: #ffffff3d;border-style:solidborder-style: none;background: rgba(0, 0, 0, 0);color:#16d3f2;text-shadow: #16d3f2 1px 0 10px;height: 30px;width:15%;border-radius:8px;text-align:center"},{"type":"hr"},</v>
       </c>
       <c r="AH128" s="2" t="str">
         <f t="shared" ref="AH128:AH132" ca="1" si="246">CONCATENATE("""",A128,"""",": """,A128,".",C128,""",")</f>
@@ -17994,6 +18263,9 @@
       <c r="AK128" s="2" t="str">
         <f t="shared" ca="1" si="238"/>
         <v>120.Цветной Питон</v>
+      </c>
+      <c r="AL128" s="31" t="s">
+        <v>440</v>
       </c>
     </row>
     <row r="129" spans="1:56" ht="14.25" customHeight="1">
@@ -18091,7 +18363,7 @@
       </c>
       <c r="AG129" s="2" t="str">
         <f t="shared" ca="1" si="174"/>
-        <v>{"type":"h4","title":"121. Цветные драже","style":"width:85%;float:left"},{"type":"input","title":"папка","name":"e121","state":"{{e121}}","pattern":"[0-9]{1,2}","style":"width:15%;text-align:center;border-radius:8px"},{"type":"hr"},</v>
+        <v>{"type":"h4","title":"121. Цветные драже","style":"font-size:14px;width:85%;float:left"},{"type":"input","title":"папка","name":"e121","state":"{{e121}}","pattern":"[0-9]{1,2}","style":"background: #1c1c1c;border-color: #ffffff3d;border-style:solidborder-style: none;background: rgba(0, 0, 0, 0);color:#16d3f2;text-shadow: #16d3f2 1px 0 10px;height: 30px;width:15%;border-radius:8px;text-align:center"},{"type":"hr"},</v>
       </c>
       <c r="AH129" s="2" t="str">
         <f t="shared" ca="1" si="246"/>
@@ -18109,7 +18381,9 @@
         <f t="shared" ca="1" si="238"/>
         <v>121.Цветные драже</v>
       </c>
-      <c r="AL129" s="2"/>
+      <c r="AL129" s="31" t="s">
+        <v>440</v>
+      </c>
       <c r="AM129" s="2"/>
       <c r="AN129" s="17"/>
       <c r="AO129" s="2"/>
@@ -18224,7 +18498,7 @@
       </c>
       <c r="AG130" s="2" t="str">
         <f t="shared" ca="1" si="174"/>
-        <v>{"type":"h4","title":"122. Цветные кудри","style":"width:85%;float:left"},{"type":"input","title":"папка","name":"e122","state":"{{e122}}","pattern":"[0-9]{1,2}","style":"width:15%;text-align:center;border-radius:8px"},{"type":"hr"},</v>
+        <v>{"type":"h4","title":"122. Цветные кудри","style":"font-size:14px;width:85%;float:left"},{"type":"input","title":"папка","name":"e122","state":"{{e122}}","pattern":"[0-9]{1,2}","style":"background: #1c1c1c;border-color: #ffffff3d;border-style:solidborder-style: none;background: rgba(0, 0, 0, 0);color:#16d3f2;text-shadow: #16d3f2 1px 0 10px;height: 30px;width:15%;border-radius:8px;text-align:center"},{"type":"hr"},</v>
       </c>
       <c r="AH130" s="2" t="str">
         <f t="shared" ca="1" si="246"/>
@@ -18242,7 +18516,9 @@
         <f t="shared" ca="1" si="238"/>
         <v>122.Цветные кудри</v>
       </c>
-      <c r="AL130" s="2"/>
+      <c r="AL130" s="31" t="s">
+        <v>440</v>
+      </c>
       <c r="AM130" s="2"/>
       <c r="AN130" s="17"/>
       <c r="AO130" s="2"/>
@@ -18357,7 +18633,7 @@
       </c>
       <c r="AG131" s="2" t="str">
         <f t="shared" ca="1" si="174"/>
-        <v>{"type":"h4","title":"123. Цветок лотоса","style":"width:85%;float:left"},{"type":"input","title":"папка","name":"e123","state":"{{e123}}","pattern":"[0-9]{1,2}","style":"width:15%;text-align:center;border-radius:8px"},{"type":"hr"},</v>
+        <v>{"type":"h4","title":"123. Цветок лотоса","style":"font-size:14px;width:85%;float:left"},{"type":"input","title":"папка","name":"e123","state":"{{e123}}","pattern":"[0-9]{1,2}","style":"background: #1c1c1c;border-color: #ffffff3d;border-style:solidborder-style: none;background: rgba(0, 0, 0, 0);color:#16d3f2;text-shadow: #16d3f2 1px 0 10px;height: 30px;width:15%;border-radius:8px;text-align:center"},{"type":"hr"},</v>
       </c>
       <c r="AH131" s="2" t="str">
         <f t="shared" ca="1" si="246"/>
@@ -18375,7 +18651,9 @@
         <f t="shared" ca="1" si="238"/>
         <v>123.Цветок лотоса</v>
       </c>
-      <c r="AL131" s="2"/>
+      <c r="AL131" s="31" t="s">
+        <v>440</v>
+      </c>
       <c r="AM131" s="2"/>
       <c r="AN131" s="17"/>
       <c r="AO131" s="2"/>
@@ -18489,7 +18767,7 @@
       </c>
       <c r="AG132" s="2" t="str">
         <f t="shared" ca="1" si="174"/>
-        <v>{"type":"h4","title":"124. Цифровая турбулентность","style":"width:85%;float:left"},{"type":"input","title":"папка","name":"e124","state":"{{e124}}","pattern":"[0-9]{1,2}","style":"width:15%;text-align:center;border-radius:8px"},{"type":"hr"},</v>
+        <v>{"type":"h4","title":"124. Цифровая турбулентность","style":"font-size:14px;width:85%;float:left"},{"type":"input","title":"папка","name":"e124","state":"{{e124}}","pattern":"[0-9]{1,2}","style":"background: #1c1c1c;border-color: #ffffff3d;border-style:solidborder-style: none;background: rgba(0, 0, 0, 0);color:#16d3f2;text-shadow: #16d3f2 1px 0 10px;height: 30px;width:15%;border-radius:8px;text-align:center"},{"type":"hr"},</v>
       </c>
       <c r="AH132" s="2" t="str">
         <f t="shared" ca="1" si="246"/>
@@ -18506,6 +18784,9 @@
       <c r="AK132" s="2" t="str">
         <f t="shared" ca="1" si="238"/>
         <v>124.Цифровая турбулентность</v>
+      </c>
+      <c r="AL132" s="31" t="s">
+        <v>440</v>
       </c>
     </row>
     <row r="133" spans="1:56" ht="14.25" customHeight="1">
@@ -18603,7 +18884,7 @@
       </c>
       <c r="AG133" s="2" t="str">
         <f t="shared" ca="1" si="174"/>
-        <v>{"type":"h4","title":"125. Шapы","style":"width:85%;float:left"},{"type":"input","title":"папка","name":"e125","state":"{{e125}}","pattern":"[0-9]{1,2}","style":"width:15%;text-align:center;border-radius:8px"},{"type":"hr"},</v>
+        <v>{"type":"h4","title":"125. Шapы","style":"font-size:14px;width:85%;float:left"},{"type":"input","title":"папка","name":"e125","state":"{{e125}}","pattern":"[0-9]{1,2}","style":"background: #1c1c1c;border-color: #ffffff3d;border-style:solidborder-style: none;background: rgba(0, 0, 0, 0);color:#16d3f2;text-shadow: #16d3f2 1px 0 10px;height: 30px;width:15%;border-radius:8px;text-align:center"},{"type":"hr"},</v>
       </c>
       <c r="AH133" s="2" t="str">
         <f ca="1">CONCATENATE("""",A133,"""",": """,A133,".",C133,""",")</f>
@@ -18621,7 +18902,9 @@
         <f t="shared" ca="1" si="238"/>
         <v>125.Шapы</v>
       </c>
-      <c r="AL133" s="2"/>
+      <c r="AL133" s="31" t="s">
+        <v>440</v>
+      </c>
       <c r="AM133" s="2"/>
       <c r="AN133" s="17"/>
       <c r="AO133" s="2"/>
@@ -18736,7 +19019,7 @@
       </c>
       <c r="AG134" s="2" t="str">
         <f t="shared" ca="1" si="174"/>
-        <v>{"type":"h4","title":"126. Nexus","style":"width:85%;float:left"},{"type":"input","title":"папка","name":"e126","state":"{{e126}}","pattern":"[0-9]{1,2}","style":"width:15%;text-align:center;border-radius:8px"},{"type":"hr"},</v>
+        <v>{"type":"h4","title":"126. Nexus","style":"font-size:14px;width:85%;float:left"},{"type":"input","title":"папка","name":"e126","state":"{{e126}}","pattern":"[0-9]{1,2}","style":"background: #1c1c1c;border-color: #ffffff3d;border-style:solidborder-style: none;background: rgba(0, 0, 0, 0);color:#16d3f2;text-shadow: #16d3f2 1px 0 10px;height: 30px;width:15%;border-radius:8px;text-align:center"},{"type":"hr"},</v>
       </c>
       <c r="AH134" s="2" t="str">
         <f ca="1">CONCATENATE("""",A134,"""",": """,A134,".",C134,""",")</f>
@@ -18754,7 +19037,9 @@
         <f t="shared" ca="1" si="238"/>
         <v>126.Nexus</v>
       </c>
-      <c r="AL134" s="2"/>
+      <c r="AL134" s="31" t="s">
+        <v>440</v>
+      </c>
       <c r="AM134" s="2"/>
       <c r="AN134" s="17"/>
       <c r="AO134" s="2"/>
@@ -18869,7 +19154,7 @@
       </c>
       <c r="AG135" s="2" t="str">
         <f t="shared" ca="1" si="174"/>
-        <v>{"type":"h4","title":"127. Часы","style":"width:85%;float:left"},{"type":"input","title":"папка","name":"e127","state":"{{e127}}","pattern":"[0-9]{1,2}","style":"width:15%;text-align:center;border-radius:8px"},{"type":"hr"},</v>
+        <v>{"type":"h4","title":"127. Часы","style":"font-size:14px;width:85%;float:left"},{"type":"input","title":"папка","name":"e127","state":"{{e127}}","pattern":"[0-9]{1,2}","style":"background: #1c1c1c;border-color: #ffffff3d;border-style:solidborder-style: none;background: rgba(0, 0, 0, 0);color:#16d3f2;text-shadow: #16d3f2 1px 0 10px;height: 30px;width:15%;border-radius:8px;text-align:center"},{"type":"hr"},</v>
       </c>
       <c r="AH135" s="2" t="str">
         <f ca="1">CONCATENATE("""",A135,"""",": """,A135,".",C135,"""")</f>
@@ -18887,7 +19172,9 @@
         <f t="shared" ca="1" si="238"/>
         <v>127.Часы</v>
       </c>
-      <c r="AL135" s="2"/>
+      <c r="AL135" s="31" t="s">
+        <v>440</v>
+      </c>
       <c r="AM135" s="2"/>
       <c r="AN135" s="17"/>
       <c r="AO135" s="2"/>
@@ -18925,7 +19212,6 @@
       <c r="AI136" s="16"/>
       <c r="AJ136" s="2"/>
       <c r="AK136" s="2"/>
-      <c r="AL136" s="2"/>
       <c r="AM136" s="2"/>
       <c r="AN136" s="17"/>
       <c r="AO136" s="2"/>
@@ -18969,6 +19255,7 @@
       <c r="AE137" s="4"/>
       <c r="AI137" s="4"/>
       <c r="AJ137" s="4"/>
+      <c r="AL137" s="2"/>
       <c r="AM137" s="4"/>
       <c r="AN137" s="17"/>
       <c r="AO137" s="4"/>
@@ -18986,6 +19273,33 @@
       <c r="BC137" s="18"/>
       <c r="BD137" s="18"/>
     </row>
+    <row r="139" spans="1:56">
+      <c r="AL139" s="2"/>
+    </row>
+    <row r="141" spans="1:56">
+      <c r="AL141" s="2"/>
+    </row>
+    <row r="142" spans="1:56">
+      <c r="AL142" s="2"/>
+    </row>
+    <row r="144" spans="1:56">
+      <c r="AL144" s="2"/>
+    </row>
+    <row r="146" spans="38:38">
+      <c r="AL146" s="2"/>
+    </row>
+    <row r="148" spans="38:38">
+      <c r="AL148" s="2"/>
+    </row>
+    <row r="150" spans="38:38">
+      <c r="AL150" s="2"/>
+    </row>
+    <row r="151" spans="38:38">
+      <c r="AL151" s="2"/>
+    </row>
+    <row r="153" spans="38:38">
+      <c r="AL153" s="2"/>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/FieryLedLamp/Таблица эффектов.xlsx
+++ b/FieryLedLamp/Таблица эффектов.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="20827"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7410C05A-469B-468E-AAC6-EE9F20DFE27E}" xr6:coauthVersionLast="37" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{54387BB5-B7FE-419D-8BE0-79397EB9D236}" xr6:coauthVersionLast="37" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11310" tabRatio="168" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -5356,7 +5356,7 @@
         <v>195</v>
       </c>
       <c r="J28" s="40">
-        <v>70</v>
+        <v>30</v>
       </c>
       <c r="L28" s="40">
         <v>99</v>
@@ -5405,7 +5405,7 @@
       </c>
       <c r="Z28" s="2" t="str">
         <f t="shared" si="43"/>
-        <v xml:space="preserve">  {  30, 195,  70}, // Завиток</v>
+        <v xml:space="preserve">  {  30, 195,  30}, // Завиток</v>
       </c>
       <c r="AA28" s="2" t="str">
         <f t="shared" ca="1" si="53"/>
